--- a/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/fixed_results.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/fixed_results.xlsx
@@ -538,7 +538,7 @@
         <v>0.9999999806619203</v>
       </c>
       <c r="D2" t="n">
-        <v>0.687621867518375</v>
+        <v>0.6876218693451388</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999999439809756</v>
@@ -553,7 +553,7 @@
         <v>1.348770282944445e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2178739293897248</v>
+        <v>0.2178739281156145</v>
       </c>
       <c r="J2" t="n">
         <v>2.855521134126945e-08</v>
@@ -601,7 +601,7 @@
         <v>0.9999999804207697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6876192646743456</v>
+        <v>0.6876192637821648</v>
       </c>
       <c r="E3" t="n">
         <v>0.99999994613141</v>
@@ -616,7 +616,7 @@
         <v>1.36558978018298e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2178757447916281</v>
+        <v>0.2178757454138963</v>
       </c>
       <c r="J3" t="n">
         <v>2.745904609430782e-08</v>
@@ -664,7 +664,7 @@
         <v>0.9999999800112873</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6876170635554723</v>
+        <v>0.6876170626521457</v>
       </c>
       <c r="E4" t="n">
         <v>0.99999994815757</v>
@@ -679,7 +679,7 @@
         <v>1.394149884321051e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2178772800028614</v>
+        <v>0.2178772806329032</v>
       </c>
       <c r="J4" t="n">
         <v>2.64262286293823e-08</v>
@@ -727,7 +727,7 @@
         <v>0.9999999793581077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.687613779953085</v>
+        <v>0.6876137797467825</v>
       </c>
       <c r="E5" t="n">
         <v>0.9999999506888863</v>
@@ -742,7 +742,7 @@
         <v>1.439707111422609e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2178795702123231</v>
+        <v>0.2178795703562126</v>
       </c>
       <c r="J5" t="n">
         <v>2.513591214199747e-08</v>
@@ -790,7 +790,7 @@
         <v>0.9999999395272041</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6993689991271083</v>
+        <v>0.6993690008551376</v>
       </c>
       <c r="E6" t="n">
         <v>0.9999999379075246</v>
@@ -805,7 +805,7 @@
         <v>4.217787448118276e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2096806743039082</v>
+        <v>0.2096806730986621</v>
       </c>
       <c r="J6" t="n">
         <v>4.674797277166518e-08</v>
@@ -853,7 +853,7 @@
         <v>0.9999999165544189</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6993321158306869</v>
+        <v>0.6993321150599113</v>
       </c>
       <c r="E7" t="n">
         <v>0.9999999215478872</v>
@@ -868,7 +868,7 @@
         <v>5.82006701440073e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2097063992439235</v>
+        <v>0.2097063997815152</v>
       </c>
       <c r="J7" t="n">
         <v>5.906476118269603e-08</v>
@@ -916,7 +916,7 @@
         <v>0.9999996977015518</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7092111689960852</v>
+        <v>0.7092111689960855</v>
       </c>
       <c r="E8" t="n">
         <v>0.9999999436636311</v>
@@ -931,7 +931,7 @@
         <v>2.108436663793775e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>0.202816070158798</v>
+        <v>0.2028160701587978</v>
       </c>
       <c r="J8" t="n">
         <v>5.762961578110815e-08</v>
@@ -979,7 +979,7 @@
         <v>0.9999996917946546</v>
       </c>
       <c r="D9" t="n">
-        <v>0.709603594974836</v>
+        <v>0.7096035949748364</v>
       </c>
       <c r="E9" t="n">
         <v>0.9999998463743777</v>
@@ -994,7 +994,7 @@
         <v>2.149635415444389e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>0.202542365372532</v>
+        <v>0.2025423653725318</v>
       </c>
       <c r="J9" t="n">
         <v>1.57152222764505e-07</v>
@@ -1042,7 +1042,7 @@
         <v>0.9999996870684</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7094173706692528</v>
+        <v>0.7094173706692531</v>
       </c>
       <c r="E10" t="n">
         <v>0.9999999015487445</v>
@@ -1057,7 +1057,7 @@
         <v>2.18259955573923e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2026722509726634</v>
+        <v>0.2026722509726631</v>
       </c>
       <c r="J10" t="n">
         <v>1.007112836915295e-07</v>
@@ -1105,7 +1105,7 @@
         <v>0.9999996788573463</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7096055405836744</v>
+        <v>0.7096055405836748</v>
       </c>
       <c r="E11" t="n">
         <v>0.9999998668266097</v>
@@ -1120,7 +1120,7 @@
         <v>2.23986907433818e-07</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2025410083715176</v>
+        <v>0.2025410083715173</v>
       </c>
       <c r="J11" t="n">
         <v>1.362304932446047e-07</v>
@@ -1168,7 +1168,7 @@
         <v>0.9999901879963111</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6875647245101493</v>
+        <v>0.6875647262211237</v>
       </c>
       <c r="E12" t="n">
         <v>0.9999961488648854</v>
@@ -1183,7 +1183,7 @@
         <v>6.843564182611307e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2179137848419627</v>
+        <v>0.2179137836486118</v>
       </c>
       <c r="J12" t="n">
         <v>4.628792566847459e-06</v>
@@ -1231,7 +1231,7 @@
         <v>0.9999881130278672</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6878937146035831</v>
+        <v>0.6878937148124503</v>
       </c>
       <c r="E13" t="n">
         <v>0.9999956247171677</v>
@@ -1246,7 +1246,7 @@
         <v>8.290789456218834e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2176843245919212</v>
+        <v>0.2176843244462429</v>
       </c>
       <c r="J13" t="n">
         <v>5.258781125443174e-06</v>
@@ -1294,7 +1294,7 @@
         <v>0.9999624432869626</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6940630525253446</v>
+        <v>0.6940630525253451</v>
       </c>
       <c r="E14" t="n">
         <v>0.9999209896837229</v>
@@ -1309,7 +1309,7 @@
         <v>2.619462693954217e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2133814052932207</v>
+        <v>0.2133814052932204</v>
       </c>
       <c r="J14" t="n">
         <v>1.475490198270067e-05</v>
@@ -1357,7 +1357,7 @@
         <v>0.9999537885357667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6951906919065272</v>
+        <v>0.6951906919065274</v>
       </c>
       <c r="E15" t="n">
         <v>0.9999043494580043</v>
@@ -1372,7 +1372,7 @@
         <v>3.223104388062146e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2125949122664488</v>
+        <v>0.2125949122664486</v>
       </c>
       <c r="J15" t="n">
         <v>1.786240630640725e-05</v>
@@ -1420,7 +1420,7 @@
         <v>0.9999341760621283</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7053228294380571</v>
+        <v>0.7053228321503262</v>
       </c>
       <c r="E16" t="n">
         <v>0.9999008475262201</v>
@@ -1435,7 +1435,7 @@
         <v>4.591012782516773e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.205528064790365</v>
+        <v>0.2055280628986425</v>
       </c>
       <c r="J16" t="n">
         <v>8.456004079445233e-05</v>
@@ -1483,7 +1483,7 @@
         <v>0.999933801701145</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7052368644913747</v>
+        <v>0.705236865230241</v>
       </c>
       <c r="E17" t="n">
         <v>0.9998873563329915</v>
@@ -1498,7 +1498,7 @@
         <v>4.617123284486323e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2055880226388055</v>
+        <v>0.2055880221234696</v>
       </c>
       <c r="J17" t="n">
         <v>9.606571287992681e-05</v>
@@ -1546,7 +1546,7 @@
         <v>0.9998347941286017</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6946298100710873</v>
+        <v>0.6946298100710875</v>
       </c>
       <c r="E18" t="n">
         <v>0.9998678159818952</v>
@@ -1561,7 +1561,7 @@
         <v>0.000115225902894896</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2129861097182032</v>
+        <v>0.212986109718203</v>
       </c>
       <c r="J18" t="n">
         <v>5.292546349918628e-05</v>
@@ -1609,7 +1609,7 @@
         <v>0.9998633966794602</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6923963089712082</v>
+        <v>0.6923963089712084</v>
       </c>
       <c r="E19" t="n">
         <v>0.9999012449282039</v>
@@ -1624,7 +1624,7 @@
         <v>9.527652264659747e-05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.214543906536633</v>
+        <v>0.2145439065366329</v>
       </c>
       <c r="J19" t="n">
         <v>3.954077068198084e-05</v>
@@ -1661,5167 +1661,5167 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>model_8_4_8</t>
+          <t>model_1_9_10</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9999999887844401</v>
+        <v>0.9999824376857704</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6835956985437711</v>
+        <v>0.632739324669802</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999999827060823</v>
+        <v>0.9999788457550571</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9999999660585012</v>
+        <v>0.999976369464441</v>
       </c>
       <c r="G20" t="n">
-        <v>0.999999974118793</v>
+        <v>0.9999773445468096</v>
       </c>
       <c r="H20" t="n">
-        <v>7.822500553526071e-09</v>
+        <v>1.224916219316119e-05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2206820557073874</v>
+        <v>0.2561527780732892</v>
       </c>
       <c r="J20" t="n">
-        <v>1.319141805275543e-08</v>
+        <v>4.428862769549209e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>3.563857656477475e-08</v>
+        <v>3.897840316982885e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>2.441499730876509e-08</v>
+        <v>2.170338111783876e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>2.146399958705323e-05</v>
+        <v>0.0009337966631654914</v>
       </c>
       <c r="N20" t="n">
-        <v>8.844490122966993e-05</v>
+        <v>0.003499880311262257</v>
       </c>
       <c r="O20" t="n">
-        <v>1.000000006565206</v>
+        <v>1.000021074777075</v>
       </c>
       <c r="P20" t="n">
-        <v>9.22101837812024e-05</v>
+        <v>0.00364887746186371</v>
       </c>
       <c r="Q20" t="n">
-        <v>167.3325231392495</v>
+        <v>110.6201060314148</v>
       </c>
       <c r="R20" t="n">
-        <v>246.5594517556825</v>
+        <v>164.2506423256156</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Hidden Size=[16], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>model_8_4_9</t>
+          <t>model_1_9_11</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9999999887844401</v>
+        <v>0.9999812230682711</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6835956985437711</v>
+        <v>0.6321752101827884</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999999827060823</v>
+        <v>0.9999465781440237</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9999999660585012</v>
+        <v>0.9999734370016319</v>
       </c>
       <c r="G21" t="n">
-        <v>0.999999974118793</v>
+        <v>0.9999712934285331</v>
       </c>
       <c r="H21" t="n">
-        <v>7.822500553526071e-09</v>
+        <v>1.309631972362924e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2206820557073874</v>
+        <v>0.2565462301979142</v>
       </c>
       <c r="J21" t="n">
-        <v>1.319141805275543e-08</v>
+        <v>1.118442514271067e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>3.563857656477475e-08</v>
+        <v>4.381548006833604e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>2.441499730876509e-08</v>
+        <v>2.75002073848097e-05</v>
       </c>
       <c r="M21" t="n">
-        <v>2.146399958705323e-05</v>
+        <v>0.0009322422409937476</v>
       </c>
       <c r="N21" t="n">
-        <v>8.844490122966993e-05</v>
+        <v>0.003618883767631843</v>
       </c>
       <c r="O21" t="n">
-        <v>1.000000006565206</v>
+        <v>1.000022532318075</v>
       </c>
       <c r="P21" t="n">
-        <v>9.22101837812024e-05</v>
+        <v>0.003772947141742065</v>
       </c>
       <c r="Q21" t="n">
-        <v>167.3325231392495</v>
+        <v>110.4863586087099</v>
       </c>
       <c r="R21" t="n">
-        <v>246.5594517556825</v>
+        <v>164.1168949029107</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Hidden Size=[16], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>model_8_4_13</t>
+          <t>model_1_9_9</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9999999887844401</v>
+        <v>0.9999810071025832</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6835956985437711</v>
+        <v>0.6333633637238554</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999999827060823</v>
+        <v>0.9999957632228472</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9999999660585012</v>
+        <v>0.9999751579086703</v>
       </c>
       <c r="G22" t="n">
-        <v>0.999999974118793</v>
+        <v>0.9999781498345034</v>
       </c>
       <c r="H22" t="n">
-        <v>7.822500553526071e-09</v>
+        <v>1.324694900318108e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2206820557073874</v>
+        <v>0.2557175304465775</v>
       </c>
       <c r="J22" t="n">
-        <v>1.319141805275543e-08</v>
+        <v>8.870136771804359e-07</v>
       </c>
       <c r="K22" t="n">
-        <v>3.563857656477475e-08</v>
+        <v>4.097685594184648e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>2.441499730876509e-08</v>
+        <v>2.093193480951346e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>2.146399958705323e-05</v>
+        <v>0.0009662341618183339</v>
       </c>
       <c r="N22" t="n">
-        <v>8.844490122966993e-05</v>
+        <v>0.003639635833868695</v>
       </c>
       <c r="O22" t="n">
-        <v>1.000000006565206</v>
+        <v>1.0000227914769</v>
       </c>
       <c r="P22" t="n">
-        <v>9.22101837812024e-05</v>
+        <v>0.003794582666401319</v>
       </c>
       <c r="Q22" t="n">
-        <v>167.3325231392495</v>
+        <v>110.4634865919154</v>
       </c>
       <c r="R22" t="n">
-        <v>246.5594517556825</v>
+        <v>164.0940228861162</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Hidden Size=[16], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>model_8_4_5</t>
+          <t>model_15_8_5</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9999999887844401</v>
+        <v>0.9999783783833383</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6835956985437711</v>
+        <v>0.7149941759477471</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9999999827060823</v>
+        <v>0.9995860565780834</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999999660585012</v>
+        <v>0.9999943726253411</v>
       </c>
       <c r="G23" t="n">
-        <v>0.999999974118793</v>
+        <v>0.9999030852053284</v>
       </c>
       <c r="H23" t="n">
-        <v>7.822500553526071e-09</v>
+        <v>1.5080398056136e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2206820557073874</v>
+        <v>0.1987826045693948</v>
       </c>
       <c r="J23" t="n">
-        <v>1.319141805275543e-08</v>
+        <v>9.026402385932538e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>3.563857656477475e-08</v>
+        <v>3.988461790937978e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>2.441499730876509e-08</v>
+        <v>4.712624282513169e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>2.146399958705323e-05</v>
+        <v>0.001332518631016334</v>
       </c>
       <c r="N23" t="n">
-        <v>8.844490122966993e-05</v>
+        <v>0.003883348819786346</v>
       </c>
       <c r="O23" t="n">
-        <v>1.000000006565206</v>
+        <v>1.000019219214811</v>
       </c>
       <c r="P23" t="n">
-        <v>9.22101837812024e-05</v>
+        <v>0.004048671018684913</v>
       </c>
       <c r="Q23" t="n">
-        <v>167.3325231392495</v>
+        <v>124.2042295988747</v>
       </c>
       <c r="R23" t="n">
-        <v>246.5594517556825</v>
+        <v>186.3668966671529</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Hidden Size=[16], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>model_8_4_6</t>
+          <t>model_15_8_1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9999999887844401</v>
+        <v>0.9999783778667723</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6835956985437711</v>
+        <v>0.7149944826474529</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999999827060823</v>
+        <v>0.9995860503843127</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999999660585012</v>
+        <v>0.9999943713609607</v>
       </c>
       <c r="G24" t="n">
-        <v>0.999999974118793</v>
+        <v>0.9999030820196078</v>
       </c>
       <c r="H24" t="n">
-        <v>7.822500553526071e-09</v>
+        <v>1.508075834457701e-05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2206820557073874</v>
+        <v>0.1987823906559895</v>
       </c>
       <c r="J24" t="n">
-        <v>1.319141805275543e-08</v>
+        <v>9.026537446580411e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>3.563857656477475e-08</v>
+        <v>3.989357933954833e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>2.441499730876509e-08</v>
+        <v>4.712779192864263e-05</v>
       </c>
       <c r="M24" t="n">
-        <v>2.146399958705323e-05</v>
+        <v>0.001332664111957869</v>
       </c>
       <c r="N24" t="n">
-        <v>8.844490122966993e-05</v>
+        <v>0.00388339520839394</v>
       </c>
       <c r="O24" t="n">
-        <v>1.000000006565206</v>
+        <v>1.00001921967398</v>
       </c>
       <c r="P24" t="n">
-        <v>9.22101837812024e-05</v>
+        <v>0.004048719382151571</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.3325231392495</v>
+        <v>124.2041818170939</v>
       </c>
       <c r="R24" t="n">
-        <v>246.5594517556825</v>
+        <v>186.3668488853721</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Hidden Size=[16], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>model_20_9_20</t>
+          <t>model_15_8_4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9999999776156919</v>
+        <v>0.9999783778495409</v>
       </c>
       <c r="D25" t="n">
-        <v>0.70803319562976</v>
+        <v>0.7149942983076065</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9999998853395371</v>
+        <v>0.9995860515040325</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999999406512844</v>
+        <v>0.9999943709038286</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9999999371899754</v>
+        <v>0.9999030828130285</v>
       </c>
       <c r="H25" t="n">
-        <v>1.561235133768988e-08</v>
+        <v>1.50807703629823e-05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2036376695582144</v>
+        <v>0.1987825192272386</v>
       </c>
       <c r="J25" t="n">
-        <v>3.793026996765561e-08</v>
+        <v>9.026513030100994e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>2.045748774287647e-08</v>
+        <v>3.989681931275974e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>2.919387885526604e-08</v>
+        <v>4.712740611614296e-05</v>
       </c>
       <c r="M25" t="n">
-        <v>6.1231462494511e-05</v>
+        <v>0.00133253333351798</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0001249493951073389</v>
+        <v>0.003883396755803133</v>
       </c>
       <c r="O25" t="n">
-        <v>1.00000001013629</v>
+        <v>1.000019219689297</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0001302687495379635</v>
+        <v>0.004048720995437177</v>
       </c>
       <c r="Q25" t="n">
-        <v>189.950406967091</v>
+        <v>124.2041802232217</v>
       </c>
       <c r="R25" t="n">
-        <v>283.8038454819425</v>
+        <v>186.3668472915</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Hidden Size=[19], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>151</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>model_20_9_23</t>
+          <t>model_15_91_11</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9999999812194195</v>
+        <v>0.9999783777212938</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7080345817484653</v>
+        <v>0.7149939389980543</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9999998789965512</v>
+        <v>0.9999756800773948</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999999393674259</v>
+        <v>0.9999847319162147</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9999999344566952</v>
+        <v>0.9999805134869362</v>
       </c>
       <c r="H26" t="n">
-        <v>1.30988646247155e-08</v>
+        <v>1.508085981127559e-05</v>
       </c>
       <c r="I26" t="n">
-        <v>0.203636702783983</v>
+        <v>0.1987827698343582</v>
       </c>
       <c r="J26" t="n">
-        <v>4.002856226273664e-08</v>
+        <v>1.582264551773423e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>2.090003346106222e-08</v>
+        <v>9.387385216441107e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>3.046429786189944e-08</v>
+        <v>1.260544106559774e-05</v>
       </c>
       <c r="M26" t="n">
-        <v>5.290216123826098e-05</v>
+        <v>0.001332416715603493</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0001144502714051631</v>
+        <v>0.003883408272545599</v>
       </c>
       <c r="O26" t="n">
-        <v>1.000000008504414</v>
+        <v>1.000019219803294</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0001193226564036038</v>
+        <v>0.004048733002471212</v>
       </c>
       <c r="Q26" t="n">
-        <v>190.3014805607288</v>
+        <v>124.204168360694</v>
       </c>
       <c r="R26" t="n">
-        <v>284.1549190755802</v>
+        <v>186.3668354289723</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Hidden Size=[19], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>model_20_9_22</t>
+          <t>model_15_91_5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9999999802970565</v>
+        <v>0.9999783777212938</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7080340850189037</v>
+        <v>0.7149939389980543</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9999998808139947</v>
+        <v>0.9999756800773948</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9999999398400927</v>
+        <v>0.9999847319162147</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9999999352787192</v>
+        <v>0.9999805134869362</v>
       </c>
       <c r="H27" t="n">
-        <v>1.374218386225786e-08</v>
+        <v>1.508085981127559e-05</v>
       </c>
       <c r="I27" t="n">
-        <v>0.20363704923724</v>
+        <v>0.1987827698343582</v>
       </c>
       <c r="J27" t="n">
-        <v>3.942734262666055e-08</v>
+        <v>1.582264551773423e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>2.073710533227211e-08</v>
+        <v>9.387385216441107e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>3.008222397946634e-08</v>
+        <v>1.260544106559774e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>5.537371231447737e-05</v>
+        <v>0.001332416715603493</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0001172270611346112</v>
+        <v>0.003883408272545599</v>
       </c>
       <c r="O27" t="n">
-        <v>1.000000008922088</v>
+        <v>1.000019219803294</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0001222176598205816</v>
+        <v>0.004048733002471212</v>
       </c>
       <c r="Q27" t="n">
-        <v>190.2055912416839</v>
+        <v>124.204168360694</v>
       </c>
       <c r="R27" t="n">
-        <v>284.0590297565354</v>
+        <v>186.3668354289723</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Hidden Size=[19], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>model_15_9_2</t>
+          <t>model_15_91_17</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.999999975528733</v>
+        <v>0.9999783777212938</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6894521869611354</v>
+        <v>0.7149939389980543</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9999999662175618</v>
+        <v>0.9999756800773948</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9999998366697398</v>
+        <v>0.9999847319162147</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9999999491909892</v>
+        <v>0.9999805134869362</v>
       </c>
       <c r="H28" t="n">
-        <v>1.706793958350636e-08</v>
+        <v>1.508085981127559e-05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2165973391051725</v>
+        <v>0.1987827698343582</v>
       </c>
       <c r="J28" t="n">
-        <v>4.483960547832417e-08</v>
+        <v>1.582264551773423e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>6.017377490972669e-08</v>
+        <v>9.387385216441107e-06</v>
       </c>
       <c r="L28" t="n">
-        <v>5.250669019402543e-08</v>
+        <v>1.260544106559774e-05</v>
       </c>
       <c r="M28" t="n">
-        <v>4.555879112221499e-05</v>
+        <v>0.001332416715603493</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0001306443247275072</v>
+        <v>0.003883408272545599</v>
       </c>
       <c r="O28" t="n">
-        <v>1.000000011985927</v>
+        <v>1.000019219803294</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0001362061241021919</v>
+        <v>0.004048733002471212</v>
       </c>
       <c r="Q28" t="n">
-        <v>181.7721280227586</v>
+        <v>124.204168360694</v>
       </c>
       <c r="R28" t="n">
-        <v>270.7500632381373</v>
+        <v>186.3668354289723</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Hidden Size=[18], regularizer=0.05, learning_rate=0.01</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>159</v>
+        <v>9</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>model_15_9_1</t>
+          <t>model_15_91_16</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9999999755245295</v>
+        <v>0.9999783777212938</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6894524529842996</v>
+        <v>0.7149939389980543</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9999999662177108</v>
+        <v>0.9999756800773948</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9999998368622159</v>
+        <v>0.9999847319162147</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9999999492253945</v>
+        <v>0.9999805134869362</v>
       </c>
       <c r="H29" t="n">
-        <v>1.707087142979436e-08</v>
+        <v>1.508085981127559e-05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2165971535623766</v>
+        <v>0.1987827698343582</v>
       </c>
       <c r="J29" t="n">
-        <v>4.48394076306118e-08</v>
+        <v>1.582264551773423e-05</v>
       </c>
       <c r="K29" t="n">
-        <v>6.010286328354651e-08</v>
+        <v>9.387385216441107e-06</v>
       </c>
       <c r="L29" t="n">
-        <v>5.247113545707916e-08</v>
+        <v>1.260544106559774e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>4.565299679878966e-05</v>
+        <v>0.001332416715603493</v>
       </c>
       <c r="N29" t="n">
-        <v>0.000130655544963826</v>
+        <v>0.003883408272545599</v>
       </c>
       <c r="O29" t="n">
-        <v>1.000000011987985</v>
+        <v>1.000019219803294</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0001362178220071998</v>
+        <v>0.004048733002471212</v>
       </c>
       <c r="Q29" t="n">
-        <v>181.7717845021487</v>
+        <v>124.204168360694</v>
       </c>
       <c r="R29" t="n">
-        <v>270.7497197175273</v>
+        <v>186.3668354289723</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Hidden Size=[18], regularizer=0.05, learning_rate=0.01</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>464</v>
+        <v>10</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>model_10_7_10</t>
+          <t>model_15_91_15</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9999995213032573</v>
+        <v>0.9999783777212938</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6359279436152309</v>
+        <v>0.7149939389980543</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9999995178447941</v>
+        <v>0.9999756800773948</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9999980705207312</v>
+        <v>0.9999847319162147</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9999992061370397</v>
+        <v>0.9999805134869362</v>
       </c>
       <c r="H30" t="n">
-        <v>3.338759326595451e-07</v>
+        <v>1.508085981127559e-05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2539288165768551</v>
+        <v>0.1987827698343582</v>
       </c>
       <c r="J30" t="n">
-        <v>5.576939187906515e-07</v>
+        <v>1.582264551773423e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>8.552502340626587e-07</v>
+        <v>9.387385216441107e-06</v>
       </c>
       <c r="L30" t="n">
-        <v>7.06472076426655e-07</v>
+        <v>1.260544106559774e-05</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0001540369443877847</v>
+        <v>0.001332416715603493</v>
       </c>
       <c r="N30" t="n">
-        <v>0.000577819982918162</v>
+        <v>0.003883408272545599</v>
       </c>
       <c r="O30" t="n">
-        <v>1.000000255304929</v>
+        <v>1.000019219803294</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0006024189758432475</v>
+        <v>0.004048733002471212</v>
       </c>
       <c r="Q30" t="n">
-        <v>167.8249927441618</v>
+        <v>124.204168360694</v>
       </c>
       <c r="R30" t="n">
-        <v>251.9274246600676</v>
+        <v>186.3668354289723</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>513</v>
+        <v>11</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>model_12_8_18</t>
+          <t>model_15_91_14</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9999994479220363</v>
+        <v>0.9999783777212938</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6827176608502481</v>
+        <v>0.7149939389980543</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9999997203035355</v>
+        <v>0.9999756800773948</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9999937807402967</v>
+        <v>0.9999847319162147</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9999981266371775</v>
+        <v>0.9999805134869362</v>
       </c>
       <c r="H31" t="n">
-        <v>3.850570278988963e-07</v>
+        <v>1.508085981127559e-05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2212944594019751</v>
+        <v>0.1987827698343582</v>
       </c>
       <c r="J31" t="n">
-        <v>2.111152381245624e-07</v>
+        <v>1.582264551773423e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>2.1939276825075e-06</v>
+        <v>9.387385216441107e-06</v>
       </c>
       <c r="L31" t="n">
-        <v>1.202521460316031e-06</v>
+        <v>1.260544106559774e-05</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0001200476928500252</v>
+        <v>0.001332416715603493</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0006205296349884479</v>
+        <v>0.003883408272545599</v>
       </c>
       <c r="O31" t="n">
-        <v>1.000000294441581</v>
+        <v>1.000019219803294</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0006469468662233334</v>
+        <v>0.004048733002471212</v>
       </c>
       <c r="Q31" t="n">
-        <v>167.5397487784305</v>
+        <v>124.204168360694</v>
       </c>
       <c r="R31" t="n">
-        <v>251.6421806943363</v>
+        <v>186.3668354289723</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>514</v>
+        <v>166</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>model_12_8_19</t>
+          <t>model_26_8_20</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9999994462674966</v>
+        <v>0.9999175600278689</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6827171015794838</v>
+        <v>0.6844242091420173</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9999997210608862</v>
+        <v>0.9998829304706699</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9999937578791099</v>
+        <v>0.9986958490108135</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9999981208515529</v>
+        <v>0.9998249307160491</v>
       </c>
       <c r="H32" t="n">
-        <v>3.862110173575958e-07</v>
+        <v>5.749928948059668e-05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2212948494757553</v>
+        <v>0.2201041956051232</v>
       </c>
       <c r="J32" t="n">
-        <v>2.105435888813036e-07</v>
+        <v>5.499577353764501e-05</v>
       </c>
       <c r="K32" t="n">
-        <v>2.201992274258454e-06</v>
+        <v>0.0001822836770231747</v>
       </c>
       <c r="L32" t="n">
-        <v>1.206235283170666e-06</v>
+        <v>0.0001186395041790392</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0001197426196332044</v>
+        <v>0.003552437546164673</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0006214587817044633</v>
+        <v>0.007582828593644768</v>
       </c>
       <c r="O32" t="n">
-        <v>1.000000295324002</v>
+        <v>1.000058192921504</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0006479155686386485</v>
+        <v>0.007905645305495354</v>
       </c>
       <c r="Q32" t="n">
-        <v>167.5337638795257</v>
+        <v>135.527475934193</v>
       </c>
       <c r="R32" t="n">
-        <v>251.6361957954315</v>
+        <v>206.2222737765486</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>515</v>
+        <v>167</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>model_12_8_20</t>
+          <t>model_26_8_22</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9999994448873223</v>
+        <v>0.9999174181823928</v>
       </c>
       <c r="D33" t="n">
-        <v>0.682716629649437</v>
+        <v>0.6844970630138659</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9999997219480435</v>
+        <v>0.9998709921095716</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9999937382295067</v>
+        <v>0.9985695115522971</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9999981159229973</v>
+        <v>0.9998077634031004</v>
       </c>
       <c r="H33" t="n">
-        <v>3.871736455549835e-07</v>
+        <v>5.759822224207356e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2212951786321303</v>
+        <v>0.2200533823192994</v>
       </c>
       <c r="J33" t="n">
-        <v>2.098739614213454e-07</v>
+        <v>6.060405954618704e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>2.20892393665629e-06</v>
+        <v>0.0001999421051308726</v>
       </c>
       <c r="L33" t="n">
-        <v>1.209398949038818e-06</v>
+        <v>0.0001302733068104245</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0001194048094189576</v>
+        <v>0.003579759020839035</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0006222327904851877</v>
+        <v>0.007589349263413403</v>
       </c>
       <c r="O33" t="n">
-        <v>1.000000296060095</v>
+        <v>1.000058293047723</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0006487225285755874</v>
+        <v>0.007912443573675688</v>
       </c>
       <c r="Q33" t="n">
-        <v>167.5287850960526</v>
+        <v>135.5240377091832</v>
       </c>
       <c r="R33" t="n">
-        <v>251.6312170119585</v>
+        <v>206.2188355515389</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>516</v>
+        <v>168</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>model_12_8_21</t>
+          <t>model_26_8_19</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9999994423553863</v>
+        <v>0.9999171132901271</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6827156959790139</v>
+        <v>0.6843842430849003</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9999997231764592</v>
+        <v>0.9998891344438654</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9999937032811899</v>
+        <v>0.9987554601202251</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9999981070421852</v>
+        <v>0.9998332285172216</v>
       </c>
       <c r="H34" t="n">
-        <v>3.889395913476652e-07</v>
+        <v>5.781087501457174e-05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2212958298379052</v>
+        <v>0.2201320706738328</v>
       </c>
       <c r="J34" t="n">
-        <v>2.089467516491023e-07</v>
+        <v>5.208133195026384e-05</v>
       </c>
       <c r="K34" t="n">
-        <v>2.221252426442816e-06</v>
+        <v>0.0001739517182967122</v>
       </c>
       <c r="L34" t="n">
-        <v>1.215099589045959e-06</v>
+        <v>0.0001130163189196471</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0001189082115615162</v>
+        <v>0.003537470590598948</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0006236502155436693</v>
+        <v>0.007603346303738357</v>
       </c>
       <c r="O34" t="n">
-        <v>1.000000297410461</v>
+        <v>1.000058508265793</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0006502002963532829</v>
+        <v>0.007927036496985144</v>
       </c>
       <c r="Q34" t="n">
-        <v>167.5196835951049</v>
+        <v>135.5166673018854</v>
       </c>
       <c r="R34" t="n">
-        <v>251.6221155110107</v>
+        <v>206.2114651442411</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>465</v>
+        <v>169</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>model_12_8_1</t>
+          <t>model_26_8_23</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.999999514529348</v>
+        <v>0.9999169242335386</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6827503306944052</v>
+        <v>0.6845303143463952</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9999996529120336</v>
+        <v>0.9998652723934057</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9999949409738189</v>
+        <v>0.9985039579636773</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9999984058223177</v>
+        <v>0.9997990205907366</v>
       </c>
       <c r="H35" t="n">
-        <v>3.386005214513614e-07</v>
+        <v>5.794273604307085e-05</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2212716732124858</v>
+        <v>0.2200301905599465</v>
       </c>
       <c r="J35" t="n">
-        <v>2.61982427255746e-07</v>
+        <v>6.329101162296232e-05</v>
       </c>
       <c r="K35" t="n">
-        <v>1.784639670103916e-06</v>
+        <v>0.0002091046555370538</v>
       </c>
       <c r="L35" t="n">
-        <v>1.023311048679831e-06</v>
+        <v>0.0001361980635728198</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0001400536389194251</v>
+        <v>0.003592432253035084</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0005818939091031642</v>
+        <v>0.00761201261448448</v>
       </c>
       <c r="O35" t="n">
-        <v>1.000000258917681</v>
+        <v>1.000058641717502</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0006066663375001349</v>
+        <v>0.007936071750521466</v>
       </c>
       <c r="Q35" t="n">
-        <v>167.7968896544537</v>
+        <v>135.5121106894625</v>
       </c>
       <c r="R35" t="n">
-        <v>251.8993215703595</v>
+        <v>206.2069085318181</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>849</v>
+        <v>170</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>model_4_8_3</t>
+          <t>model_26_8_18</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9999975732308737</v>
+        <v>0.9999162441627131</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6760507191202545</v>
+        <v>0.6843416630972603</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9999755059529065</v>
+        <v>0.9998954560609334</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9999765983017626</v>
+        <v>0.9988116207934004</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9999762480379871</v>
+        <v>0.9998412117896859</v>
       </c>
       <c r="H36" t="n">
-        <v>1.692595192512898e-06</v>
+        <v>5.841706406934232e-05</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2259444417172752</v>
+        <v>0.2201617688769266</v>
       </c>
       <c r="J36" t="n">
-        <v>5.789084837835901e-06</v>
+        <v>4.911162478001668e-05</v>
       </c>
       <c r="K36" t="n">
-        <v>4.789634174250745e-06</v>
+        <v>0.0001661020336395298</v>
       </c>
       <c r="L36" t="n">
-        <v>5.289280146564661e-06</v>
+        <v>0.0001076062808734784</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0003098770912610102</v>
+        <v>0.00352172106373943</v>
       </c>
       <c r="N36" t="n">
-        <v>0.001300997768066071</v>
+        <v>0.007643105656036839</v>
       </c>
       <c r="O36" t="n">
-        <v>1.000001574120514</v>
+        <v>1.000059121767497</v>
       </c>
       <c r="P36" t="n">
-        <v>0.001356383936489294</v>
+        <v>0.007968488487224177</v>
       </c>
       <c r="Q36" t="n">
-        <v>148.5784951800234</v>
+        <v>135.4958050356839</v>
       </c>
       <c r="R36" t="n">
-        <v>222.9299204969836</v>
+        <v>206.1906028780395</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Hidden Size=[15], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>850</v>
+        <v>171</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>model_4_8_2</t>
+          <t>model_26_8_24</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9999975732649335</v>
+        <v>0.999916202485718</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6760507234946704</v>
+        <v>0.6845614681017209</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9999755052296538</v>
+        <v>0.9998596919703749</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9999765998640118</v>
+        <v>0.9984375597114954</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9999762480157337</v>
+        <v>0.9997902392984934</v>
       </c>
       <c r="H37" t="n">
-        <v>1.692571436764949e-06</v>
+        <v>5.844613246347704e-05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2259444386662576</v>
+        <v>0.2200084617947666</v>
       </c>
       <c r="J37" t="n">
-        <v>5.78925577614039e-06</v>
+        <v>6.591252793893064e-05</v>
       </c>
       <c r="K37" t="n">
-        <v>4.789314428138526e-06</v>
+        <v>0.0002183852661841201</v>
       </c>
       <c r="L37" t="n">
-        <v>5.289285102139458e-06</v>
+        <v>0.0001421488970615254</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0003099256102038868</v>
+        <v>0.003604406103626687</v>
       </c>
       <c r="N37" t="n">
-        <v>0.001300988638215165</v>
+        <v>0.007645007028347132</v>
       </c>
       <c r="O37" t="n">
-        <v>1.000001574098421</v>
+        <v>1.000059151186552</v>
       </c>
       <c r="P37" t="n">
-        <v>0.001356374417961734</v>
+        <v>0.007970470804890103</v>
       </c>
       <c r="Q37" t="n">
-        <v>148.5785232504264</v>
+        <v>135.4948100810499</v>
       </c>
       <c r="R37" t="n">
-        <v>222.9299485673867</v>
+        <v>206.1896079234055</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Hidden Size=[15], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1158</v>
+        <v>206</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>model_22_9_8</t>
+          <t>model_1_7_5</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9999929202281488</v>
+        <v>0.9999019210168766</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7046803583826999</v>
+        <v>0.6416420531688076</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9998732845916114</v>
+        <v>0.9996850657358354</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9999886761980677</v>
+        <v>0.9998822701620602</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9999825673235379</v>
+        <v>0.9998292185994488</v>
       </c>
       <c r="H38" t="n">
-        <v>4.937918349671362e-06</v>
+        <v>6.840700811507937e-05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2059761681586699</v>
+        <v>0.2499434047571774</v>
       </c>
       <c r="J38" t="n">
-        <v>1.779512456270932e-05</v>
+        <v>4.986914109913049e-05</v>
       </c>
       <c r="K38" t="n">
-        <v>5.515522572451323e-06</v>
+        <v>3.635885438510682e-05</v>
       </c>
       <c r="L38" t="n">
-        <v>1.165532356758032e-05</v>
+        <v>4.311399774211865e-05</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0006562202678881386</v>
+        <v>0.00331983683548586</v>
       </c>
       <c r="N38" t="n">
-        <v>0.002222142738365689</v>
+        <v>0.008270852925489569</v>
       </c>
       <c r="O38" t="n">
-        <v>1.000002980956569</v>
+        <v>1.000117694779748</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002316743955207526</v>
+        <v>0.008622960257553502</v>
       </c>
       <c r="Q38" t="n">
-        <v>186.437133404558</v>
+        <v>107.1800705615228</v>
       </c>
       <c r="R38" t="n">
-        <v>285.1660752188822</v>
+        <v>160.8106068557236</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Hidden Size=[20], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1159</v>
+        <v>271</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>model_22_9_9</t>
+          <t>model_24_6_1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9999929102937389</v>
+        <v>0.9998772568522829</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7045279138799019</v>
+        <v>0.6953236951806069</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9998680042352619</v>
+        <v>0.9992464413357113</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9999871627208635</v>
+        <v>0.9999311630973508</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9999814613623329</v>
+        <v>0.9996049314884677</v>
       </c>
       <c r="H39" t="n">
-        <v>4.944847288244522e-06</v>
+        <v>8.560948772677005e-05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2060824934080547</v>
+        <v>0.2125021466630589</v>
       </c>
       <c r="J39" t="n">
-        <v>1.853666499706751e-05</v>
+        <v>0.0004869797480956775</v>
       </c>
       <c r="K39" t="n">
-        <v>6.252697042040485e-06</v>
+        <v>4.807953428294554e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>1.239475883018185e-05</v>
+        <v>0.0002675279455697005</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0006558249157261669</v>
+        <v>0.003039641464052098</v>
       </c>
       <c r="N39" t="n">
-        <v>0.002223701258767581</v>
+        <v>0.009252539528517024</v>
       </c>
       <c r="O39" t="n">
-        <v>1.000002985139478</v>
+        <v>1.000056650683562</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002318368825049508</v>
+        <v>0.009646439291643251</v>
       </c>
       <c r="Q39" t="n">
-        <v>186.4343289508403</v>
+        <v>170.7314288860582</v>
       </c>
       <c r="R39" t="n">
-        <v>285.1632707651645</v>
+        <v>263.3659915760414</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Hidden Size=[20], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125</v>
+        <v>272</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>model_34_6_8</t>
+          <t>model_24_6_2</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9806908472843459</v>
+        <v>0.9998772535679586</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9965704493670673</v>
+        <v>0.6953236171988354</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9629377668455102</v>
+        <v>0.9992464253770095</v>
       </c>
       <c r="F40" t="n">
-        <v>0.963700872596626</v>
+        <v>0.9999311582642559</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9635936996655063</v>
+        <v>0.9996049188770614</v>
       </c>
       <c r="H40" t="n">
-        <v>0.01346752713426032</v>
+        <v>8.561177843968698e-05</v>
       </c>
       <c r="I40" t="n">
-        <v>1.392545136406434</v>
+        <v>0.2125022010528936</v>
       </c>
       <c r="J40" t="n">
-        <v>0.01719451591716697</v>
+        <v>0.0004869900612470943</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0584851285020009</v>
+        <v>4.808290998608842e-05</v>
       </c>
       <c r="L40" t="n">
-        <v>0.03783982220958394</v>
+        <v>0.0002675364856165914</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1723521648806496</v>
+        <v>0.00303957893450805</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1160496752871817</v>
+        <v>0.0092526633160235</v>
       </c>
       <c r="O40" t="n">
-        <v>1.006716227031532</v>
+        <v>1.000056652199404</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1209901502201025</v>
+        <v>0.009646568349040152</v>
       </c>
       <c r="Q40" t="n">
-        <v>194.6149477772319</v>
+        <v>170.7313753713758</v>
       </c>
       <c r="R40" t="n">
-        <v>307.9703994899746</v>
+        <v>263.3659380613591</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Hidden Size=[23], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130</v>
+        <v>273</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>model_34_6_11</t>
+          <t>model_24_6_3</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9803773538413249</v>
+        <v>0.9998772468545838</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.9921128778537884</v>
+        <v>0.6953233864263156</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9634169254006607</v>
+        <v>0.9992463892956478</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9602460593099947</v>
+        <v>0.9999311488343215</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9610228805108989</v>
+        <v>0.9996048968369156</v>
       </c>
       <c r="H41" t="n">
-        <v>0.01368617895769712</v>
+        <v>8.561646080760894e-05</v>
       </c>
       <c r="I41" t="n">
-        <v>1.389436120376988</v>
+        <v>0.212502362009473</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01697221686224933</v>
+        <v>0.000487013378466105</v>
       </c>
       <c r="K41" t="n">
-        <v>0.06405152123573549</v>
+        <v>4.808949637853128e-05</v>
       </c>
       <c r="L41" t="n">
-        <v>0.04051186904899241</v>
+        <v>0.0002675514105087907</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1754274818582809</v>
+        <v>0.003039656208896305</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1169879436424844</v>
+        <v>0.009252916340679242</v>
       </c>
       <c r="O41" t="n">
-        <v>1.006825268229104</v>
+        <v>1.000056655297884</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1219683626017736</v>
+        <v>0.009646832145479322</v>
       </c>
       <c r="Q41" t="n">
-        <v>194.5827375811388</v>
+        <v>170.7312659882988</v>
       </c>
       <c r="R41" t="n">
-        <v>307.9381892938814</v>
+        <v>263.365828678282</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Hidden Size=[23], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>model_34_6_5</t>
+          <t>model_24_6_4</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9802612232452551</v>
+        <v>0.9998772453676729</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.003990345818492</v>
+        <v>0.6953233605968566</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9611316016262702</v>
+        <v>0.9992463876845833</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9677064119909918</v>
+        <v>0.9999311419456817</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9662952160954289</v>
+        <v>0.9996048924758356</v>
       </c>
       <c r="H42" t="n">
-        <v>0.01376717639848175</v>
+        <v>8.561749788130167e-05</v>
       </c>
       <c r="I42" t="n">
-        <v>1.397720280974634</v>
+        <v>0.2125023800247088</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01803246155529951</v>
+        <v>0.0004870144196003748</v>
       </c>
       <c r="K42" t="n">
-        <v>0.05203140625143408</v>
+        <v>4.809430778904601e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>0.03503193180420581</v>
+        <v>0.0002675543636947104</v>
       </c>
       <c r="M42" t="n">
-        <v>0.167995048995626</v>
+        <v>0.00303958479201932</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1173336115462306</v>
+        <v>0.009252972380878572</v>
       </c>
       <c r="O42" t="n">
-        <v>1.006865661479911</v>
+        <v>1.000056655984151</v>
       </c>
       <c r="P42" t="n">
-        <v>0.1223287463038135</v>
+        <v>0.009646890571425959</v>
       </c>
       <c r="Q42" t="n">
-        <v>194.5709360836892</v>
+        <v>170.7312417624104</v>
       </c>
       <c r="R42" t="n">
-        <v>307.9263877964319</v>
+        <v>263.3658044523936</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Hidden Size=[23], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132</v>
+        <v>418</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>model_34_6_12</t>
+          <t>model_10_9_17</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9802022524823231</v>
+        <v>0.9998543467922655</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.9910547376355927</v>
+        <v>0.7208698788780216</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9634215042793883</v>
+        <v>0.9995018676523859</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9592389220848575</v>
+        <v>0.9998057146463667</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9602432901511693</v>
+        <v>0.9996241831794923</v>
       </c>
       <c r="H43" t="n">
-        <v>0.01380830665218113</v>
+        <v>0.0001015885345277736</v>
       </c>
       <c r="I43" t="n">
-        <v>1.388698100832047</v>
+        <v>0.1946844864483355</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0169700925541204</v>
+        <v>0.0003479491282802201</v>
       </c>
       <c r="K43" t="n">
-        <v>0.06567422002341544</v>
+        <v>9.022056172498979e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>0.04132215628876793</v>
+        <v>0.0002190848450026049</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1762365941024472</v>
+        <v>0.002894344699846855</v>
       </c>
       <c r="N43" t="n">
-        <v>0.117508751385508</v>
+        <v>0.01007911377690388</v>
       </c>
       <c r="O43" t="n">
-        <v>1.006886173049627</v>
+        <v>1.000057306180092</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1225113422086384</v>
+        <v>0.01050820251702851</v>
       </c>
       <c r="Q43" t="n">
-        <v>194.564969873179</v>
+        <v>188.3891597566478</v>
       </c>
       <c r="R43" t="n">
-        <v>307.9204215859216</v>
+        <v>291.9936048704449</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Hidden Size=[23], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133</v>
+        <v>419</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>model_34_6_13</t>
+          <t>model_10_9_20</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9800116462893799</v>
+        <v>0.999854301070547</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.9901532961923787</v>
+        <v>0.7204679321271619</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9633796912261227</v>
+        <v>0.9994480783848717</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9583042116034012</v>
+        <v>0.9997738911845117</v>
       </c>
       <c r="G44" t="n">
-        <v>0.959509476923382</v>
+        <v>0.9995792821478924</v>
       </c>
       <c r="H44" t="n">
-        <v>0.01394124848102377</v>
+        <v>0.0001016204239894585</v>
       </c>
       <c r="I44" t="n">
-        <v>1.388069373757628</v>
+        <v>0.1949648316739104</v>
       </c>
       <c r="J44" t="n">
-        <v>0.01698949114801857</v>
+        <v>0.0003855213293871159</v>
       </c>
       <c r="K44" t="n">
-        <v>0.06718022489269677</v>
+        <v>0.0001049984672690873</v>
       </c>
       <c r="L44" t="n">
-        <v>0.04208486389210559</v>
+        <v>0.0002452601916389126</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1769580560370133</v>
+        <v>0.002764731093614225</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1180730641637786</v>
+        <v>0.01008069561039606</v>
       </c>
       <c r="O44" t="n">
-        <v>1.006952470855868</v>
+        <v>1.000057324168965</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1230996789501684</v>
+        <v>0.0105098516924473</v>
       </c>
       <c r="Q44" t="n">
-        <v>194.5458066332221</v>
+        <v>188.3885320390082</v>
       </c>
       <c r="R44" t="n">
-        <v>307.9012583459648</v>
+        <v>291.9929771528053</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Hidden Size=[23], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134</v>
+        <v>415</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>model_34_6_14</t>
+          <t>model_10_9_18</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.979813478097858</v>
+        <v>0.9998547274585187</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.9893830481882042</v>
+        <v>0.7207292005712203</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9633041723704688</v>
+        <v>0.9994839610083919</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9574405960241208</v>
+        <v>0.9997948718218834</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9588232612125925</v>
+        <v>0.9996091359398528</v>
       </c>
       <c r="H45" t="n">
-        <v>0.01407946456620206</v>
+        <v>0.0001013230317805038</v>
       </c>
       <c r="I45" t="n">
-        <v>1.38753214998354</v>
+        <v>0.194782605145823</v>
       </c>
       <c r="J45" t="n">
-        <v>0.01702452708770879</v>
+        <v>0.0003604570515219385</v>
       </c>
       <c r="K45" t="n">
-        <v>0.06857168170567371</v>
+        <v>9.525565931348651e-05</v>
       </c>
       <c r="L45" t="n">
-        <v>0.04279809979509822</v>
+        <v>0.0002278567306241799</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1776009689220075</v>
+        <v>0.002848804037435473</v>
       </c>
       <c r="N45" t="n">
-        <v>0.1186569195883749</v>
+        <v>0.01006593422293747</v>
       </c>
       <c r="O45" t="n">
-        <v>1.007021398922484</v>
+        <v>1.000057156409763</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1237083903089371</v>
+        <v>0.01049446188216431</v>
       </c>
       <c r="Q45" t="n">
-        <v>194.5260759138878</v>
+        <v>188.3943936209094</v>
       </c>
       <c r="R45" t="n">
-        <v>307.8815276266305</v>
+        <v>291.9988387347065</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Hidden Size=[23], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126</v>
+        <v>416</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>model_34_6_7</t>
+          <t>model_10_9_19</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9806661310394891</v>
+        <v>0.999854692656029</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.9986332732174552</v>
+        <v>0.720595313506849</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9625354390946866</v>
+        <v>0.999466008085379</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9649858853632356</v>
+        <v>0.9997842459584683</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9644998961898456</v>
+        <v>0.9995941489397034</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0134847659382186</v>
+        <v>0.0001013473054232298</v>
       </c>
       <c r="I46" t="n">
-        <v>1.393983891207714</v>
+        <v>0.1948759871651637</v>
       </c>
       <c r="J46" t="n">
-        <v>0.01738117037176009</v>
+        <v>0.0003729973010004347</v>
       </c>
       <c r="K46" t="n">
-        <v>0.05641471683764528</v>
+        <v>0.0001001900063870504</v>
       </c>
       <c r="L46" t="n">
-        <v>0.03689794360470269</v>
+        <v>0.0002365934992454596</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1710644725107767</v>
+        <v>0.002805611729938771</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1161239249173856</v>
+        <v>0.01006713988296725</v>
       </c>
       <c r="O46" t="n">
-        <v>1.006724823986265</v>
+        <v>1.000057170102546</v>
       </c>
       <c r="P46" t="n">
-        <v>0.121067560810782</v>
+        <v>0.01049571886963762</v>
       </c>
       <c r="Q46" t="n">
-        <v>194.6123893594732</v>
+        <v>188.39391454453</v>
       </c>
       <c r="R46" t="n">
-        <v>307.9678410722158</v>
+        <v>291.998359658327</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Hidden Size=[23], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_15_7_16</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9994222233025335</v>
+        <v>-0.8346009946397621</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.215862919385021</v>
+        <v>0.3175671701132302</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9980310875093036</v>
+        <v>-10.46650935349295</v>
       </c>
       <c r="F47" t="n">
-        <v>0.993448884739919</v>
+        <v>-2.938171018242795</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9979130968726405</v>
+        <v>-1.39983232327821</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0004029810870140097</v>
+        <v>1.279576532419326</v>
       </c>
       <c r="I47" t="n">
-        <v>1.545494741901628</v>
+        <v>0.4759754500444304</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0009966098583761185</v>
+        <v>0.4264866759692428</v>
       </c>
       <c r="K47" t="n">
-        <v>0.001201181665842214</v>
+        <v>2.862870052383867</v>
       </c>
       <c r="L47" t="n">
-        <v>0.00109889619536468</v>
+        <v>1.644678282477699</v>
       </c>
       <c r="M47" t="n">
-        <v>0.007736235556064311</v>
+        <v>0.8002961772715763</v>
       </c>
       <c r="N47" t="n">
-        <v>0.02007438883288878</v>
+        <v>1.131183686418491</v>
       </c>
       <c r="O47" t="n">
-        <v>1.000322480017191</v>
+        <v>4.386955682411869</v>
       </c>
       <c r="P47" t="n">
-        <v>0.02092899712521844</v>
+        <v>1.179340517822367</v>
       </c>
       <c r="Q47" t="n">
-        <v>149.6332418552104</v>
+        <v>73.50694162170707</v>
       </c>
       <c r="R47" t="n">
-        <v>231.2979221213798</v>
+        <v>118.6053471418305</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_15_7_15</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9994214399446949</v>
+        <v>-0.8346009946397621</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.214961070023567</v>
+        <v>0.3175671701132302</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9980944253599157</v>
+        <v>-10.46650935349295</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9929229407799136</v>
+        <v>-2.938171018242795</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9978519776448332</v>
+        <v>-1.39983232327821</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0004035274544855323</v>
+        <v>1.279576532419326</v>
       </c>
       <c r="I48" t="n">
-        <v>1.544865730317057</v>
+        <v>0.4759754500444304</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0009645499640808861</v>
+        <v>0.4264866759692428</v>
       </c>
       <c r="K48" t="n">
-        <v>0.001297616275361055</v>
+        <v>2.862870052383867</v>
       </c>
       <c r="L48" t="n">
-        <v>0.001131079618744766</v>
+        <v>1.644678282477699</v>
       </c>
       <c r="M48" t="n">
-        <v>0.00770800453586945</v>
+        <v>0.8002961772715763</v>
       </c>
       <c r="N48" t="n">
-        <v>0.02008799279384409</v>
+        <v>1.131183686418491</v>
       </c>
       <c r="O48" t="n">
-        <v>1.00032291724017</v>
+        <v>4.386955682411869</v>
       </c>
       <c r="P48" t="n">
-        <v>0.02094318023495571</v>
+        <v>1.179340517822367</v>
       </c>
       <c r="Q48" t="n">
-        <v>149.6305320634252</v>
+        <v>73.50694162170707</v>
       </c>
       <c r="R48" t="n">
-        <v>231.2952123295946</v>
+        <v>118.6053471418305</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_15_7_14</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9994198551031707</v>
+        <v>-0.8346009946397621</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.216871211807754</v>
+        <v>0.3175671701132302</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9979562688355529</v>
+        <v>-10.46650935349295</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9940097282580392</v>
+        <v>-2.938171018242795</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9979747824793055</v>
+        <v>-1.39983232327821</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0004046328316372937</v>
+        <v>1.279576532419326</v>
       </c>
       <c r="I49" t="n">
-        <v>1.546197994175945</v>
+        <v>0.4759754500444304</v>
       </c>
       <c r="J49" t="n">
-        <v>0.001034481032541016</v>
+        <v>0.4264866759692428</v>
       </c>
       <c r="K49" t="n">
-        <v>0.001098348037577801</v>
+        <v>2.862870052383867</v>
       </c>
       <c r="L49" t="n">
-        <v>0.001066414535059408</v>
+        <v>1.644678282477699</v>
       </c>
       <c r="M49" t="n">
-        <v>0.007766876982261291</v>
+        <v>0.8002961772715763</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0201154873576877</v>
+        <v>1.131183686418491</v>
       </c>
       <c r="O49" t="n">
-        <v>1.000323801802881</v>
+        <v>4.386955682411869</v>
       </c>
       <c r="P49" t="n">
-        <v>0.02097184529930373</v>
+        <v>1.179340517822367</v>
       </c>
       <c r="Q49" t="n">
-        <v>149.6250609812151</v>
+        <v>73.50694162170707</v>
       </c>
       <c r="R49" t="n">
-        <v>231.2897412473846</v>
+        <v>118.6053471418305</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_15_7_13</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9994183876556122</v>
+        <v>-0.8346009946397621</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.214154139067569</v>
+        <v>0.3175671701132302</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9981481816016304</v>
+        <v>-10.46650935349295</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9924325866343769</v>
+        <v>-2.938171018242795</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9977924440286084</v>
+        <v>-1.39983232327821</v>
       </c>
       <c r="H50" t="n">
-        <v>0.000405656330187586</v>
+        <v>1.279576532419326</v>
       </c>
       <c r="I50" t="n">
-        <v>1.544302921337015</v>
+        <v>0.4759754500444304</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0009373400191517166</v>
+        <v>0.4264866759692428</v>
       </c>
       <c r="K50" t="n">
-        <v>0.001387525303977516</v>
+        <v>2.862870052383867</v>
       </c>
       <c r="L50" t="n">
-        <v>0.001162428109965102</v>
+        <v>1.644678282477699</v>
       </c>
       <c r="M50" t="n">
-        <v>0.007681717344675583</v>
+        <v>0.8002961772715763</v>
       </c>
       <c r="N50" t="n">
-        <v>0.02014091185094622</v>
+        <v>1.131183686418491</v>
       </c>
       <c r="O50" t="n">
-        <v>1.000324620843379</v>
+        <v>4.386955682411869</v>
       </c>
       <c r="P50" t="n">
-        <v>0.02099835216587622</v>
+        <v>1.179340517822367</v>
       </c>
       <c r="Q50" t="n">
-        <v>149.6200084683946</v>
+        <v>73.50694162170707</v>
       </c>
       <c r="R50" t="n">
-        <v>231.284688734564</v>
+        <v>118.6053471418305</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_15_7_23</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9994137222909962</v>
+        <v>-0.8346009946397621</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.213431681027461</v>
+        <v>0.3175671701132302</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9981938985183032</v>
+        <v>-10.46650935349295</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9919773681380805</v>
+        <v>-2.938171018242795</v>
       </c>
       <c r="G51" t="n">
-        <v>0.997735157057506</v>
+        <v>-1.39983232327821</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0004089102753752285</v>
+        <v>1.279576532419326</v>
       </c>
       <c r="I51" t="n">
-        <v>1.543799029560829</v>
+        <v>0.4759754500444304</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0009141993615217084</v>
+        <v>0.4264866759692428</v>
       </c>
       <c r="K51" t="n">
-        <v>0.001470992025290693</v>
+        <v>2.862870052383867</v>
       </c>
       <c r="L51" t="n">
-        <v>0.001192593589983376</v>
+        <v>1.644678282477699</v>
       </c>
       <c r="M51" t="n">
-        <v>0.007657484786282116</v>
+        <v>0.8002961772715763</v>
       </c>
       <c r="N51" t="n">
-        <v>0.02022152999590359</v>
+        <v>1.131183686418491</v>
       </c>
       <c r="O51" t="n">
-        <v>1.000327224767816</v>
+        <v>4.386955682411869</v>
       </c>
       <c r="P51" t="n">
-        <v>0.02108240239216699</v>
+        <v>1.179340517822367</v>
       </c>
       <c r="Q51" t="n">
-        <v>149.604029603197</v>
+        <v>73.50694162170707</v>
       </c>
       <c r="R51" t="n">
-        <v>231.2687098693664</v>
+        <v>118.6053471418305</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.9994132312482719</v>
+        <v>-0.8373299699203969</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.217999180319584</v>
+        <v>0.7110100186810322</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9978676537970956</v>
+        <v>-1.660000410834247</v>
       </c>
       <c r="F52" t="n">
-        <v>0.994603742611607</v>
+        <v>-3.046506564858483</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9980356114422755</v>
+        <v>-0.9829999421786029</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0004092527622420131</v>
+        <v>1.281479906906125</v>
       </c>
       <c r="I52" t="n">
-        <v>1.546984716760999</v>
+        <v>0.201561429041229</v>
       </c>
       <c r="J52" t="n">
-        <v>0.001079335550628661</v>
+        <v>1.346419734370387</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0009894323610210956</v>
+        <v>0.7419484016768835</v>
       </c>
       <c r="L52" t="n">
-        <v>0.001034383955824878</v>
+        <v>1.044184113435906</v>
       </c>
       <c r="M52" t="n">
-        <v>0.007799741126195694</v>
+        <v>0.8029720724244975</v>
       </c>
       <c r="N52" t="n">
-        <v>0.02022999659520518</v>
+        <v>1.132024693593795</v>
       </c>
       <c r="O52" t="n">
-        <v>1.000327498838174</v>
+        <v>2.259883407945415</v>
       </c>
       <c r="P52" t="n">
-        <v>0.02109122943212912</v>
+        <v>1.180217328414249</v>
       </c>
       <c r="Q52" t="n">
-        <v>149.602355184427</v>
+        <v>117.5039688253126</v>
       </c>
       <c r="R52" t="n">
-        <v>231.2670354505964</v>
+        <v>189.4176424925364</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.9994079804950831</v>
+        <v>-0.8373299699203969</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.212784597767559</v>
+        <v>0.7110100186810322</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9982328894567501</v>
+        <v>-1.660000410834247</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9915565250116015</v>
+        <v>-3.046506564858483</v>
       </c>
       <c r="G53" t="n">
-        <v>0.997680620672819</v>
+        <v>-0.9829999421786029</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0004129149975604951</v>
+        <v>1.281479906906125</v>
       </c>
       <c r="I53" t="n">
-        <v>1.543347709324816</v>
+        <v>0.201561429041229</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0008944632108156055</v>
+        <v>1.346419734370387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.001548155840557769</v>
+        <v>0.7419484016768835</v>
       </c>
       <c r="L53" t="n">
-        <v>0.001221310699491631</v>
+        <v>1.044184113435906</v>
       </c>
       <c r="M53" t="n">
-        <v>0.007635223633581962</v>
+        <v>0.8029720724244975</v>
       </c>
       <c r="N53" t="n">
-        <v>0.02032030997697858</v>
+        <v>1.132024693593795</v>
       </c>
       <c r="O53" t="n">
-        <v>1.000330429491116</v>
+        <v>2.259883407945415</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02118538764153909</v>
+        <v>1.180217328414249</v>
       </c>
       <c r="Q53" t="n">
-        <v>149.5845376064626</v>
+        <v>117.5039688253126</v>
       </c>
       <c r="R53" t="n">
-        <v>231.249217872632</v>
+        <v>189.4176424925364</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>model_23_9_12</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.9994015625663231</v>
+        <v>-0.8373299699203969</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.212204578315365</v>
+        <v>0.7110100186810322</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9982662481859317</v>
+        <v>-1.660000410834247</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9911687427898362</v>
+        <v>-3.046506564858483</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9976291491767525</v>
+        <v>-0.9829999421786029</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0004173913011557393</v>
+        <v>1.281479906906125</v>
       </c>
       <c r="I54" t="n">
-        <v>1.542943163986869</v>
+        <v>0.201561429041229</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0008775779309860843</v>
+        <v>1.346419734370387</v>
       </c>
       <c r="K54" t="n">
-        <v>0.00161925776391458</v>
+        <v>0.7419484016768835</v>
       </c>
       <c r="L54" t="n">
-        <v>0.001248413937038087</v>
+        <v>1.044184113435906</v>
       </c>
       <c r="M54" t="n">
-        <v>0.007614966570989626</v>
+        <v>0.8029720724244975</v>
       </c>
       <c r="N54" t="n">
-        <v>0.02043015666008803</v>
+        <v>1.132024693593795</v>
       </c>
       <c r="O54" t="n">
-        <v>1.000334011590889</v>
+        <v>2.259883407945415</v>
       </c>
       <c r="P54" t="n">
-        <v>0.02129991072536249</v>
+        <v>1.180217328414249</v>
       </c>
       <c r="Q54" t="n">
-        <v>149.5629728081704</v>
+        <v>117.5039688253126</v>
       </c>
       <c r="R54" t="n">
-        <v>231.2276530743398</v>
+        <v>189.4176424925364</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>model_19_9_4</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9851270915948591</v>
+        <v>-0.8373299699203969</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.183530531908446</v>
+        <v>0.7110100186810322</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9817337032197653</v>
+        <v>-1.660000410834247</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9796321310432828</v>
+        <v>-3.046506564858483</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9860799989066572</v>
+        <v>-0.9829999421786029</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0103733861584313</v>
+        <v>1.281479906906125</v>
       </c>
       <c r="I55" t="n">
-        <v>1.522943917840706</v>
+        <v>0.201561429041229</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01579808808055</v>
+        <v>1.346419734370387</v>
       </c>
       <c r="K55" t="n">
-        <v>0.005463377292529593</v>
+        <v>0.7419484016768835</v>
       </c>
       <c r="L55" t="n">
-        <v>0.01063072078036867</v>
+        <v>1.044184113435906</v>
       </c>
       <c r="M55" t="n">
-        <v>0.04945284371550981</v>
+        <v>0.8029720724244975</v>
       </c>
       <c r="N55" t="n">
-        <v>0.1018498215925354</v>
+        <v>1.132024693593795</v>
       </c>
       <c r="O55" t="n">
-        <v>1.006999015720066</v>
+        <v>2.259883407945415</v>
       </c>
       <c r="P55" t="n">
-        <v>0.1061857793559256</v>
+        <v>1.180217328414249</v>
       </c>
       <c r="Q55" t="n">
-        <v>159.1370235519185</v>
+        <v>117.5039688253126</v>
       </c>
       <c r="R55" t="n">
-        <v>250.5527104170336</v>
+        <v>189.4176424925364</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 7], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>model_19_9_3</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.983364399007113</v>
+        <v>-0.8373299699203969</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.187747130232372</v>
+        <v>0.7110100186810322</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9818856977667689</v>
+        <v>-1.660000410834247</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9890145336316298</v>
+        <v>-3.046506564858483</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9878137414542055</v>
+        <v>-0.9829999421786029</v>
       </c>
       <c r="H56" t="n">
-        <v>0.01160280883711698</v>
+        <v>1.281479906906125</v>
       </c>
       <c r="I56" t="n">
-        <v>1.525884862644343</v>
+        <v>0.201561429041229</v>
       </c>
       <c r="J56" t="n">
-        <v>0.01566663159157386</v>
+        <v>1.346419734370387</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00294668763002856</v>
+        <v>0.7419484016768835</v>
       </c>
       <c r="L56" t="n">
-        <v>0.00930665961080121</v>
+        <v>1.044184113435906</v>
       </c>
       <c r="M56" t="n">
-        <v>0.04658561916637306</v>
+        <v>0.8029720724244975</v>
       </c>
       <c r="N56" t="n">
-        <v>0.1077163350523818</v>
+        <v>1.132024693593795</v>
       </c>
       <c r="O56" t="n">
-        <v>1.0078285181143</v>
+        <v>2.259883407945415</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1123020424391147</v>
+        <v>1.180217328414249</v>
       </c>
       <c r="Q56" t="n">
-        <v>158.9130161381009</v>
+        <v>117.5039688253126</v>
       </c>
       <c r="R56" t="n">
-        <v>250.328703003216</v>
+        <v>189.4176424925364</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 7], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>model_25_9_21</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.9812122665999468</v>
+        <v>-0.8373299699203969</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.127661043121466</v>
+        <v>0.7110100186810322</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9999740301413741</v>
+        <v>-1.660000410834247</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9920219830039159</v>
+        <v>-3.046506564858483</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9938783002374351</v>
+        <v>-0.9829999421786029</v>
       </c>
       <c r="H57" t="n">
-        <v>0.01310385354979022</v>
+        <v>1.281479906906125</v>
       </c>
       <c r="I57" t="n">
-        <v>1.483976705384723</v>
+        <v>0.201561429041229</v>
       </c>
       <c r="J57" t="n">
-        <v>4.399042390705269e-06</v>
+        <v>1.346419734370387</v>
       </c>
       <c r="K57" t="n">
-        <v>0.005997784036268253</v>
+        <v>0.7419484016768835</v>
       </c>
       <c r="L57" t="n">
-        <v>0.00300109153932948</v>
+        <v>1.044184113435906</v>
       </c>
       <c r="M57" t="n">
-        <v>0.03105946380343061</v>
+        <v>0.8029720724244975</v>
       </c>
       <c r="N57" t="n">
-        <v>0.1144720644951868</v>
+        <v>1.132024693593795</v>
       </c>
       <c r="O57" t="n">
-        <v>1.008671261569255</v>
+        <v>2.259883407945415</v>
       </c>
       <c r="P57" t="n">
-        <v>0.1193453772705878</v>
+        <v>1.180217328414249</v>
       </c>
       <c r="Q57" t="n">
-        <v>160.6696978558534</v>
+        <v>117.5039688253126</v>
       </c>
       <c r="R57" t="n">
-        <v>253.3042605458366</v>
+        <v>189.4176424925364</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 6], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>251</v>
+        <v>177</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>model_25_7_9</t>
+          <t>model_5_5_20</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.9812122665999468</v>
+        <v>0.999872460934557</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.127661043121466</v>
+        <v>0.4272465209132277</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9944015935482765</v>
+        <v>0.9999797698452421</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9987723732705883</v>
+        <v>0.9996650388518905</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9981855870840236</v>
+        <v>0.9998672456542589</v>
       </c>
       <c r="H58" t="n">
-        <v>0.01310385354979022</v>
+        <v>8.8954489605355e-05</v>
       </c>
       <c r="I58" t="n">
-        <v>1.483976705384723</v>
+        <v>0.3994775500734228</v>
       </c>
       <c r="J58" t="n">
-        <v>0.001264078154876628</v>
+        <v>5.900260647481696e-06</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0006922575961502595</v>
+        <v>5.830575251664376e-05</v>
       </c>
       <c r="L58" t="n">
-        <v>0.0009781678755134437</v>
+        <v>3.210300658206273e-05</v>
       </c>
       <c r="M58" t="n">
-        <v>0.03105946380343061</v>
+        <v>0.003378190416651791</v>
       </c>
       <c r="N58" t="n">
-        <v>0.1144720644951868</v>
+        <v>0.009431568777534044</v>
       </c>
       <c r="O58" t="n">
-        <v>1.008671261569255</v>
+        <v>1.003060937570633</v>
       </c>
       <c r="P58" t="n">
-        <v>0.1193453772705878</v>
+        <v>0.00983309018643256</v>
       </c>
       <c r="Q58" t="n">
-        <v>160.6696978558534</v>
+        <v>68.65477134353272</v>
       </c>
       <c r="R58" t="n">
-        <v>253.3042605458366</v>
+        <v>99.12666696523773</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 6], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 2], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>model_3_9_17</t>
+          <t>model_5_5_19</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.9981337244395351</v>
+        <v>0.999872460934557</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.129687375783148</v>
+        <v>0.4272465209132277</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9981550003080292</v>
+        <v>0.9999797698452421</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9642503881674657</v>
+        <v>0.9996650388518905</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9879537649727851</v>
+        <v>0.9998672456542589</v>
       </c>
       <c r="H59" t="n">
-        <v>0.001301668546553642</v>
+        <v>8.8954489605355e-05</v>
       </c>
       <c r="I59" t="n">
-        <v>1.485390008728796</v>
+        <v>0.3994775500734228</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0004389765237607787</v>
+        <v>5.900260647481696e-06</v>
       </c>
       <c r="K59" t="n">
-        <v>0.006648599233412404</v>
+        <v>5.830575251664376e-05</v>
       </c>
       <c r="L59" t="n">
-        <v>0.003543788016314006</v>
+        <v>3.210300658206273e-05</v>
       </c>
       <c r="M59" t="n">
-        <v>0.01926871906488325</v>
+        <v>0.003378190416651791</v>
       </c>
       <c r="N59" t="n">
-        <v>0.03607864391234297</v>
+        <v>0.009431568777534044</v>
       </c>
       <c r="O59" t="n">
-        <v>1.001317370983858</v>
+        <v>1.003060937570633</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0376145864767802</v>
+        <v>0.00983309018643256</v>
       </c>
       <c r="Q59" t="n">
-        <v>129.2882166802886</v>
+        <v>68.65477134353272</v>
       </c>
       <c r="R59" t="n">
-        <v>199.9830145226442</v>
+        <v>99.12666696523773</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 2], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>model_3_9_18</t>
+          <t>model_5_5_18</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.99813069544636</v>
+        <v>0.999872460934557</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.130556511072789</v>
+        <v>0.4272465209132277</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9981734522944796</v>
+        <v>0.9999797698452421</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9630860448900022</v>
+        <v>0.9996650388518905</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9875931904456695</v>
+        <v>0.9998672456542589</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00130378117409229</v>
+        <v>8.8954489605355e-05</v>
       </c>
       <c r="I60" t="n">
-        <v>1.485996203276478</v>
+        <v>0.3994775500734228</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0004345862851586896</v>
+        <v>5.900260647481696e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>0.006865140097079278</v>
+        <v>5.830575251664376e-05</v>
       </c>
       <c r="L60" t="n">
-        <v>0.003649862626787176</v>
+        <v>3.210300658206273e-05</v>
       </c>
       <c r="M60" t="n">
-        <v>0.01808945234528061</v>
+        <v>0.003378190416651791</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0361079101318851</v>
+        <v>0.009431568777534044</v>
       </c>
       <c r="O60" t="n">
-        <v>1.001319509096687</v>
+        <v>1.003060937570633</v>
       </c>
       <c r="P60" t="n">
-        <v>0.03764509861987767</v>
+        <v>0.00983309018643256</v>
       </c>
       <c r="Q60" t="n">
-        <v>129.284973281677</v>
+        <v>68.65477134353272</v>
       </c>
       <c r="R60" t="n">
-        <v>199.9797711240326</v>
+        <v>99.12666696523773</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 2], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>model_3_9_16</t>
+          <t>model_5_5_17</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.9981301544134182</v>
+        <v>0.999872460934557</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.128728522562406</v>
+        <v>0.4272465209132277</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9981260778588105</v>
+        <v>0.9999797698452421</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9655240072121135</v>
+        <v>0.9996650388518905</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9883446488761505</v>
+        <v>0.9998672456542589</v>
       </c>
       <c r="H61" t="n">
-        <v>0.001304158527564585</v>
+        <v>8.8954489605355e-05</v>
       </c>
       <c r="I61" t="n">
-        <v>1.484721238743997</v>
+        <v>0.3994775500734228</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0004458579754335983</v>
+        <v>5.900260647481696e-06</v>
       </c>
       <c r="K61" t="n">
-        <v>0.006411735609729672</v>
+        <v>5.830575251664376e-05</v>
       </c>
       <c r="L61" t="n">
-        <v>0.003428796926617779</v>
+        <v>3.210300658206273e-05</v>
       </c>
       <c r="M61" t="n">
-        <v>0.02057888642296909</v>
+        <v>0.003378190416651791</v>
       </c>
       <c r="N61" t="n">
-        <v>0.03611313511126644</v>
+        <v>0.009431568777534044</v>
       </c>
       <c r="O61" t="n">
-        <v>1.001319891002293</v>
+        <v>1.003060937570633</v>
       </c>
       <c r="P61" t="n">
-        <v>0.03765054603744847</v>
+        <v>0.00983309018643256</v>
       </c>
       <c r="Q61" t="n">
-        <v>129.284394505297</v>
+        <v>68.65477134353272</v>
       </c>
       <c r="R61" t="n">
-        <v>199.9791923476526</v>
+        <v>99.12666696523773</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 2], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>model_3_9_19</t>
+          <t>model_5_5_16</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.9981228993423897</v>
+        <v>0.999872460934557</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.131343490528958</v>
+        <v>0.4272465209132277</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9981842076404479</v>
+        <v>0.9999797698452421</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9620229414745076</v>
+        <v>0.9996650388518905</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9872615007031802</v>
+        <v>0.9998672456542589</v>
       </c>
       <c r="H62" t="n">
-        <v>0.001309218711580695</v>
+        <v>8.8954489605355e-05</v>
       </c>
       <c r="I62" t="n">
-        <v>1.486545096712463</v>
+        <v>0.3994775500734228</v>
       </c>
       <c r="J62" t="n">
-        <v>0.000432027290484861</v>
+        <v>5.900260647481696e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>0.007062852692852496</v>
+        <v>5.830575251664376e-05</v>
       </c>
       <c r="L62" t="n">
-        <v>0.00374743984754638</v>
+        <v>3.210300658206273e-05</v>
       </c>
       <c r="M62" t="n">
-        <v>0.01702835389364897</v>
+        <v>0.003378190416651791</v>
       </c>
       <c r="N62" t="n">
-        <v>0.036183127443336</v>
+        <v>0.009431568777534044</v>
       </c>
       <c r="O62" t="n">
-        <v>1.001325012228901</v>
+        <v>1.003060937570633</v>
       </c>
       <c r="P62" t="n">
-        <v>0.03772351808799834</v>
+        <v>0.00983309018643256</v>
       </c>
       <c r="Q62" t="n">
-        <v>129.2766494461237</v>
+        <v>68.65477134353272</v>
       </c>
       <c r="R62" t="n">
-        <v>199.9714472884793</v>
+        <v>99.12666696523773</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 2], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>352</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>model_3_9_15</t>
+          <t>model_25_7_7</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.9981175982374935</v>
+        <v>-0.816952813625083</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.127671065952589</v>
+        <v>0.6470604733949927</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9980837240190319</v>
+        <v>-3.676586454247006</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9669134291887883</v>
+        <v>-0.9194854511108208</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9887667051311743</v>
+        <v>-0.9832083899478554</v>
       </c>
       <c r="H63" t="n">
-        <v>0.001312916065632645</v>
+        <v>1.267267480842307</v>
       </c>
       <c r="I63" t="n">
-        <v>1.483983695994415</v>
+        <v>0.2461642269498667</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0004559351269013356</v>
+        <v>1.055938118674048</v>
       </c>
       <c r="K63" t="n">
-        <v>0.006153335324650226</v>
+        <v>1.082396100049207</v>
       </c>
       <c r="L63" t="n">
-        <v>0.003304635485687487</v>
+        <v>1.069167178217443</v>
       </c>
       <c r="M63" t="n">
-        <v>0.02203469196392295</v>
+        <v>0.8011946819012681</v>
       </c>
       <c r="N63" t="n">
-        <v>0.03623418366173916</v>
+        <v>1.125729754800106</v>
       </c>
       <c r="O63" t="n">
-        <v>1.001328754185299</v>
+        <v>2.282554927264765</v>
       </c>
       <c r="P63" t="n">
-        <v>0.03777674787531986</v>
+        <v>1.173654401043793</v>
       </c>
       <c r="Q63" t="n">
-        <v>129.2710092226927</v>
+        <v>115.526274014825</v>
       </c>
       <c r="R63" t="n">
-        <v>199.9658070650484</v>
+        <v>186.2210718571806</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>5</v>
+        <v>353</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>model_3_9_20</t>
+          <t>model_25_7_9</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.9981118086414319</v>
+        <v>-0.816952813625083</v>
       </c>
       <c r="D64" t="n">
-        <v>-1.132055813985704</v>
+        <v>0.6470604733949927</v>
       </c>
       <c r="E64" t="n">
-        <v>0.998189013129679</v>
+        <v>-3.676586454247006</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9610546278303016</v>
+        <v>-0.9194854511108208</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9869573665628893</v>
+        <v>-0.9832083899478554</v>
       </c>
       <c r="H64" t="n">
-        <v>0.001316954126919092</v>
+        <v>1.267267480842307</v>
       </c>
       <c r="I64" t="n">
-        <v>1.487041919935282</v>
+        <v>0.2461642269498667</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0004308839315093466</v>
+        <v>1.055938118674048</v>
       </c>
       <c r="K64" t="n">
-        <v>0.007242936588105091</v>
+        <v>1.082396100049207</v>
       </c>
       <c r="L64" t="n">
-        <v>0.003836910700412858</v>
+        <v>1.069167178217443</v>
       </c>
       <c r="M64" t="n">
-        <v>0.01607311387122099</v>
+        <v>0.8011946819012681</v>
       </c>
       <c r="N64" t="n">
-        <v>0.03628986259162595</v>
+        <v>1.125729754800106</v>
       </c>
       <c r="O64" t="n">
-        <v>1.001332840958989</v>
+        <v>2.282554927264765</v>
       </c>
       <c r="P64" t="n">
-        <v>0.03783479717252321</v>
+        <v>1.173654401043793</v>
       </c>
       <c r="Q64" t="n">
-        <v>129.2648673766483</v>
+        <v>115.526274014825</v>
       </c>
       <c r="R64" t="n">
-        <v>199.9596652190039</v>
+        <v>186.2210718571806</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>22</v>
+        <v>354</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>model_21_9_21</t>
+          <t>model_25_7_13</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.9974968849240629</v>
+        <v>-0.816952813625083</v>
       </c>
       <c r="D65" t="n">
-        <v>-1.173569078516263</v>
+        <v>0.6470604733949927</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9594126995355589</v>
+        <v>-3.676586454247006</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9481888173245564</v>
+        <v>-0.9194854511108208</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9833373806474599</v>
+        <v>-0.9832083899478554</v>
       </c>
       <c r="H65" t="n">
-        <v>0.001745844092787655</v>
+        <v>1.267267480842307</v>
       </c>
       <c r="I65" t="n">
-        <v>1.51599611718723</v>
+        <v>0.2461642269498667</v>
       </c>
       <c r="J65" t="n">
-        <v>0.003124962899905926</v>
+        <v>1.055938118674048</v>
       </c>
       <c r="K65" t="n">
-        <v>0.006794491777915712</v>
+        <v>1.082396100049207</v>
       </c>
       <c r="L65" t="n">
-        <v>0.00495972065593496</v>
+        <v>1.069167178217443</v>
       </c>
       <c r="M65" t="n">
-        <v>0.01333442629344843</v>
+        <v>0.8011946819012681</v>
       </c>
       <c r="N65" t="n">
-        <v>0.04178329920898606</v>
+        <v>1.125729754800106</v>
       </c>
       <c r="O65" t="n">
-        <v>1.001397087484244</v>
+        <v>2.282554927264765</v>
       </c>
       <c r="P65" t="n">
-        <v>0.04356210075966582</v>
+        <v>1.173654401043793</v>
       </c>
       <c r="Q65" t="n">
-        <v>146.7010342389754</v>
+        <v>115.526274014825</v>
       </c>
       <c r="R65" t="n">
-        <v>228.3657145051449</v>
+        <v>186.2210718571806</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>model_21_9_20</t>
+          <t>model_25_7_5</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.9974962913603277</v>
+        <v>-0.816952813625083</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.173012583441425</v>
+        <v>0.6470604733949927</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9603449504635835</v>
+        <v>-3.676586454247006</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9493958937563933</v>
+        <v>-0.9194854511108208</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9837237990209369</v>
+        <v>-0.9832083899478554</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00174625808483731</v>
+        <v>1.267267480842307</v>
       </c>
       <c r="I66" t="n">
-        <v>1.51560797936312</v>
+        <v>0.2461642269498667</v>
       </c>
       <c r="J66" t="n">
-        <v>0.003053185532844228</v>
+        <v>1.055938118674048</v>
       </c>
       <c r="K66" t="n">
-        <v>0.006636196397113316</v>
+        <v>1.082396100049207</v>
       </c>
       <c r="L66" t="n">
-        <v>0.004844701093390945</v>
+        <v>1.069167178217443</v>
       </c>
       <c r="M66" t="n">
-        <v>0.01356670794187652</v>
+        <v>0.8011946819012681</v>
       </c>
       <c r="N66" t="n">
-        <v>0.04178825295268169</v>
+        <v>1.125729754800106</v>
       </c>
       <c r="O66" t="n">
-        <v>1.001397418775631</v>
+        <v>2.282554927264765</v>
       </c>
       <c r="P66" t="n">
-        <v>0.04356726539448624</v>
+        <v>1.173654401043793</v>
       </c>
       <c r="Q66" t="n">
-        <v>146.7005600351515</v>
+        <v>115.526274014825</v>
       </c>
       <c r="R66" t="n">
-        <v>228.3652403013209</v>
+        <v>186.2210718571806</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>24</v>
+        <v>356</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>model_21_9_22</t>
+          <t>model_25_7_4</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.9974918114400293</v>
+        <v>-0.816952813625083</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.174071706334519</v>
+        <v>0.6470604733949927</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9585558406596628</v>
+        <v>-3.676586454247006</v>
       </c>
       <c r="F67" t="n">
-        <v>0.94708623450764</v>
+        <v>-0.9194854511108208</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9829836473801606</v>
+        <v>-0.9832083899478554</v>
       </c>
       <c r="H67" t="n">
-        <v>0.001749382688441911</v>
+        <v>1.267267480842307</v>
       </c>
       <c r="I67" t="n">
-        <v>1.516346684292917</v>
+        <v>0.2461642269498667</v>
       </c>
       <c r="J67" t="n">
-        <v>0.003190935560491624</v>
+        <v>1.055938118674048</v>
       </c>
       <c r="K67" t="n">
-        <v>0.006939083919943008</v>
+        <v>1.082396100049207</v>
       </c>
       <c r="L67" t="n">
-        <v>0.005065011316148468</v>
+        <v>1.069167178217443</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01312566775771961</v>
+        <v>0.8011946819012681</v>
       </c>
       <c r="N67" t="n">
-        <v>0.04182562239156653</v>
+        <v>1.125729754800106</v>
       </c>
       <c r="O67" t="n">
-        <v>1.001399919196263</v>
+        <v>2.282554927264765</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0436062257277498</v>
+        <v>1.173654401043793</v>
       </c>
       <c r="Q67" t="n">
-        <v>146.6969846054784</v>
+        <v>115.526274014825</v>
       </c>
       <c r="R67" t="n">
-        <v>228.3616648716478</v>
+        <v>186.2210718571806</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>25</v>
+        <v>398</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>model_21_9_19</t>
+          <t>model_21_8_13</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.9974879357898447</v>
+        <v>0.9998398885653129</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.172397019501408</v>
+        <v>0.6637862584611289</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9613569176706255</v>
+        <v>0.9990900185086943</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9507139332465349</v>
+        <v>0.9986179247604031</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9841450448478457</v>
+        <v>0.9992019515708304</v>
       </c>
       <c r="H68" t="n">
-        <v>0.001752085832634357</v>
+        <v>0.0001116726934064415</v>
       </c>
       <c r="I68" t="n">
-        <v>1.515178642862076</v>
+        <v>0.2344985175561355</v>
       </c>
       <c r="J68" t="n">
-        <v>0.002975270521455425</v>
+        <v>0.0002952084554723299</v>
       </c>
       <c r="K68" t="n">
-        <v>0.00646334937806662</v>
+        <v>0.0002531292133818757</v>
       </c>
       <c r="L68" t="n">
-        <v>0.004719314947026878</v>
+        <v>0.0002741688344271028</v>
       </c>
       <c r="M68" t="n">
-        <v>0.01382572615341992</v>
+        <v>0.003606057257069049</v>
       </c>
       <c r="N68" t="n">
-        <v>0.04185792437083278</v>
+        <v>0.01056753014693791</v>
       </c>
       <c r="O68" t="n">
-        <v>1.001402082349854</v>
+        <v>1.000109790698071</v>
       </c>
       <c r="P68" t="n">
-        <v>0.04363990286914773</v>
+        <v>0.01101741178309616</v>
       </c>
       <c r="Q68" t="n">
-        <v>146.6938965928766</v>
+        <v>136.1998766909195</v>
       </c>
       <c r="R68" t="n">
-        <v>228.3585768590461</v>
+        <v>208.1135503581433</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>33</v>
+        <v>399</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>model_11_9_0</t>
+          <t>model_21_8_15</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.9973270582967538</v>
+        <v>0.9998392341330478</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.142381488394762</v>
+        <v>0.6641344474209454</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9309268344854078</v>
+        <v>0.9989484684619525</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9908741749769084</v>
+        <v>0.998572398629435</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9881931366085069</v>
+        <v>0.9991229837603802</v>
       </c>
       <c r="H69" t="n">
-        <v>0.001864292827700278</v>
+        <v>0.0001121291393426277</v>
       </c>
       <c r="I69" t="n">
-        <v>1.494243753300595</v>
+        <v>0.2342556667002108</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0006918492692641998</v>
+        <v>0.0003411289176684513</v>
       </c>
       <c r="K69" t="n">
-        <v>0.001636373998995547</v>
+        <v>0.0002614673945388057</v>
       </c>
       <c r="L69" t="n">
-        <v>0.001164111634129873</v>
+        <v>0.0003012981561036285</v>
       </c>
       <c r="M69" t="n">
-        <v>0.01271647228386035</v>
+        <v>0.003357003472712287</v>
       </c>
       <c r="N69" t="n">
-        <v>0.04317745740198556</v>
+        <v>0.01058910474698535</v>
       </c>
       <c r="O69" t="n">
-        <v>1.002566024035116</v>
+        <v>1.000110239451624</v>
       </c>
       <c r="P69" t="n">
-        <v>0.04501561115324662</v>
+        <v>0.0110399048585332</v>
       </c>
       <c r="Q69" t="n">
-        <v>110.5697469573027</v>
+        <v>136.1917186421053</v>
       </c>
       <c r="R69" t="n">
-        <v>170.2946623758446</v>
+        <v>208.1053923093292</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 3], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>41</v>
+        <v>400</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>model_23_91_1</t>
+          <t>model_21_8_12</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.9970205168135117</v>
+        <v>0.9998387056214627</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.112963470138399</v>
+        <v>0.6635815203682718</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9918625157952494</v>
+        <v>0.9991670849901146</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9993495520681095</v>
+        <v>0.9986446191597441</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9982302915775975</v>
+        <v>0.9992454486291896</v>
       </c>
       <c r="H70" t="n">
-        <v>0.002078095877690824</v>
+        <v>0.0001124977595621553</v>
       </c>
       <c r="I70" t="n">
-        <v>1.473725610172412</v>
+        <v>0.2346413159410039</v>
       </c>
       <c r="J70" t="n">
-        <v>0.001664917580172036</v>
+        <v>0.0002702072030664978</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0005878843989323697</v>
+        <v>0.0002482400929394463</v>
       </c>
       <c r="L70" t="n">
-        <v>0.001126398350798677</v>
+        <v>0.0002592254583668624</v>
       </c>
       <c r="M70" t="n">
-        <v>0.01610161611232451</v>
+        <v>0.003752057778046954</v>
       </c>
       <c r="N70" t="n">
-        <v>0.04558613690247094</v>
+        <v>0.01060649610201952</v>
       </c>
       <c r="O70" t="n">
-        <v>1.002043074185021</v>
+        <v>1.000110601859568</v>
       </c>
       <c r="P70" t="n">
-        <v>0.04752683312672161</v>
+        <v>0.01105803659955624</v>
       </c>
       <c r="Q70" t="n">
-        <v>130.352606495922</v>
+        <v>136.1851545030423</v>
       </c>
       <c r="R70" t="n">
-        <v>202.2662801631459</v>
+        <v>208.0988281702662</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>42</v>
+        <v>401</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>model_23_91_2</t>
+          <t>model_21_8_16</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.9970121283093222</v>
+        <v>0.9998379180824891</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.10405854177783</v>
+        <v>0.6642822003049231</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9834703961309726</v>
+        <v>0.9988842663762694</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9989589231080829</v>
+        <v>0.9985529957962027</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9966041263833605</v>
+        <v>0.9990874989459877</v>
       </c>
       <c r="H71" t="n">
-        <v>0.002083946595713134</v>
+        <v>0.0001130470432439286</v>
       </c>
       <c r="I71" t="n">
-        <v>1.467514702522002</v>
+        <v>0.234152613707496</v>
       </c>
       <c r="J71" t="n">
-        <v>0.003381933209622365</v>
+        <v>0.0003619568122286402</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0009409405931512224</v>
+        <v>0.000265021053393808</v>
       </c>
       <c r="L71" t="n">
-        <v>0.002161433145077442</v>
+        <v>0.0003134889328112241</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01636823070747412</v>
+        <v>0.003251087154050901</v>
       </c>
       <c r="N71" t="n">
-        <v>0.04565026391723419</v>
+        <v>0.01063235831055033</v>
       </c>
       <c r="O71" t="n">
-        <v>1.002048826302179</v>
+        <v>1.000111141886293</v>
       </c>
       <c r="P71" t="n">
-        <v>0.04759369016126456</v>
+        <v>0.01108499981584635</v>
       </c>
       <c r="Q71" t="n">
-        <v>130.3469835625536</v>
+        <v>136.175413027985</v>
       </c>
       <c r="R71" t="n">
-        <v>202.2606572297774</v>
+        <v>208.0890866952089</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>75</v>
+        <v>402</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>model_27_9_4</t>
+          <t>model_21_8_17</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.9964907224644923</v>
+        <v>0.9998361985165094</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.126743300729478</v>
+        <v>0.6644145587246948</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9889980247576222</v>
+        <v>0.9988244791849437</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9971248783253183</v>
+        <v>0.9985355482141247</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9963178312942832</v>
+        <v>0.999054619799382</v>
       </c>
       <c r="H72" t="n">
-        <v>0.002447610784743799</v>
+        <v>0.0001142463864690235</v>
       </c>
       <c r="I72" t="n">
-        <v>1.483336608910871</v>
+        <v>0.2340602978697184</v>
       </c>
       <c r="J72" t="n">
-        <v>0.001865162061930964</v>
+        <v>0.0003813524643126919</v>
       </c>
       <c r="K72" t="n">
-        <v>0.004303029850810234</v>
+        <v>0.0002682166049819573</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0030840998022116</v>
+        <v>0.0003247845346473246</v>
       </c>
       <c r="M72" t="n">
-        <v>0.03425074810948517</v>
+        <v>0.003155830815393289</v>
       </c>
       <c r="N72" t="n">
-        <v>0.04947333407749875</v>
+        <v>0.01068861012802991</v>
       </c>
       <c r="O72" t="n">
-        <v>1.001203180869317</v>
+        <v>1.000112321017251</v>
       </c>
       <c r="P72" t="n">
-        <v>0.05157951633309781</v>
+        <v>0.01114364638965336</v>
       </c>
       <c r="Q72" t="n">
-        <v>200.025285840266</v>
+        <v>136.1543063139401</v>
       </c>
       <c r="R72" t="n">
-        <v>314.5996133778769</v>
+        <v>208.0679799811639</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Hidden Size=[9, 6], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>model_27_9_5</t>
+          <t>model_9_3_14</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.9964552895895378</v>
+        <v>0.9998134323178985</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.128414067590132</v>
+        <v>0.4302377896119317</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9857659128094902</v>
+        <v>0.9995802058148181</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9962300114135193</v>
+        <v>0.9991552396858996</v>
       </c>
       <c r="G73" t="n">
-        <v>0.995191234366126</v>
+        <v>0.9995906720845834</v>
       </c>
       <c r="H73" t="n">
-        <v>0.002472324101372553</v>
+        <v>0.000130125094460561</v>
       </c>
       <c r="I73" t="n">
-        <v>1.484501916284128</v>
+        <v>0.3973912341713791</v>
       </c>
       <c r="J73" t="n">
-        <v>0.00241310117765895</v>
+        <v>0.0002197337088028713</v>
       </c>
       <c r="K73" t="n">
-        <v>0.005642325877090424</v>
+        <v>0.0003763041166958021</v>
       </c>
       <c r="L73" t="n">
-        <v>0.004027711472667548</v>
+        <v>0.0002980189127493367</v>
       </c>
       <c r="M73" t="n">
-        <v>0.03736941930327024</v>
+        <v>0.004622603213278625</v>
       </c>
       <c r="N73" t="n">
-        <v>0.04972247078909649</v>
+        <v>0.01140723868692862</v>
       </c>
       <c r="O73" t="n">
-        <v>1.001215329283587</v>
+        <v>1.00034443264388</v>
       </c>
       <c r="P73" t="n">
-        <v>0.05183925931029235</v>
+        <v>0.01189286845407058</v>
       </c>
       <c r="Q73" t="n">
-        <v>200.0051932780225</v>
+        <v>91.89402861021541</v>
       </c>
       <c r="R73" t="n">
-        <v>314.5795208156333</v>
+        <v>136.9924341303388</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Hidden Size=[9, 6], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>223</v>
+        <v>423</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>model_17_8_0</t>
+          <t>model_9_3_15</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.9940721652947274</v>
+        <v>0.999809661832631</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.089134410300538</v>
+        <v>0.4303190163193522</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9928685551341716</v>
+        <v>0.9995100051356541</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9580426421692185</v>
+        <v>0.9991081005998786</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9869596401607001</v>
+        <v>0.9995510167000442</v>
       </c>
       <c r="H74" t="n">
-        <v>0.004134478395623615</v>
+        <v>0.000132754889428691</v>
       </c>
       <c r="I74" t="n">
-        <v>1.457105589880681</v>
+        <v>0.3973345810959013</v>
       </c>
       <c r="J74" t="n">
-        <v>0.01172593266106263</v>
+        <v>0.0002564789905092275</v>
       </c>
       <c r="K74" t="n">
-        <v>0.01411455725477146</v>
+        <v>0.0003973025369942908</v>
       </c>
       <c r="L74" t="n">
-        <v>0.01292025544616741</v>
+        <v>0.0003268907637517591</v>
       </c>
       <c r="M74" t="n">
-        <v>0.07287409925704169</v>
+        <v>0.004550843876384613</v>
       </c>
       <c r="N74" t="n">
-        <v>0.0642999097637284</v>
+        <v>0.01152193080298137</v>
       </c>
       <c r="O74" t="n">
-        <v>1.002332262834861</v>
+        <v>1.000351393539758</v>
       </c>
       <c r="P74" t="n">
-        <v>0.06703729004153304</v>
+        <v>0.01201244325094911</v>
       </c>
       <c r="Q74" t="n">
-        <v>180.9767882044121</v>
+        <v>91.85401213333191</v>
       </c>
       <c r="R74" t="n">
-        <v>284.5812333182092</v>
+        <v>136.9524176534553</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>224</v>
+        <v>424</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>model_17_8_1</t>
+          <t>model_9_3_11</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.9940721406161716</v>
+        <v>0.9998094816227628</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.089133929103165</v>
+        <v>0.4298529531088932</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9928685422681883</v>
+        <v>0.9997790550607649</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9580423852254671</v>
+        <v>0.9993134339569143</v>
       </c>
       <c r="G75" t="n">
-        <v>0.986959585864863</v>
+        <v>0.9997105471371779</v>
       </c>
       <c r="H75" t="n">
-        <v>0.004134495608140663</v>
+        <v>0.0001328805801477082</v>
       </c>
       <c r="I75" t="n">
-        <v>1.457105254260638</v>
+        <v>0.3976596455368723</v>
       </c>
       <c r="J75" t="n">
-        <v>0.01172595381605391</v>
+        <v>0.0001156496508361982</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01411464369127453</v>
+        <v>0.0003058354234737572</v>
       </c>
       <c r="L75" t="n">
-        <v>0.01292030924192879</v>
+        <v>0.0002107416186912952</v>
       </c>
       <c r="M75" t="n">
-        <v>0.07287416091545047</v>
+        <v>0.004967281549311515</v>
       </c>
       <c r="N75" t="n">
-        <v>0.06430004360916611</v>
+        <v>0.01152738392471198</v>
       </c>
       <c r="O75" t="n">
-        <v>1.002332272544457</v>
+        <v>1.000351726234899</v>
       </c>
       <c r="P75" t="n">
-        <v>0.06703742958504813</v>
+        <v>0.01201812852336131</v>
       </c>
       <c r="Q75" t="n">
-        <v>180.9767798780988</v>
+        <v>91.85211945343343</v>
       </c>
       <c r="R75" t="n">
-        <v>284.5812249918959</v>
+        <v>136.9505249735569</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>297</v>
+        <v>425</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>model_1_6_4</t>
+          <t>model_9_3_16</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.9928580000259046</v>
+        <v>0.9998044405251622</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.104021232251144</v>
+        <v>0.4303838888760601</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9999999999907133</v>
+        <v>0.9994404095602268</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9966826025411751</v>
+        <v>0.9990636549725834</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9972379853550232</v>
+        <v>0.9995124046475837</v>
       </c>
       <c r="H76" t="n">
-        <v>0.004981320509523863</v>
+        <v>0.000136396587282909</v>
       </c>
       <c r="I76" t="n">
-        <v>1.467488680299773</v>
+        <v>0.3972893345265361</v>
       </c>
       <c r="J76" t="n">
-        <v>2.849903853388917e-12</v>
+        <v>0.0002929075415580569</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00513009699899882</v>
+        <v>0.0004171011381372948</v>
       </c>
       <c r="L76" t="n">
-        <v>0.002565048500966058</v>
+        <v>0.0003550029971468072</v>
       </c>
       <c r="M76" t="n">
-        <v>0.01628568009081332</v>
+        <v>0.004487018970611979</v>
       </c>
       <c r="N76" t="n">
-        <v>0.070578470580793</v>
+        <v>0.01167889495127467</v>
       </c>
       <c r="O76" t="n">
-        <v>1.00504141174642</v>
+        <v>1.000361032876624</v>
       </c>
       <c r="P76" t="n">
-        <v>0.07358314219099271</v>
+        <v>0.01217608968799583</v>
       </c>
       <c r="Q76" t="n">
-        <v>126.6041205210799</v>
+        <v>91.79988766557588</v>
       </c>
       <c r="R76" t="n">
-        <v>197.2989183634355</v>
+        <v>136.8982931856993</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>299</v>
+        <v>426</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>model_1_8_14</t>
+          <t>model_9_3_10</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.9928580000259046</v>
+        <v>0.999799585827322</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.104021232251144</v>
+        <v>0.4296439191815783</v>
       </c>
       <c r="E77" t="n">
-        <v>0.995958576007826</v>
+        <v>0.9998320119833325</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9739169950842363</v>
+        <v>0.9993699555391964</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9933860309331687</v>
+        <v>0.9997468735486883</v>
       </c>
       <c r="H77" t="n">
-        <v>0.004981320509523863</v>
+        <v>0.0001397825864437454</v>
       </c>
       <c r="I77" t="n">
-        <v>1.467488680299773</v>
+        <v>0.3978054401312572</v>
       </c>
       <c r="J77" t="n">
-        <v>0.006795797331205126</v>
+        <v>8.79303030860066e-05</v>
       </c>
       <c r="K77" t="n">
-        <v>0.005957153530556655</v>
+        <v>0.0002806575076319213</v>
       </c>
       <c r="L77" t="n">
-        <v>0.00637647543088089</v>
+        <v>0.0001842934893195095</v>
       </c>
       <c r="M77" t="n">
-        <v>0.01628568009081332</v>
+        <v>0.005152695071399611</v>
       </c>
       <c r="N77" t="n">
-        <v>0.070578470580793</v>
+        <v>0.01182296859691953</v>
       </c>
       <c r="O77" t="n">
-        <v>1.00504141174642</v>
+        <v>1.000369995395713</v>
       </c>
       <c r="P77" t="n">
-        <v>0.07358314219099271</v>
+        <v>0.01232629684700936</v>
       </c>
       <c r="Q77" t="n">
-        <v>126.6041205210799</v>
+        <v>91.75084459282219</v>
       </c>
       <c r="R77" t="n">
-        <v>197.2989183634355</v>
+        <v>136.8492501129456</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>300</v>
+        <v>505</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>model_1_8_15</t>
+          <t>model_27_9_5</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.9928580000259046</v>
+        <v>0.9997411850485044</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.104021232251144</v>
+        <v>0.6219949369035224</v>
       </c>
       <c r="E78" t="n">
-        <v>0.995958576007826</v>
+        <v>0.9992653203410173</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9739169950842363</v>
+        <v>0.9995986051247342</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9933860309331687</v>
+        <v>0.9994485888870477</v>
       </c>
       <c r="H78" t="n">
-        <v>0.004981320509523863</v>
+        <v>0.0001805152941378563</v>
       </c>
       <c r="I78" t="n">
-        <v>1.467488680299773</v>
+        <v>0.2636466508451418</v>
       </c>
       <c r="J78" t="n">
-        <v>0.006795797331205126</v>
+        <v>0.0006857312812995867</v>
       </c>
       <c r="K78" t="n">
-        <v>0.005957153530556655</v>
+        <v>0.0003572465882807641</v>
       </c>
       <c r="L78" t="n">
-        <v>0.00637647543088089</v>
+        <v>0.0005214889347901754</v>
       </c>
       <c r="M78" t="n">
-        <v>0.01628568009081332</v>
+        <v>0.006641632352243322</v>
       </c>
       <c r="N78" t="n">
-        <v>0.070578470580793</v>
+        <v>0.01343559801936097</v>
       </c>
       <c r="O78" t="n">
-        <v>1.00504141174642</v>
+        <v>1.000182692906938</v>
       </c>
       <c r="P78" t="n">
-        <v>0.07358314219099271</v>
+        <v>0.01400757924256723</v>
       </c>
       <c r="Q78" t="n">
-        <v>126.6041205210799</v>
+        <v>133.2393901034304</v>
       </c>
       <c r="R78" t="n">
-        <v>197.2989183634355</v>
+        <v>203.9341879457861</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>301</v>
+        <v>506</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>model_1_8_17</t>
+          <t>model_27_9_6</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.9928580000259046</v>
+        <v>0.9997409171345143</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.104021232251144</v>
+        <v>0.6221606675075196</v>
       </c>
       <c r="E79" t="n">
-        <v>0.995958576007826</v>
+        <v>0.9992240690341431</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9739169950842363</v>
+        <v>0.9996223655053467</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9933860309331687</v>
+        <v>0.9994394125265013</v>
       </c>
       <c r="H79" t="n">
-        <v>0.004981320509523863</v>
+        <v>0.0001807021557254221</v>
       </c>
       <c r="I79" t="n">
-        <v>1.467488680299773</v>
+        <v>0.2635310589577515</v>
       </c>
       <c r="J79" t="n">
-        <v>0.006795797331205126</v>
+        <v>0.0007242342004593935</v>
       </c>
       <c r="K79" t="n">
-        <v>0.005957153530556655</v>
+        <v>0.0003360995447256816</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00637647543088089</v>
+        <v>0.0005301673425592381</v>
       </c>
       <c r="M79" t="n">
-        <v>0.01628568009081332</v>
+        <v>0.006522059901552027</v>
       </c>
       <c r="N79" t="n">
-        <v>0.070578470580793</v>
+        <v>0.01344255019426828</v>
       </c>
       <c r="O79" t="n">
-        <v>1.00504141174642</v>
+        <v>1.000182882022696</v>
       </c>
       <c r="P79" t="n">
-        <v>0.07358314219099271</v>
+        <v>0.01401482738595333</v>
       </c>
       <c r="Q79" t="n">
-        <v>126.6041205210799</v>
+        <v>133.2373208611576</v>
       </c>
       <c r="R79" t="n">
-        <v>197.2989183634355</v>
+        <v>203.9321187035132</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1054</v>
+        <v>507</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>model_15_7_4</t>
+          <t>model_27_9_4</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.9688283122720798</v>
+        <v>0.9997402224432987</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.068613624161532</v>
+        <v>0.6218081742063298</v>
       </c>
       <c r="E80" t="n">
-        <v>0.890525414825174</v>
+        <v>0.9993078854902009</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9490923661428921</v>
+        <v>0.9995716908384122</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9700295179938513</v>
+        <v>0.9994569290538777</v>
       </c>
       <c r="H80" t="n">
-        <v>0.02174127246692258</v>
+        <v>0.0001811866810142119</v>
       </c>
       <c r="I80" t="n">
-        <v>1.442792986515161</v>
+        <v>0.263776911956499</v>
       </c>
       <c r="J80" t="n">
-        <v>0.004071810391023722</v>
+        <v>0.0006460020551920201</v>
       </c>
       <c r="K80" t="n">
-        <v>0.03700751941246753</v>
+        <v>0.0003812006483772317</v>
       </c>
       <c r="L80" t="n">
-        <v>0.02053968537417149</v>
+        <v>0.000513601344906631</v>
       </c>
       <c r="M80" t="n">
-        <v>0.0363175924586614</v>
+        <v>0.006781215061954402</v>
       </c>
       <c r="N80" t="n">
-        <v>0.1474492199603734</v>
+        <v>0.01346056020432329</v>
       </c>
       <c r="O80" t="n">
-        <v>1.018246841596831</v>
+        <v>1.000183372392966</v>
       </c>
       <c r="P80" t="n">
-        <v>0.15372643851605</v>
+        <v>0.01403360411942225</v>
       </c>
       <c r="Q80" t="n">
-        <v>137.6570857357295</v>
+        <v>133.2319653427871</v>
       </c>
       <c r="R80" t="n">
-        <v>216.8840143521626</v>
+        <v>203.9267631851427</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Hidden Size=[8, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1110</v>
+        <v>508</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>model_15_7_3</t>
+          <t>model_27_9_7</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.9657195635700334</v>
+        <v>0.9997397410301249</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.083626380106328</v>
+        <v>0.6223076943399952</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9138715756257425</v>
+        <v>0.9991845387547407</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9599471659908522</v>
+        <v>0.9996433391936241</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9764201013395667</v>
+        <v>0.9994297751760323</v>
       </c>
       <c r="H81" t="n">
-        <v>0.02390952697891182</v>
+        <v>0.000181522451572265</v>
       </c>
       <c r="I81" t="n">
-        <v>1.453263911937107</v>
+        <v>0.2634285123631397</v>
       </c>
       <c r="J81" t="n">
-        <v>0.003203470584241562</v>
+        <v>0.0007611307564117458</v>
       </c>
       <c r="K81" t="n">
-        <v>0.02911657682379042</v>
+        <v>0.0003174326930977737</v>
       </c>
       <c r="L81" t="n">
-        <v>0.01616002370401599</v>
+        <v>0.0005392817247547597</v>
       </c>
       <c r="M81" t="n">
-        <v>0.03779077774456588</v>
+        <v>0.006411802296011761</v>
       </c>
       <c r="N81" t="n">
-        <v>0.1546270577192485</v>
+        <v>0.01347302681554019</v>
       </c>
       <c r="O81" t="n">
-        <v>1.020066596934615</v>
+        <v>1.00018371221403</v>
       </c>
       <c r="P81" t="n">
-        <v>0.1612098516884929</v>
+        <v>0.01404660146008809</v>
       </c>
       <c r="Q81" t="n">
-        <v>137.4669565622147</v>
+        <v>133.2282624235739</v>
       </c>
       <c r="R81" t="n">
-        <v>216.6938851786477</v>
+        <v>203.9230602659295</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Hidden Size=[8, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>model_25_91_17</t>
+          <t>model_12_3_24</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.9993976585816139</v>
+        <v>0.9999999996019001</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.27169295297483</v>
+        <v>0.6454956274887458</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9815732251767233</v>
+        <v>0.9999999981292351</v>
       </c>
       <c r="F82" t="n">
-        <v>0.997646971733492</v>
+        <v>0.9999999999998979</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9922275315235652</v>
+        <v>0.9999999991112503</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0004201142077884647</v>
+        <v>2.776621751554447e-10</v>
       </c>
       <c r="I82" t="n">
-        <v>1.584434435597657</v>
+        <v>0.2472556577865098</v>
       </c>
       <c r="J82" t="n">
-        <v>0.002116694554375266</v>
+        <v>1.017791267645133e-09</v>
       </c>
       <c r="K82" t="n">
-        <v>0.0003754802493763916</v>
+        <v>5.994109880543635e-14</v>
       </c>
       <c r="L82" t="n">
-        <v>0.001246085515169791</v>
+        <v>5.08926079976734e-10</v>
       </c>
       <c r="M82" t="n">
-        <v>0.01191953538024707</v>
+        <v>4.293428399004596e-06</v>
       </c>
       <c r="N82" t="n">
-        <v>0.02049668772725156</v>
+        <v>1.666319822709448e-05</v>
       </c>
       <c r="O82" t="n">
-        <v>1.00012680871966</v>
+        <v>1.00000000021232</v>
       </c>
       <c r="P82" t="n">
-        <v>0.02136927415779347</v>
+        <v>1.737258507319747e-05</v>
       </c>
       <c r="Q82" t="n">
-        <v>291.5499679206908</v>
+        <v>182.0092318769428</v>
       </c>
       <c r="R82" t="n">
-        <v>459.7548317525025</v>
+        <v>266.1116637928487</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Hidden Size=[9, 10], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>model_25_91_16</t>
+          <t>model_12_3_11</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.9993972878501589</v>
+        <v>0.9999999996019001</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.271024675614923</v>
+        <v>0.6454956274887458</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9817107171558271</v>
+        <v>0.9999999981292351</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9977341982724243</v>
+        <v>0.9999999999998979</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9923202005083785</v>
+        <v>0.9999999991112503</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0004203727813262448</v>
+        <v>2.776621751554447e-10</v>
       </c>
       <c r="I83" t="n">
-        <v>1.583968333143018</v>
+        <v>0.2472556577865098</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002100900769177884</v>
+        <v>1.017791267645133e-09</v>
       </c>
       <c r="K83" t="n">
-        <v>0.000361561231463734</v>
+        <v>5.994109880543635e-14</v>
       </c>
       <c r="L83" t="n">
-        <v>0.001231228783356543</v>
+        <v>5.08926079976734e-10</v>
       </c>
       <c r="M83" t="n">
-        <v>0.01260430876351792</v>
+        <v>4.293428399004596e-06</v>
       </c>
       <c r="N83" t="n">
-        <v>0.02050299444779335</v>
+        <v>1.666319822709448e-05</v>
       </c>
       <c r="O83" t="n">
-        <v>1.000126886768388</v>
+        <v>1.00000000021232</v>
       </c>
       <c r="P83" t="n">
-        <v>0.02137584936848544</v>
+        <v>1.737258507319747e-05</v>
       </c>
       <c r="Q83" t="n">
-        <v>291.5487373315239</v>
+        <v>182.0092318769428</v>
       </c>
       <c r="R83" t="n">
-        <v>459.7536011633356</v>
+        <v>266.1116637928487</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Hidden Size=[9, 10], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>model_25_91_18</t>
+          <t>model_12_3_1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.9993972239946503</v>
+        <v>0.9999999996019001</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.272294968383647</v>
+        <v>0.6454956274887458</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9814471923900744</v>
+        <v>0.9999999981292351</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9975668255770097</v>
+        <v>0.9999999999998979</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9921424778455643</v>
+        <v>0.9999999991112503</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0004204173185365637</v>
+        <v>2.776621751554447e-10</v>
       </c>
       <c r="I84" t="n">
-        <v>1.584854322424017</v>
+        <v>0.2472556577865098</v>
       </c>
       <c r="J84" t="n">
-        <v>0.002131172015337963</v>
+        <v>1.017791267645133e-09</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0003882694280067106</v>
+        <v>5.994109880543635e-14</v>
       </c>
       <c r="L84" t="n">
-        <v>0.001259721357693987</v>
+        <v>5.08926079976734e-10</v>
       </c>
       <c r="M84" t="n">
-        <v>0.01130308107047358</v>
+        <v>4.293428399004596e-06</v>
       </c>
       <c r="N84" t="n">
-        <v>0.02050408053380019</v>
+        <v>1.666319822709448e-05</v>
       </c>
       <c r="O84" t="n">
-        <v>1.000126900211653</v>
+        <v>1.00000000021232</v>
       </c>
       <c r="P84" t="n">
-        <v>0.02137698169142209</v>
+        <v>1.737258507319747e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>291.5485254488656</v>
+        <v>182.0092318769428</v>
       </c>
       <c r="R84" t="n">
-        <v>459.7533892806773</v>
+        <v>266.1116637928487</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Hidden Size=[9, 10], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>model_25_91_19</t>
+          <t>model_12_3_2</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.9993962264580788</v>
+        <v>0.9999999996019001</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.27283704599983</v>
+        <v>0.6454956274887458</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9813321917988621</v>
+        <v>0.9999999981292351</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9974935286532162</v>
+        <v>0.9999999999998979</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9920647855353726</v>
+        <v>0.9999999991112503</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0004211130689426811</v>
+        <v>2.776621751554447e-10</v>
       </c>
       <c r="I85" t="n">
-        <v>1.585232404523855</v>
+        <v>0.2472556577865098</v>
       </c>
       <c r="J85" t="n">
-        <v>0.002144382201466764</v>
+        <v>1.017791267645133e-09</v>
       </c>
       <c r="K85" t="n">
-        <v>0.0003999656526616564</v>
+        <v>5.994109880543635e-14</v>
       </c>
       <c r="L85" t="n">
-        <v>0.001272177022540159</v>
+        <v>5.08926079976734e-10</v>
       </c>
       <c r="M85" t="n">
-        <v>0.01074839815013933</v>
+        <v>4.293428399004596e-06</v>
       </c>
       <c r="N85" t="n">
-        <v>0.02052103966524799</v>
+        <v>1.666319822709448e-05</v>
       </c>
       <c r="O85" t="n">
-        <v>1.000127110219352</v>
+        <v>1.00000000021232</v>
       </c>
       <c r="P85" t="n">
-        <v>0.02139466280820587</v>
+        <v>1.737258507319747e-05</v>
       </c>
       <c r="Q85" t="n">
-        <v>291.5452183760611</v>
+        <v>182.0092318769428</v>
       </c>
       <c r="R85" t="n">
-        <v>459.7500822078728</v>
+        <v>266.1116637928487</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Hidden Size=[9, 10], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>model_25_91_15</t>
+          <t>model_12_3_3</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.9993958479702487</v>
+        <v>0.9999999996019001</v>
       </c>
       <c r="D86" t="n">
-        <v>-1.270282239369369</v>
+        <v>0.6454956274887458</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9818607689954453</v>
+        <v>0.9999999981292351</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9978291758900757</v>
+        <v>0.9999999999998979</v>
       </c>
       <c r="G86" t="n">
-        <v>0.992421217451505</v>
+        <v>0.9999999991112503</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0004213770523083729</v>
+        <v>2.776621751554447e-10</v>
       </c>
       <c r="I86" t="n">
-        <v>1.583450507196448</v>
+        <v>0.2472556577865098</v>
       </c>
       <c r="J86" t="n">
-        <v>0.002083664225352944</v>
+        <v>1.017791267645133e-09</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0003464053491190385</v>
+        <v>5.994109880543635e-14</v>
       </c>
       <c r="L86" t="n">
-        <v>0.001215033703248043</v>
+        <v>5.08926079976734e-10</v>
       </c>
       <c r="M86" t="n">
-        <v>0.013365246888658</v>
+        <v>4.293428399004596e-06</v>
       </c>
       <c r="N86" t="n">
-        <v>0.02052747067488766</v>
+        <v>1.666319822709448e-05</v>
       </c>
       <c r="O86" t="n">
-        <v>1.000127189901</v>
+        <v>1.00000000021232</v>
       </c>
       <c r="P86" t="n">
-        <v>0.02140136759923993</v>
+        <v>1.737258507319747e-05</v>
       </c>
       <c r="Q86" t="n">
-        <v>291.543965027837</v>
+        <v>182.0092318769428</v>
       </c>
       <c r="R86" t="n">
-        <v>459.7488288596487</v>
+        <v>266.1116637928487</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Hidden Size=[9, 10], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>23</v>
+        <v>229</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>model_13_9_2</t>
+          <t>model_7_7_6</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.998790171615378</v>
+        <v>0.9999999993247947</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.160046018017896</v>
+        <v>0.6648820990179763</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9999252256264806</v>
+        <v>0.9999999990045999</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9847454037603179</v>
+        <v>0.9999999982719161</v>
       </c>
       <c r="G87" t="n">
-        <v>0.9984171961017584</v>
+        <v>0.9999999987079971</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0008438172734780755</v>
+        <v>4.709345124382253e-10</v>
       </c>
       <c r="I87" t="n">
-        <v>1.506564207518176</v>
+        <v>0.2337342032099032</v>
       </c>
       <c r="J87" t="n">
-        <v>3.066519896102934e-05</v>
+        <v>5.682629716495394e-10</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0007967808850970781</v>
+        <v>6.761849205696576e-10</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0004137200753140844</v>
+        <v>6.226291189178326e-10</v>
       </c>
       <c r="M87" t="n">
-        <v>0.01934617789723483</v>
+        <v>6.032537760572896e-06</v>
       </c>
       <c r="N87" t="n">
-        <v>0.02904853306929759</v>
+        <v>2.17010256079805e-05</v>
       </c>
       <c r="O87" t="n">
-        <v>1.000287483972583</v>
+        <v>1.000000000395242</v>
       </c>
       <c r="P87" t="n">
-        <v>0.03028518926081073</v>
+        <v>2.262488319542814e-05</v>
       </c>
       <c r="Q87" t="n">
-        <v>264.1551491748527</v>
+        <v>172.9526041419766</v>
       </c>
       <c r="R87" t="n">
-        <v>416.5146272833778</v>
+        <v>252.1795327584096</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Hidden Size=[8, 10], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[16], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>model_13_9_1</t>
+          <t>model_7_7_5</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.998722222809442</v>
+        <v>0.9999999992733436</v>
       </c>
       <c r="D88" t="n">
-        <v>-1.163621594186058</v>
+        <v>0.6648944639332407</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9999756203852246</v>
+        <v>0.9999999991960528</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9984337114603199</v>
+        <v>0.999999998454481</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9998243805511782</v>
+        <v>0.9999999988963567</v>
       </c>
       <c r="H88" t="n">
-        <v>0.000891209429993671</v>
+        <v>5.068200144513984e-10</v>
       </c>
       <c r="I88" t="n">
-        <v>1.509058059515436</v>
+        <v>0.2337255790701345</v>
       </c>
       <c r="J88" t="n">
-        <v>9.998154481177645e-06</v>
+        <v>4.589646316336132e-10</v>
       </c>
       <c r="K88" t="n">
-        <v>8.181067196765699e-05</v>
+        <v>6.047488047201463e-10</v>
       </c>
       <c r="L88" t="n">
-        <v>4.590416518048936e-05</v>
+        <v>5.318567181768798e-10</v>
       </c>
       <c r="M88" t="n">
-        <v>0.02024735244833832</v>
+        <v>6.233719184441904e-06</v>
       </c>
       <c r="N88" t="n">
-        <v>0.02985313099146672</v>
+        <v>2.251266342420191e-05</v>
       </c>
       <c r="O88" t="n">
-        <v>1.000303630223499</v>
+        <v>1.00000000042536</v>
       </c>
       <c r="P88" t="n">
-        <v>0.03112404058227392</v>
+        <v>2.3471074113808e-05</v>
       </c>
       <c r="Q88" t="n">
-        <v>264.0458622152311</v>
+        <v>172.8057303528944</v>
       </c>
       <c r="R88" t="n">
-        <v>416.4053403237562</v>
+        <v>252.0326589693275</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Hidden Size=[8, 10], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[16], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>model_17_9_9</t>
+          <t>model_7_7_4</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.9983415329337868</v>
+        <v>0.9999999992355183</v>
       </c>
       <c r="D89" t="n">
-        <v>-1.295731807796933</v>
+        <v>0.6649073081394713</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9937449232870675</v>
+        <v>0.9999999994502354</v>
       </c>
       <c r="F89" t="n">
-        <v>0.978477187876806</v>
+        <v>0.9999999987556912</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9867728037714634</v>
+        <v>0.9999999991691993</v>
       </c>
       <c r="H89" t="n">
-        <v>0.001156728653215137</v>
+        <v>5.332019723327619e-10</v>
       </c>
       <c r="I89" t="n">
-        <v>1.601200781297059</v>
+        <v>0.2337166206399809</v>
       </c>
       <c r="J89" t="n">
-        <v>0.00138737812741892</v>
+        <v>3.138545177715458e-10</v>
       </c>
       <c r="K89" t="n">
-        <v>0.004398550779569585</v>
+        <v>4.868877147661604e-10</v>
       </c>
       <c r="L89" t="n">
-        <v>0.00289296448849592</v>
+        <v>4.003711162688531e-10</v>
       </c>
       <c r="M89" t="n">
-        <v>0.01092026135158896</v>
+        <v>6.312434753116786e-06</v>
       </c>
       <c r="N89" t="n">
-        <v>0.03401071380043554</v>
+        <v>2.309116654335077e-05</v>
       </c>
       <c r="O89" t="n">
-        <v>1.000437397907573</v>
+        <v>1.000000000447502</v>
       </c>
       <c r="P89" t="n">
-        <v>0.03545862029880342</v>
+        <v>2.407420530840557e-05</v>
       </c>
       <c r="Q89" t="n">
-        <v>243.524318768903</v>
+        <v>172.7042416571643</v>
       </c>
       <c r="R89" t="n">
-        <v>383.6950386287461</v>
+        <v>251.9311702735973</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Hidden Size=[10, 7], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[16], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>96</v>
+        <v>232</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>model_17_9_10</t>
+          <t>model_7_7_3</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.9983391104027814</v>
+        <v>0.9999999989493326</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.293505926090197</v>
+        <v>0.6648995475750088</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9932360292865134</v>
+        <v>0.9999999992658696</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9776370725400386</v>
+        <v>0.999999999259471</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9861222616321549</v>
+        <v>0.9999999992657446</v>
       </c>
       <c r="H90" t="n">
-        <v>0.001158418292451398</v>
+        <v>7.328075302124826e-10</v>
       </c>
       <c r="I90" t="n">
-        <v>1.59964829876587</v>
+        <v>0.2337220333897797</v>
       </c>
       <c r="J90" t="n">
-        <v>0.001500250988607615</v>
+        <v>4.191070052153439e-10</v>
       </c>
       <c r="K90" t="n">
-        <v>0.004570242561680368</v>
+        <v>2.897628425429315e-10</v>
       </c>
       <c r="L90" t="n">
-        <v>0.003035246743538719</v>
+        <v>3.53845009959606e-10</v>
       </c>
       <c r="M90" t="n">
-        <v>0.01065794170421387</v>
+        <v>7.788755377889258e-06</v>
       </c>
       <c r="N90" t="n">
-        <v>0.03403554454465798</v>
+        <v>2.707041799109284e-05</v>
       </c>
       <c r="O90" t="n">
-        <v>1.000438036816849</v>
+        <v>1.000000000615025</v>
       </c>
       <c r="P90" t="n">
-        <v>0.03548450813921413</v>
+        <v>2.822286172846409e-05</v>
       </c>
       <c r="Q90" t="n">
-        <v>243.5213994906439</v>
+        <v>172.0682760533529</v>
       </c>
       <c r="R90" t="n">
-        <v>383.692119350487</v>
+        <v>251.2952046697859</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Hidden Size=[10, 7], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[16], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>152</v>
+        <v>234</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>model_21_7_12</t>
+          <t>model_7_7_2</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.9980940470507259</v>
+        <v>0.9999999987866073</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.154307115795969</v>
+        <v>0.6649132578559733</v>
       </c>
       <c r="E91" t="n">
-        <v>0.994530436769096</v>
+        <v>0.9999999994776528</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9495178908830361</v>
+        <v>0.999999999246484</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9822813139015869</v>
+        <v>0.9999999993846913</v>
       </c>
       <c r="H91" t="n">
-        <v>0.001329342278191353</v>
+        <v>8.463033004999989e-10</v>
       </c>
       <c r="I91" t="n">
-        <v>1.502561503591556</v>
+        <v>0.2337124708997197</v>
       </c>
       <c r="J91" t="n">
-        <v>0.001291792341715817</v>
+        <v>2.982022362809777e-10</v>
       </c>
       <c r="K91" t="n">
-        <v>0.004669364684438787</v>
+        <v>2.948445678491528e-10</v>
       </c>
       <c r="L91" t="n">
-        <v>0.002980577580904087</v>
+        <v>2.965234020650653e-10</v>
       </c>
       <c r="M91" t="n">
-        <v>0.01480255291032351</v>
+        <v>8.146597837000965e-06</v>
       </c>
       <c r="N91" t="n">
-        <v>0.03646014643677879</v>
+        <v>2.90912925202714e-05</v>
       </c>
       <c r="O91" t="n">
-        <v>1.000397764093762</v>
+        <v>1.000000000710279</v>
       </c>
       <c r="P91" t="n">
-        <v>0.03801233035350036</v>
+        <v>3.032976907013677e-05</v>
       </c>
       <c r="Q91" t="n">
-        <v>291.2461419734866</v>
+        <v>171.7802866186856</v>
       </c>
       <c r="R91" t="n">
-        <v>460.6698816301665</v>
+        <v>251.0072152351187</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 15], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[16], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>163</v>
+        <v>317</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>model_21_7_13</t>
+          <t>model_22_7_15</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.9980594558707542</v>
+        <v>0.9999999919840447</v>
       </c>
       <c r="D92" t="n">
-        <v>-1.154459619832083</v>
+        <v>0.6883950691503815</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9941506416244468</v>
+        <v>0.9999999290416339</v>
       </c>
       <c r="F92" t="n">
-        <v>0.944039951856071</v>
+        <v>0.9999999765380368</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9805086283360054</v>
+        <v>0.9999999726616423</v>
       </c>
       <c r="H92" t="n">
-        <v>0.001353468539023999</v>
+        <v>5.590876877308144e-09</v>
       </c>
       <c r="I92" t="n">
-        <v>1.502667870363557</v>
+        <v>0.217334645553057</v>
       </c>
       <c r="J92" t="n">
-        <v>0.00138149172694402</v>
+        <v>8.507294233862944e-09</v>
       </c>
       <c r="K92" t="n">
-        <v>0.005176049042193243</v>
+        <v>1.611306566309559e-08</v>
       </c>
       <c r="L92" t="n">
-        <v>0.003278772764532168</v>
+        <v>1.231017994847927e-08</v>
       </c>
       <c r="M92" t="n">
-        <v>0.01445988313517689</v>
+        <v>2.046853175736909e-05</v>
       </c>
       <c r="N92" t="n">
-        <v>0.03678951670006007</v>
+        <v>7.477216646124508e-05</v>
       </c>
       <c r="O92" t="n">
-        <v>1.000404983122625</v>
+        <v>1.000000003375139</v>
       </c>
       <c r="P92" t="n">
-        <v>0.03835572259077996</v>
+        <v>7.795537238722289e-05</v>
       </c>
       <c r="Q92" t="n">
-        <v>291.2101693866882</v>
+        <v>200.0042593934624</v>
       </c>
       <c r="R92" t="n">
-        <v>460.633909043368</v>
+        <v>298.7332012077866</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 15], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>165</v>
+        <v>318</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>model_21_7_9</t>
+          <t>model_22_7_23</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.9980521087674107</v>
+        <v>0.9999999919840447</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.153835837003836</v>
+        <v>0.6883950691503815</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9958347851353947</v>
+        <v>0.9999999290416339</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9665507924033494</v>
+        <v>0.9999999765380368</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9878798122247531</v>
+        <v>0.9999999726616423</v>
       </c>
       <c r="H93" t="n">
-        <v>0.001358592912687273</v>
+        <v>5.590876877308144e-09</v>
       </c>
       <c r="I93" t="n">
-        <v>1.502232801446293</v>
+        <v>0.217334645553057</v>
       </c>
       <c r="J93" t="n">
-        <v>0.0009837335151912682</v>
+        <v>8.507294233862944e-09</v>
       </c>
       <c r="K93" t="n">
-        <v>0.003093899034851874</v>
+        <v>1.611306566309559e-08</v>
       </c>
       <c r="L93" t="n">
-        <v>0.002038817086018828</v>
+        <v>1.231017994847927e-08</v>
       </c>
       <c r="M93" t="n">
-        <v>0.01607222944751914</v>
+        <v>2.046853175736909e-05</v>
       </c>
       <c r="N93" t="n">
-        <v>0.0368590953861767</v>
+        <v>7.477216646124508e-05</v>
       </c>
       <c r="O93" t="n">
-        <v>1.000406516431149</v>
+        <v>1.000000003375139</v>
       </c>
       <c r="P93" t="n">
-        <v>0.03842826338561232</v>
+        <v>7.795537238722289e-05</v>
       </c>
       <c r="Q93" t="n">
-        <v>291.2026114757002</v>
+        <v>200.0042593934624</v>
       </c>
       <c r="R93" t="n">
-        <v>460.62635113238</v>
+        <v>298.7332012077866</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 15], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>480</v>
+        <v>319</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>model_11_7_2</t>
+          <t>model_22_7_12</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.9938537251406427</v>
+        <v>0.9999999919840447</v>
       </c>
       <c r="D94" t="n">
-        <v>-1.086196038813809</v>
+        <v>0.6883950691503815</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9421886109900087</v>
+        <v>0.9999999290416339</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9678106510014334</v>
+        <v>0.9999999765380368</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9759173939663308</v>
+        <v>0.9999999726616423</v>
       </c>
       <c r="H94" t="n">
-        <v>0.004286833537543533</v>
+        <v>5.590876877308144e-09</v>
       </c>
       <c r="I94" t="n">
-        <v>1.455056168121436</v>
+        <v>0.217334645553057</v>
       </c>
       <c r="J94" t="n">
-        <v>0.005367384854767211</v>
+        <v>8.507294233862944e-09</v>
       </c>
       <c r="K94" t="n">
-        <v>0.02142534336625496</v>
+        <v>1.611306566309559e-08</v>
       </c>
       <c r="L94" t="n">
-        <v>0.01339636411051109</v>
+        <v>1.231017994847927e-08</v>
       </c>
       <c r="M94" t="n">
-        <v>0.08510587984365077</v>
+        <v>2.046853175736909e-05</v>
       </c>
       <c r="N94" t="n">
-        <v>0.06547391493979517</v>
+        <v>7.477216646124508e-05</v>
       </c>
       <c r="O94" t="n">
-        <v>1.001676256779825</v>
+        <v>1.000000003375139</v>
       </c>
       <c r="P94" t="n">
-        <v>0.06826127504847071</v>
+        <v>7.795537238722289e-05</v>
       </c>
       <c r="Q94" t="n">
-        <v>234.9044138434223</v>
+        <v>200.0042593934624</v>
       </c>
       <c r="R94" t="n">
-        <v>371.4185062286608</v>
+        <v>298.7332012077866</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 10], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>model_11_7_3</t>
+          <t>model_22_7_10</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.9938537047047659</v>
+        <v>0.9999999919840447</v>
       </c>
       <c r="D95" t="n">
-        <v>-1.086196090791455</v>
+        <v>0.6883950691503815</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9421885086126595</v>
+        <v>0.9999999290416339</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9678105239253015</v>
+        <v>0.9999999765380368</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9759173338041669</v>
+        <v>0.9999999726616423</v>
       </c>
       <c r="H95" t="n">
-        <v>0.004286847790925358</v>
+        <v>5.590876877308144e-09</v>
       </c>
       <c r="I95" t="n">
-        <v>1.45505620437421</v>
+        <v>0.217334645553057</v>
       </c>
       <c r="J95" t="n">
-        <v>0.005367394359791104</v>
+        <v>8.507294233862944e-09</v>
       </c>
       <c r="K95" t="n">
-        <v>0.02142542794857316</v>
+        <v>1.611306566309559e-08</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0133963975767503</v>
+        <v>1.231017994847927e-08</v>
       </c>
       <c r="M95" t="n">
-        <v>0.08510601790571001</v>
+        <v>2.046853175736909e-05</v>
       </c>
       <c r="N95" t="n">
-        <v>0.06547402378749421</v>
+        <v>7.477216646124508e-05</v>
       </c>
       <c r="O95" t="n">
-        <v>1.001676262353246</v>
+        <v>1.000000003375139</v>
       </c>
       <c r="P95" t="n">
-        <v>0.06826138853004164</v>
+        <v>7.795537238722289e-05</v>
       </c>
       <c r="Q95" t="n">
-        <v>234.9044071935918</v>
+        <v>200.0042593934624</v>
       </c>
       <c r="R95" t="n">
-        <v>371.4184995788303</v>
+        <v>298.7332012077866</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 10], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>482</v>
+        <v>321</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>model_11_7_4</t>
+          <t>model_22_7_9</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.9938536914606365</v>
+        <v>0.9999999919840447</v>
       </c>
       <c r="D96" t="n">
-        <v>-1.086196107166172</v>
+        <v>0.6883950691503815</v>
       </c>
       <c r="E96" t="n">
-        <v>0.942188424788605</v>
+        <v>0.9999999290416339</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9678105172341445</v>
+        <v>0.9999999765380368</v>
       </c>
       <c r="G96" t="n">
-        <v>0.9759172925908001</v>
+        <v>0.9999999726616423</v>
       </c>
       <c r="H96" t="n">
-        <v>0.004286857028289308</v>
+        <v>5.590876877308144e-09</v>
       </c>
       <c r="I96" t="n">
-        <v>1.455056215795061</v>
+        <v>0.217334645553057</v>
       </c>
       <c r="J96" t="n">
-        <v>0.005367402142270783</v>
+        <v>8.507294233862944e-09</v>
       </c>
       <c r="K96" t="n">
-        <v>0.02142543240223074</v>
+        <v>1.611306566309559e-08</v>
       </c>
       <c r="L96" t="n">
-        <v>0.01339642050239496</v>
+        <v>1.231017994847927e-08</v>
       </c>
       <c r="M96" t="n">
-        <v>0.08510608257778976</v>
+        <v>2.046853175736909e-05</v>
       </c>
       <c r="N96" t="n">
-        <v>0.06547409432966071</v>
+        <v>7.477216646124508e-05</v>
       </c>
       <c r="O96" t="n">
-        <v>1.001676265965281</v>
+        <v>1.000000003375139</v>
       </c>
       <c r="P96" t="n">
-        <v>0.06826146207533422</v>
+        <v>7.795537238722289e-05</v>
       </c>
       <c r="Q96" t="n">
-        <v>234.9044028839665</v>
+        <v>200.0042593934624</v>
       </c>
       <c r="R96" t="n">
-        <v>371.4184952692049</v>
+        <v>298.7332012077866</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 10], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>model_11_7_5</t>
+          <t>model_3_7_0</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.9938536809809376</v>
+        <v>0.9999999782017038</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.086196163125871</v>
+        <v>0.6555855082500333</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9421883327439815</v>
+        <v>0.9999998917091525</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9678104484877081</v>
+        <v>0.9999999189702031</v>
       </c>
       <c r="G97" t="n">
-        <v>0.9759172739951334</v>
+        <v>0.9999998989152552</v>
       </c>
       <c r="H97" t="n">
-        <v>0.00428686433754993</v>
+        <v>1.520362647976472e-08</v>
       </c>
       <c r="I97" t="n">
-        <v>1.455056254825192</v>
+        <v>0.2402182830795437</v>
       </c>
       <c r="J97" t="n">
-        <v>0.005367410687973047</v>
+        <v>8.414343367327005e-08</v>
       </c>
       <c r="K97" t="n">
-        <v>0.02142547816009932</v>
+        <v>1.088696349308891e-08</v>
       </c>
       <c r="L97" t="n">
-        <v>0.01339643084655461</v>
+        <v>4.750688960010146e-08</v>
       </c>
       <c r="M97" t="n">
-        <v>0.08510637020689155</v>
+        <v>2.123938392069712e-05</v>
       </c>
       <c r="N97" t="n">
-        <v>0.06547415014759589</v>
+        <v>0.0001233029864997792</v>
       </c>
       <c r="O97" t="n">
-        <v>1.001676268823381</v>
+        <v>1.000000014139435</v>
       </c>
       <c r="P97" t="n">
-        <v>0.06826152026955445</v>
+        <v>0.0001285522499074443</v>
       </c>
       <c r="Q97" t="n">
-        <v>234.9043994738904</v>
+        <v>158.0034637067116</v>
       </c>
       <c r="R97" t="n">
-        <v>371.4184918591288</v>
+        <v>232.3548890236719</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 10], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>892</v>
+        <v>544</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>model_3_8_13</t>
+          <t>model_3_7_11</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.9868234505058795</v>
+        <v>0.9999999781940745</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.981858013838266</v>
+        <v>0.6555855581853158</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9731142804569755</v>
+        <v>0.999999891652635</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9944980018813278</v>
+        <v>0.9999999189733376</v>
       </c>
       <c r="G98" t="n">
-        <v>0.980457719100143</v>
+        <v>0.9999998988513028</v>
       </c>
       <c r="H98" t="n">
-        <v>0.009190229134400457</v>
+        <v>1.520894772343696e-08</v>
       </c>
       <c r="I98" t="n">
-        <v>1.382283675035602</v>
+        <v>0.2402182482512536</v>
       </c>
       <c r="J98" t="n">
-        <v>0.009517950466307023</v>
+        <v>8.418734845135642e-08</v>
       </c>
       <c r="K98" t="n">
-        <v>0.001015640458428667</v>
+        <v>1.088654234116888e-08</v>
       </c>
       <c r="L98" t="n">
-        <v>0.005266795462377459</v>
+        <v>4.753694539626266e-08</v>
       </c>
       <c r="M98" t="n">
-        <v>0.01820466383598073</v>
+        <v>2.115705962381663e-05</v>
       </c>
       <c r="N98" t="n">
-        <v>0.09586568277752189</v>
+        <v>0.0001233245625308963</v>
       </c>
       <c r="O98" t="n">
-        <v>1.00574976705198</v>
+        <v>1.000000014144384</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0999468833626819</v>
+        <v>0.0001285747444748746</v>
       </c>
       <c r="Q98" t="n">
-        <v>167.3792288198223</v>
+        <v>158.0027638325489</v>
       </c>
       <c r="R98" t="n">
-        <v>263.6704189844102</v>
+        <v>232.3541891495092</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Hidden Size=[10, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>894</v>
+        <v>545</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>model_3_8_1</t>
+          <t>model_3_7_1</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.9868234505058795</v>
+        <v>0.9999999781940745</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.981858013838266</v>
+        <v>0.6555855581853158</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9731142804569755</v>
+        <v>0.999999891652635</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9944980018813278</v>
+        <v>0.9999999189733376</v>
       </c>
       <c r="G99" t="n">
-        <v>0.980457719100143</v>
+        <v>0.9999998988513028</v>
       </c>
       <c r="H99" t="n">
-        <v>0.009190229134400457</v>
+        <v>1.520894772343696e-08</v>
       </c>
       <c r="I99" t="n">
-        <v>1.382283675035602</v>
+        <v>0.2402182482512536</v>
       </c>
       <c r="J99" t="n">
-        <v>0.009517950466307023</v>
+        <v>8.418734845135642e-08</v>
       </c>
       <c r="K99" t="n">
-        <v>0.001015640458428667</v>
+        <v>1.088654234116888e-08</v>
       </c>
       <c r="L99" t="n">
-        <v>0.005266795462377459</v>
+        <v>4.753694539626266e-08</v>
       </c>
       <c r="M99" t="n">
-        <v>0.01820466383598073</v>
+        <v>2.115705962381663e-05</v>
       </c>
       <c r="N99" t="n">
-        <v>0.09586568277752189</v>
+        <v>0.0001233245625308963</v>
       </c>
       <c r="O99" t="n">
-        <v>1.00574976705198</v>
+        <v>1.000000014144384</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0999468833626819</v>
+        <v>0.0001285747444748746</v>
       </c>
       <c r="Q99" t="n">
-        <v>167.3792288198223</v>
+        <v>158.0027638325489</v>
       </c>
       <c r="R99" t="n">
-        <v>263.6704189844102</v>
+        <v>232.3541891495092</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Hidden Size=[10, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>895</v>
+        <v>546</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>model_3_8_2</t>
+          <t>model_3_7_13</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.9868234505058795</v>
+        <v>0.9999999781940745</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.981858013838266</v>
+        <v>0.6555855581853158</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9731142804569755</v>
+        <v>0.999999891652635</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9944980018813278</v>
+        <v>0.9999999189733376</v>
       </c>
       <c r="G100" t="n">
-        <v>0.980457719100143</v>
+        <v>0.9999998988513028</v>
       </c>
       <c r="H100" t="n">
-        <v>0.009190229134400457</v>
+        <v>1.520894772343696e-08</v>
       </c>
       <c r="I100" t="n">
-        <v>1.382283675035602</v>
+        <v>0.2402182482512536</v>
       </c>
       <c r="J100" t="n">
-        <v>0.009517950466307023</v>
+        <v>8.418734845135642e-08</v>
       </c>
       <c r="K100" t="n">
-        <v>0.001015640458428667</v>
+        <v>1.088654234116888e-08</v>
       </c>
       <c r="L100" t="n">
-        <v>0.005266795462377459</v>
+        <v>4.753694539626266e-08</v>
       </c>
       <c r="M100" t="n">
-        <v>0.01820466383598073</v>
+        <v>2.115705962381663e-05</v>
       </c>
       <c r="N100" t="n">
-        <v>0.09586568277752189</v>
+        <v>0.0001233245625308963</v>
       </c>
       <c r="O100" t="n">
-        <v>1.00574976705198</v>
+        <v>1.000000014144384</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0999468833626819</v>
+        <v>0.0001285747444748746</v>
       </c>
       <c r="Q100" t="n">
-        <v>167.3792288198223</v>
+        <v>158.0027638325489</v>
       </c>
       <c r="R100" t="n">
-        <v>263.6704189844102</v>
+        <v>232.3541891495092</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Hidden Size=[10, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>896</v>
+        <v>547</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>model_3_8_3</t>
+          <t>model_3_7_23</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.9868234505058795</v>
+        <v>0.9999999781940745</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.981858013838266</v>
+        <v>0.6555855581853158</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9731142804569755</v>
+        <v>0.999999891652635</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9944980018813278</v>
+        <v>0.9999999189733376</v>
       </c>
       <c r="G101" t="n">
-        <v>0.980457719100143</v>
+        <v>0.9999998988513028</v>
       </c>
       <c r="H101" t="n">
-        <v>0.009190229134400457</v>
+        <v>1.520894772343696e-08</v>
       </c>
       <c r="I101" t="n">
-        <v>1.382283675035602</v>
+        <v>0.2402182482512536</v>
       </c>
       <c r="J101" t="n">
-        <v>0.009517950466307023</v>
+        <v>8.418734845135642e-08</v>
       </c>
       <c r="K101" t="n">
-        <v>0.001015640458428667</v>
+        <v>1.088654234116888e-08</v>
       </c>
       <c r="L101" t="n">
-        <v>0.005266795462377459</v>
+        <v>4.753694539626266e-08</v>
       </c>
       <c r="M101" t="n">
-        <v>0.01820466383598073</v>
+        <v>2.115705962381663e-05</v>
       </c>
       <c r="N101" t="n">
-        <v>0.09586568277752189</v>
+        <v>0.0001233245625308963</v>
       </c>
       <c r="O101" t="n">
-        <v>1.00574976705198</v>
+        <v>1.000000014144384</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0999468833626819</v>
+        <v>0.0001285747444748746</v>
       </c>
       <c r="Q101" t="n">
-        <v>167.3792288198223</v>
+        <v>158.0027638325489</v>
       </c>
       <c r="R101" t="n">
-        <v>263.6704189844102</v>
+        <v>232.3541891495092</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Hidden Size=[10, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>

--- a/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/fixed_results.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/fixed_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S101"/>
+  <dimension ref="A1:S100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,3210 +527,3210 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>301</v>
+        <v>28</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_24_4_24</t>
+          <t>model_23_8_5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9999999806619203</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6876218693451388</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999439809756</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999997514965295</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9999998942912885</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H2" t="n">
-        <v>1.348770282944445e-08</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2178739281156145</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J2" t="n">
-        <v>2.855521134126945e-08</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.03699967670796e-08</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.946260405417452e-08</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.658110703139747e-05</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001161365697334154</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O2" t="n">
-        <v>1.000000027300818</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001210807439428085</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q2" t="n">
-        <v>118.2429749362951</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R2" t="n">
-        <v>168.2168837558914</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Hidden Size=[10], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>302</v>
+        <v>29</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_24_4_23</t>
+          <t>model_23_8_6</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9999999804207697</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6876192637821648</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E3" t="n">
-        <v>0.99999994613141</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999997475641398</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9999998946918838</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36558978018298e-08</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2178757454138963</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J3" t="n">
-        <v>2.745904609430782e-08</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.116706594760257e-08</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>3.931305602095519e-08</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.732136296596167e-05</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001168584519914148</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O3" t="n">
-        <v>1.000000027641266</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001218333582230333</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q3" t="n">
-        <v>118.2181886704763</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R3" t="n">
-        <v>168.1920974900725</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Hidden Size=[10], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>304</v>
+        <v>30</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_24_4_22</t>
+          <t>model_23_8_7</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9999999800112873</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6876170626521457</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E4" t="n">
-        <v>0.99999994815757</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999997415294031</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9999998943974835</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H4" t="n">
-        <v>1.394149884321051e-08</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2178772806329032</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J4" t="n">
-        <v>2.64262286293823e-08</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.239026685042467e-08</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.94229599263799e-08</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.821759625908838e-05</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001180741243592791</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O4" t="n">
-        <v>1.000000028219359</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001231007842803863</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q4" t="n">
-        <v>118.1767918327205</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R4" t="n">
-        <v>168.1507006523167</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Hidden Size=[10], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>306</v>
+        <v>31</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_24_4_21</t>
+          <t>model_23_8_8</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9999999793581077</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6876137797467825</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999999506888863</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999997305355558</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9999998931804955</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H5" t="n">
-        <v>1.439707111422609e-08</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2178795703562126</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J5" t="n">
-        <v>2.513591214199747e-08</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>5.461864638624463e-08</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.987727926412105e-08</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.935594593541231e-05</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0001199877956886703</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O5" t="n">
-        <v>1.000000029141495</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0001250959245601155</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q5" t="n">
-        <v>118.1124820917948</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R5" t="n">
-        <v>168.086390911391</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Hidden Size=[10], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>351</v>
+        <v>32</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_38_9_24</t>
+          <t>model_23_8_9</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9999999395272041</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6993690008551376</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999999379075246</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.999999874153959</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9999999142933731</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H6" t="n">
-        <v>4.217787448118276e-08</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2096806730986621</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J6" t="n">
-        <v>4.674797277166518e-08</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.631381515985109e-08</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.148458723577943e-08</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>7.463044668731696e-05</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002053725261109254</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O6" t="n">
-        <v>1.000000043980215</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002141156597272045</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q6" t="n">
-        <v>147.9627401095845</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R6" t="n">
-        <v>217.4386621270719</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Hidden Size=[14], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>518</v>
+        <v>33</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>model_38_9_22</t>
+          <t>model_23_8_10</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9999999165544189</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6993321150599113</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999999215478872</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999998667102848</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G7" t="n">
-        <v>0.999999901110316</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H7" t="n">
-        <v>5.82006701440073e-08</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2097063997815152</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J7" t="n">
-        <v>5.906476118269603e-08</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>5.964472400978124e-08</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.940374449869302e-08</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>8.206195377082635e-05</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000241248150550439</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O7" t="n">
-        <v>1.000000060687695</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002515185837718888</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q7" t="n">
-        <v>147.3187379355469</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R7" t="n">
-        <v>216.7946599530343</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Hidden Size=[14], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>686</v>
+        <v>34</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>model_2_3_1</t>
+          <t>model_23_8_11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9999996977015518</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7092111689960855</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999999436636311</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999996870970161</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9999998412177309</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H8" t="n">
-        <v>2.108436663793775e-07</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2028160701587978</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J8" t="n">
-        <v>5.762961578110815e-08</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.128973426874331e-07</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.352634792342706e-07</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0001549579336752056</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00045917716230163</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9999975816124147</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0004787252847285735</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q8" t="n">
-        <v>72.7442977914375</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R8" t="n">
-        <v>98.34069011366971</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Hidden Size=[5], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>690</v>
+        <v>35</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>model_2_3_4</t>
+          <t>model_23_8_23</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9999996917946546</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7096035949748364</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9999998463743777</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999991644944359</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9999995741037109</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H9" t="n">
-        <v>2.149635415444389e-07</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2025423653725318</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J9" t="n">
-        <v>1.57152222764505e-07</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>5.684730525208435e-07</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.628126376426743e-07</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0002185428432803238</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0004636416089442781</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9999975343572372</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0004833797921074777</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q9" t="n">
-        <v>72.70559479481999</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R9" t="n">
-        <v>98.30198711705219</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Hidden Size=[5], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>692</v>
+        <v>36</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>model_2_3_2</t>
+          <t>model_23_8_12</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9999996870684</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7094173706692531</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999999015487445</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999995130754009</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9999997464362478</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H10" t="n">
-        <v>2.18259955573923e-07</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2026722509726631</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J10" t="n">
-        <v>1.007112836915295e-07</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.313006221630189e-07</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>2.160059529272742e-07</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0001912336084530859</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0004671830000908884</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9999974965472003</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0004870719476068895</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q10" t="n">
-        <v>72.67515805561614</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R10" t="n">
-        <v>98.27155037784834</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Hidden Size=[5], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>694</v>
+        <v>37</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>model_2_3_3</t>
+          <t>model_23_8_14</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9999996788573463</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7096055405836748</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999998668266097</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9999993247156949</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9999996503675567</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H11" t="n">
-        <v>2.23986907433818e-07</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2025410083715173</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J11" t="n">
-        <v>1.362304932446047e-07</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>4.594594539526444e-07</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>2.978449735986246e-07</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002080533661288841</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N11" t="n">
-        <v>0.000473272550898336</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9999974308587705</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0004934207431993181</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q11" t="n">
-        <v>72.6233564715115</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R11" t="n">
-        <v>98.2197487937437</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Hidden Size=[5], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1495</v>
+        <v>38</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>model_20_5_5</t>
+          <t>model_23_8_15</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9999901879963111</v>
+        <v>0.9999884752780204</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6875647262211237</v>
+        <v>0.7089874218240296</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9999961488648854</v>
+        <v>0.9999528494425804</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9999821426530602</v>
+        <v>0.999973474197403</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9999954551971122</v>
+        <v>0.9999714125560164</v>
       </c>
       <c r="H12" t="n">
-        <v>6.843564182611307e-06</v>
+        <v>8.038131359843399e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2179137836486118</v>
+        <v>0.2029721267789535</v>
       </c>
       <c r="J12" t="n">
-        <v>4.628792566847459e-06</v>
+        <v>2.336171527061545e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>1.180739102069544e-06</v>
+        <v>2.687660493671456e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>2.904765834458502e-06</v>
+        <v>2.511949433676961e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0005759359764579019</v>
+        <v>0.0008615130965095575</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002616020677022891</v>
+        <v>0.002835159847317854</v>
       </c>
       <c r="O12" t="n">
-        <v>1.000018114468349</v>
+        <v>1.000005319102452</v>
       </c>
       <c r="P12" t="n">
-        <v>0.002727390093153101</v>
+        <v>0.00295585847160814</v>
       </c>
       <c r="Q12" t="n">
-        <v>97.78440376543074</v>
+        <v>175.4626278394331</v>
       </c>
       <c r="R12" t="n">
-        <v>142.8828092855541</v>
+        <v>268.0971905294164</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Hidden Size=[9], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1675</v>
+        <v>150</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>model_20_5_4</t>
+          <t>model_14_8_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9999881130278672</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6878937148124503</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999956247171677</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999857558755808</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9999951492548108</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H13" t="n">
-        <v>8.290789456218834e-06</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2176843244462429</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J13" t="n">
-        <v>5.258781125443174e-06</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>9.418305380481646e-07</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>3.100305831745669e-06</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0006108776250301727</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002879373101252916</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O13" t="n">
-        <v>1.000021945179322</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P13" t="n">
-        <v>0.00300195397529727</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q13" t="n">
-        <v>97.4007307268184</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R13" t="n">
-        <v>142.4991362469418</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Hidden Size=[9], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2117</v>
+        <v>151</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>model_12_1_16</t>
+          <t>model_14_8_12</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9999624432869626</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6940630525253451</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999209896837229</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9999752491518192</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9999770064157482</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H14" t="n">
-        <v>2.619462693954217e-05</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2133814052932204</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J14" t="n">
-        <v>1.475490198270067e-05</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>1.861530130428589e-05</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>1.668510164349328e-05</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002598647410953506</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N14" t="n">
-        <v>0.005118068672804437</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O14" t="n">
-        <v>1.000180272222579</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P14" t="n">
-        <v>0.005335955452068437</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q14" t="n">
-        <v>79.09991249374431</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R14" t="n">
-        <v>114.4473114149221</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Hidden Size=[7], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2146</v>
+        <v>152</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>model_12_1_15</t>
+          <t>model_14_8_3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9999537885357667</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6951906919065274</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999043494580043</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9999698965455995</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9999720912895751</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H15" t="n">
-        <v>3.223104388062146e-05</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2125949122664486</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J15" t="n">
-        <v>1.786240630640725e-05</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>2.264103718276805e-05</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>2.025172174458765e-05</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>0.002877562537275145</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N15" t="n">
-        <v>0.005677239107226457</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O15" t="n">
-        <v>1.00022181502832</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P15" t="n">
-        <v>0.005918930929526174</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.68516094836836</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R15" t="n">
-        <v>114.0325598695462</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Hidden Size=[7], regularizer=0.05, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2204</v>
+        <v>153</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>model_34_4_10</t>
+          <t>model_14_8_4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9999341760621283</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7053228321503262</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999008475262201</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9993987599105946</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9998425031358303</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H16" t="n">
-        <v>4.591012782516773e-05</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2055280628986425</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J16" t="n">
-        <v>8.456004079445233e-05</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>9.004511915443791e-05</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>8.730375299543441e-05</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>0.003708052673618329</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N16" t="n">
-        <v>0.006775701279215881</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O16" t="n">
-        <v>1.000054474983066</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P16" t="n">
-        <v>0.007064156910307357</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q16" t="n">
-        <v>125.9776496309031</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R16" t="n">
-        <v>190.5780683489178</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Hidden Size=[13], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2206</v>
+        <v>154</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>model_34_4_11</t>
+          <t>model_14_8_15</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.999933801701145</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D17" t="n">
-        <v>0.705236865230241</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9998873563329915</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9993224185468131</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9998218104708697</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H17" t="n">
-        <v>4.617123284486323e-05</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2055880221234696</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J17" t="n">
-        <v>9.606571287992681e-05</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0001014784339304212</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>9.877412302509688e-05</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>0.00369559027898991</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00679494171018878</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O17" t="n">
-        <v>1.000054784799052</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P17" t="n">
-        <v>0.007084216446259955</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q17" t="n">
-        <v>125.966307239018</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R17" t="n">
-        <v>190.5667259570326</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Hidden Size=[13], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2464</v>
+        <v>155</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>model_6_2_2</t>
+          <t>model_14_8_16</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9998347941286017</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6946298100710875</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9998678159818952</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9999817651887613</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9999193941071228</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000115225902894896</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.212986109718203</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J18" t="n">
-        <v>5.292546349918628e-05</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>4.190712486758677e-06</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>2.855808799297248e-05</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>0.003528054321863238</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01073433290404653</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O18" t="n">
-        <v>1.00396494091356</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0111913156789042</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q18" t="n">
-        <v>68.1372319669192</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R18" t="n">
-        <v>98.60912758862422</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Hidden Size=[6], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2447</v>
+        <v>156</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>model_6_2_3</t>
+          <t>model_14_8_17</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9998633966794602</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6923963089712084</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999012449282039</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999861738207476</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9999397132915699</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H19" t="n">
-        <v>9.527652264659747e-05</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2145439065366329</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J19" t="n">
-        <v>3.954077068198084e-05</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>3.177523544322905e-06</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L19" t="n">
-        <v>2.135914711315187e-05</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>0.003140019345064315</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N19" t="n">
-        <v>0.009760969349741728</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O19" t="n">
-        <v>1.003278479692955</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P19" t="n">
-        <v>0.01017651402295231</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q19" t="n">
-        <v>68.51745425947129</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R19" t="n">
-        <v>98.98934988117631</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Hidden Size=[6], regularizer=0.2, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>model_1_9_10</t>
+          <t>model_14_8_18</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9999824376857704</v>
+        <v>0.9999608319970278</v>
       </c>
       <c r="D20" t="n">
-        <v>0.632739324669802</v>
+        <v>0.6985302352572142</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999788457550571</v>
+        <v>0.9999267873887729</v>
       </c>
       <c r="F20" t="n">
-        <v>0.999976369464441</v>
+        <v>0.9999830831127808</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9999773445468096</v>
+        <v>0.9999425692534687</v>
       </c>
       <c r="H20" t="n">
-        <v>1.224916219316119e-05</v>
+        <v>2.731845102632764e-05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2561527780732892</v>
+        <v>0.2102656857408874</v>
       </c>
       <c r="J20" t="n">
-        <v>4.428862769549209e-06</v>
+        <v>7.823985402794642e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.897840316982885e-05</v>
+        <v>6.083376499746835e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>2.170338111783876e-05</v>
+        <v>4.21616152992325e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0009337966631654914</v>
+        <v>0.001924970739619317</v>
       </c>
       <c r="N20" t="n">
-        <v>0.003499880311262257</v>
+        <v>0.005226705561472508</v>
       </c>
       <c r="O20" t="n">
-        <v>1.000021074777075</v>
+        <v>1.000034816002642</v>
       </c>
       <c r="P20" t="n">
-        <v>0.00364887746186371</v>
+        <v>0.00544921723799647</v>
       </c>
       <c r="Q20" t="n">
-        <v>110.6201060314148</v>
+        <v>123.0158964445897</v>
       </c>
       <c r="R20" t="n">
-        <v>164.2506423256156</v>
+        <v>185.1785635128679</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 4], regularizer=0.5, learning_rate=0.05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>model_1_9_11</t>
+          <t>model_27_9_0</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9999812230682711</v>
+        <v>0.9999363396204238</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6321752101827884</v>
+        <v>0.6980447931667617</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999465781440237</v>
+        <v>0.999618160175918</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9999734370016319</v>
+        <v>0.9998521351268006</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9999712934285331</v>
+        <v>0.9997825733325638</v>
       </c>
       <c r="H21" t="n">
-        <v>1.309631972362924e-05</v>
+        <v>4.44011139144324e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2565462301979142</v>
+        <v>0.2106042663415774</v>
       </c>
       <c r="J21" t="n">
-        <v>1.118442514271067e-05</v>
+        <v>0.0002152579058842146</v>
       </c>
       <c r="K21" t="n">
-        <v>4.381548006833604e-05</v>
+        <v>6.22490543296872e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>2.75002073848097e-05</v>
+        <v>0.0001387525935059136</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0009322422409937476</v>
+        <v>0.00241699650699284</v>
       </c>
       <c r="N21" t="n">
-        <v>0.003618883767631843</v>
+        <v>0.006663416084444404</v>
       </c>
       <c r="O21" t="n">
-        <v>1.000022532318075</v>
+        <v>1.000044936738524</v>
       </c>
       <c r="P21" t="n">
-        <v>0.003772947141742065</v>
+        <v>0.006947091502332062</v>
       </c>
       <c r="Q21" t="n">
-        <v>110.4863586087099</v>
+        <v>136.0444920013558</v>
       </c>
       <c r="R21" t="n">
-        <v>164.1168949029107</v>
+        <v>206.7392898437114</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>293</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>model_1_9_9</t>
+          <t>model_27_9_3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9999810071025832</v>
+        <v>0.9999363386878347</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6333633637238554</v>
+        <v>0.6980447310603225</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999957632228472</v>
+        <v>0.9996181454355461</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9999751579086703</v>
+        <v>0.9998521452074561</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9999781498345034</v>
+        <v>0.9997825694522332</v>
       </c>
       <c r="H22" t="n">
-        <v>1.324694900318108e-05</v>
+        <v>4.440176436608736e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2557175304465775</v>
+        <v>0.2106043096588668</v>
       </c>
       <c r="J22" t="n">
-        <v>8.870136771804359e-07</v>
+        <v>0.0002152662156030634</v>
       </c>
       <c r="K22" t="n">
-        <v>4.097685594184648e-05</v>
+        <v>6.224481051392741e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>2.093193480951346e-05</v>
+        <v>0.0001387550697704113</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0009662341618183339</v>
+        <v>0.002416952251804651</v>
       </c>
       <c r="N22" t="n">
-        <v>0.003639635833868695</v>
+        <v>0.006663464891937779</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0000227914769</v>
+        <v>1.000044937396823</v>
       </c>
       <c r="P22" t="n">
-        <v>0.003794582666401319</v>
+        <v>0.006947142387661475</v>
       </c>
       <c r="Q22" t="n">
-        <v>110.4634865919154</v>
+        <v>136.0444627026814</v>
       </c>
       <c r="R22" t="n">
-        <v>164.0940228861162</v>
+        <v>206.739260545037</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>294</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>model_15_8_5</t>
+          <t>model_27_9_1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9999783783833383</v>
+        <v>0.9999363386878347</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7149941759477471</v>
+        <v>0.6980447310603225</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9995860565780834</v>
+        <v>0.9996181454355461</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999943726253411</v>
+        <v>0.9998521452074561</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9999030852053284</v>
+        <v>0.9997825694522332</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5080398056136e-05</v>
+        <v>4.440176436608736e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1987826045693948</v>
+        <v>0.2106043096588668</v>
       </c>
       <c r="J23" t="n">
-        <v>9.026402385932538e-05</v>
+        <v>0.0002152662156030634</v>
       </c>
       <c r="K23" t="n">
-        <v>3.988461790937978e-06</v>
+        <v>6.224481051392741e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>4.712624282513169e-05</v>
+        <v>0.0001387550697704113</v>
       </c>
       <c r="M23" t="n">
-        <v>0.001332518631016334</v>
+        <v>0.002416952251804651</v>
       </c>
       <c r="N23" t="n">
-        <v>0.003883348819786346</v>
+        <v>0.006663464891937779</v>
       </c>
       <c r="O23" t="n">
-        <v>1.000019219214811</v>
+        <v>1.000044937396823</v>
       </c>
       <c r="P23" t="n">
-        <v>0.004048671018684913</v>
+        <v>0.006947142387661475</v>
       </c>
       <c r="Q23" t="n">
-        <v>124.2042295988747</v>
+        <v>136.0444627026814</v>
       </c>
       <c r="R23" t="n">
-        <v>186.3668966671529</v>
+        <v>206.739260545037</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>model_15_8_1</t>
+          <t>model_27_9_2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9999783778667723</v>
+        <v>0.9999363386878347</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7149944826474529</v>
+        <v>0.6980447310603225</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9995860503843127</v>
+        <v>0.9996181454355461</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999943713609607</v>
+        <v>0.9998521452074561</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9999030820196078</v>
+        <v>0.9997825694522332</v>
       </c>
       <c r="H24" t="n">
-        <v>1.508075834457701e-05</v>
+        <v>4.440176436608736e-05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1987823906559895</v>
+        <v>0.2106043096588668</v>
       </c>
       <c r="J24" t="n">
-        <v>9.026537446580411e-05</v>
+        <v>0.0002152662156030634</v>
       </c>
       <c r="K24" t="n">
-        <v>3.989357933954833e-06</v>
+        <v>6.224481051392741e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>4.712779192864263e-05</v>
+        <v>0.0001387550697704113</v>
       </c>
       <c r="M24" t="n">
-        <v>0.001332664111957869</v>
+        <v>0.002416952251804651</v>
       </c>
       <c r="N24" t="n">
-        <v>0.00388339520839394</v>
+        <v>0.006663464891937779</v>
       </c>
       <c r="O24" t="n">
-        <v>1.00001921967398</v>
+        <v>1.000044937396823</v>
       </c>
       <c r="P24" t="n">
-        <v>0.004048719382151571</v>
+        <v>0.006947142387661475</v>
       </c>
       <c r="Q24" t="n">
-        <v>124.2041818170939</v>
+        <v>136.0444627026814</v>
       </c>
       <c r="R24" t="n">
-        <v>186.3668488853721</v>
+        <v>206.739260545037</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>296</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>model_15_8_4</t>
+          <t>model_27_9_5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9999783778495409</v>
+        <v>0.9999363386878347</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7149942983076065</v>
+        <v>0.6980447310603225</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9995860515040325</v>
+        <v>0.9996181454355461</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999943709038286</v>
+        <v>0.9998521452074561</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9999030828130285</v>
+        <v>0.9997825694522332</v>
       </c>
       <c r="H25" t="n">
-        <v>1.50807703629823e-05</v>
+        <v>4.440176436608736e-05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1987825192272386</v>
+        <v>0.2106043096588668</v>
       </c>
       <c r="J25" t="n">
-        <v>9.026513030100994e-05</v>
+        <v>0.0002152662156030634</v>
       </c>
       <c r="K25" t="n">
-        <v>3.989681931275974e-06</v>
+        <v>6.224481051392741e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>4.712740611614296e-05</v>
+        <v>0.0001387550697704113</v>
       </c>
       <c r="M25" t="n">
-        <v>0.00133253333351798</v>
+        <v>0.002416952251804651</v>
       </c>
       <c r="N25" t="n">
-        <v>0.003883396755803133</v>
+        <v>0.006663464891937779</v>
       </c>
       <c r="O25" t="n">
-        <v>1.000019219689297</v>
+        <v>1.000044937396823</v>
       </c>
       <c r="P25" t="n">
-        <v>0.004048720995437177</v>
+        <v>0.006947142387661475</v>
       </c>
       <c r="Q25" t="n">
-        <v>124.2041802232217</v>
+        <v>136.0444627026814</v>
       </c>
       <c r="R25" t="n">
-        <v>186.3668472915</v>
+        <v>206.739260545037</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>297</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>model_15_91_11</t>
+          <t>model_27_9_9</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9999783777212938</v>
+        <v>0.9999363386878347</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7149939389980543</v>
+        <v>0.6980447310603225</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9999756800773948</v>
+        <v>0.9996181454355461</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999847319162147</v>
+        <v>0.9998521452074561</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9999805134869362</v>
+        <v>0.9997825694522332</v>
       </c>
       <c r="H26" t="n">
-        <v>1.508085981127559e-05</v>
+        <v>4.440176436608736e-05</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1987827698343582</v>
+        <v>0.2106043096588668</v>
       </c>
       <c r="J26" t="n">
-        <v>1.582264551773423e-05</v>
+        <v>0.0002152662156030634</v>
       </c>
       <c r="K26" t="n">
-        <v>9.387385216441107e-06</v>
+        <v>6.224481051392741e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>1.260544106559774e-05</v>
+        <v>0.0001387550697704113</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001332416715603493</v>
+        <v>0.002416952251804651</v>
       </c>
       <c r="N26" t="n">
-        <v>0.003883408272545599</v>
+        <v>0.006663464891937779</v>
       </c>
       <c r="O26" t="n">
-        <v>1.000019219803294</v>
+        <v>1.000044937396823</v>
       </c>
       <c r="P26" t="n">
-        <v>0.004048733002471212</v>
+        <v>0.006947142387661475</v>
       </c>
       <c r="Q26" t="n">
-        <v>124.204168360694</v>
+        <v>136.0444627026814</v>
       </c>
       <c r="R26" t="n">
-        <v>186.3668354289723</v>
+        <v>206.739260545037</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>298</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>model_15_91_5</t>
+          <t>model_27_9_4</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9999783777212938</v>
+        <v>0.9999363386878347</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7149939389980543</v>
+        <v>0.6980447310603225</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9999756800773948</v>
+        <v>0.9996181454355461</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9999847319162147</v>
+        <v>0.9998521452074561</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9999805134869362</v>
+        <v>0.9997825694522332</v>
       </c>
       <c r="H27" t="n">
-        <v>1.508085981127559e-05</v>
+        <v>4.440176436608736e-05</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1987827698343582</v>
+        <v>0.2106043096588668</v>
       </c>
       <c r="J27" t="n">
-        <v>1.582264551773423e-05</v>
+        <v>0.0002152662156030634</v>
       </c>
       <c r="K27" t="n">
-        <v>9.387385216441107e-06</v>
+        <v>6.224481051392741e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.260544106559774e-05</v>
+        <v>0.0001387550697704113</v>
       </c>
       <c r="M27" t="n">
-        <v>0.001332416715603493</v>
+        <v>0.002416952251804651</v>
       </c>
       <c r="N27" t="n">
-        <v>0.003883408272545599</v>
+        <v>0.006663464891937779</v>
       </c>
       <c r="O27" t="n">
-        <v>1.000019219803294</v>
+        <v>1.000044937396823</v>
       </c>
       <c r="P27" t="n">
-        <v>0.004048733002471212</v>
+        <v>0.006947142387661475</v>
       </c>
       <c r="Q27" t="n">
-        <v>124.204168360694</v>
+        <v>136.0444627026814</v>
       </c>
       <c r="R27" t="n">
-        <v>186.3668354289723</v>
+        <v>206.739260545037</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>model_15_91_17</t>
+          <t>model_27_9_11</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9999783777212938</v>
+        <v>0.9999363386878347</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7149939389980543</v>
+        <v>0.6980447310603225</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9999756800773948</v>
+        <v>0.9996181454355461</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9999847319162147</v>
+        <v>0.9998521452074561</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9999805134869362</v>
+        <v>0.9997825694522332</v>
       </c>
       <c r="H28" t="n">
-        <v>1.508085981127559e-05</v>
+        <v>4.440176436608736e-05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1987827698343582</v>
+        <v>0.2106043096588668</v>
       </c>
       <c r="J28" t="n">
-        <v>1.582264551773423e-05</v>
+        <v>0.0002152662156030634</v>
       </c>
       <c r="K28" t="n">
-        <v>9.387385216441107e-06</v>
+        <v>6.224481051392741e-05</v>
       </c>
       <c r="L28" t="n">
-        <v>1.260544106559774e-05</v>
+        <v>0.0001387550697704113</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001332416715603493</v>
+        <v>0.002416952251804651</v>
       </c>
       <c r="N28" t="n">
-        <v>0.003883408272545599</v>
+        <v>0.006663464891937779</v>
       </c>
       <c r="O28" t="n">
-        <v>1.000019219803294</v>
+        <v>1.000044937396823</v>
       </c>
       <c r="P28" t="n">
-        <v>0.004048733002471212</v>
+        <v>0.006947142387661475</v>
       </c>
       <c r="Q28" t="n">
-        <v>124.204168360694</v>
+        <v>136.0444627026814</v>
       </c>
       <c r="R28" t="n">
-        <v>186.3668354289723</v>
+        <v>206.739260545037</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 4], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>9</v>
+        <v>347</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>model_15_91_16</t>
+          <t>model_7_8_23</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9999783777212938</v>
+        <v>0.9999234912387716</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7149939389980543</v>
+        <v>0.6581129363422745</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9999756800773948</v>
+        <v>0.9997483243437091</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9999847319162147</v>
+        <v>0.999885611654839</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9999805134869362</v>
+        <v>0.9998339185374064</v>
       </c>
       <c r="H29" t="n">
-        <v>1.508085981127559e-05</v>
+        <v>5.336245629343939e-05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1987827698343582</v>
+        <v>0.2384554814220398</v>
       </c>
       <c r="J29" t="n">
-        <v>1.582264551773423e-05</v>
+        <v>0.0001817731440841656</v>
       </c>
       <c r="K29" t="n">
-        <v>9.387385216441107e-06</v>
+        <v>0.0001324386759531968</v>
       </c>
       <c r="L29" t="n">
-        <v>1.260544106559774e-05</v>
+        <v>0.0001571071327130013</v>
       </c>
       <c r="M29" t="n">
-        <v>0.001332416715603493</v>
+        <v>0.003089625212894956</v>
       </c>
       <c r="N29" t="n">
-        <v>0.003883408272545599</v>
+        <v>0.007304961074053673</v>
       </c>
       <c r="O29" t="n">
-        <v>1.000019219803294</v>
+        <v>1.000042702564407</v>
       </c>
       <c r="P29" t="n">
-        <v>0.004048733002471212</v>
+        <v>0.007615948390330206</v>
       </c>
       <c r="Q29" t="n">
-        <v>124.204168360694</v>
+        <v>153.6768062498612</v>
       </c>
       <c r="R29" t="n">
-        <v>186.3668354289723</v>
+        <v>235.3414865160307</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10</v>
+        <v>348</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>model_15_91_15</t>
+          <t>model_7_8_24</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9999783777212938</v>
+        <v>0.9999234486676564</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7149939389980543</v>
+        <v>0.6581743721363854</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9999756800773948</v>
+        <v>0.999743938984766</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9999847319162147</v>
+        <v>0.9998850190624539</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9999805134869362</v>
+        <v>0.9998318830537043</v>
       </c>
       <c r="H30" t="n">
-        <v>1.508085981127559e-05</v>
+        <v>5.339214830830798e-05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1987827698343582</v>
+        <v>0.2384126318865689</v>
       </c>
       <c r="J30" t="n">
-        <v>1.582264551773423e-05</v>
+        <v>0.0001849404765738016</v>
       </c>
       <c r="K30" t="n">
-        <v>9.387385216441107e-06</v>
+        <v>0.0001331247786393199</v>
       </c>
       <c r="L30" t="n">
-        <v>1.260544106559774e-05</v>
+        <v>0.0001590326276065607</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001332416715603493</v>
+        <v>0.003086604557187442</v>
       </c>
       <c r="N30" t="n">
-        <v>0.003883408272545599</v>
+        <v>0.007306993109912448</v>
       </c>
       <c r="O30" t="n">
-        <v>1.000019219803294</v>
+        <v>1.000042726325029</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004048733002471212</v>
+        <v>0.007618066934162383</v>
       </c>
       <c r="Q30" t="n">
-        <v>124.204168360694</v>
+        <v>153.6756937164677</v>
       </c>
       <c r="R30" t="n">
-        <v>186.3668354289723</v>
+        <v>235.3403739826371</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11</v>
+        <v>349</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>model_15_91_14</t>
+          <t>model_7_8_22</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9999783777212938</v>
+        <v>0.9999234102010466</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7149939389980543</v>
+        <v>0.658044606226555</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9999756800773948</v>
+        <v>0.9997531576242404</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9999847319162147</v>
+        <v>0.999886200330247</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9999805134869362</v>
+        <v>0.9998361249588964</v>
       </c>
       <c r="H31" t="n">
-        <v>1.508085981127559e-05</v>
+        <v>5.341897755957801e-05</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1987827698343582</v>
+        <v>0.2385031395301449</v>
       </c>
       <c r="J31" t="n">
-        <v>1.582264551773423e-05</v>
+        <v>0.0001782822995131146</v>
       </c>
       <c r="K31" t="n">
-        <v>9.387385216441107e-06</v>
+        <v>0.0001317571083382833</v>
       </c>
       <c r="L31" t="n">
-        <v>1.260544106559774e-05</v>
+        <v>0.0001550199367766194</v>
       </c>
       <c r="M31" t="n">
-        <v>0.001332416715603493</v>
+        <v>0.003092935849647407</v>
       </c>
       <c r="N31" t="n">
-        <v>0.003883408272545599</v>
+        <v>0.00730882874061077</v>
       </c>
       <c r="O31" t="n">
-        <v>1.000019219803294</v>
+        <v>1.000042747794765</v>
       </c>
       <c r="P31" t="n">
-        <v>0.004048733002471212</v>
+        <v>0.007619980711459811</v>
       </c>
       <c r="Q31" t="n">
-        <v>124.204168360694</v>
+        <v>153.6746889802432</v>
       </c>
       <c r="R31" t="n">
-        <v>186.3668354289723</v>
+        <v>235.3393692464126</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 4], regularizer=0.03, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>166</v>
+        <v>350</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>model_26_8_20</t>
+          <t>model_7_8_21</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9999175600278689</v>
+        <v>0.9999231535652613</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6844242091420173</v>
+        <v>0.6579684796556798</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9998829304706699</v>
+        <v>0.9997584623215144</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9986958490108135</v>
+        <v>0.9998867539653675</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9998249307160491</v>
+        <v>0.9998384884503001</v>
       </c>
       <c r="H32" t="n">
-        <v>5.749928948059668e-05</v>
+        <v>5.359797295382842e-05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2201041956051232</v>
+        <v>0.2385562354206792</v>
       </c>
       <c r="J32" t="n">
-        <v>5.499577353764501e-05</v>
+        <v>0.0001744509734479692</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0001822836770231747</v>
+        <v>0.0001311161103220537</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0001186395041790392</v>
+        <v>0.0001527841583107757</v>
       </c>
       <c r="M32" t="n">
-        <v>0.003552437546164673</v>
+        <v>0.00309674237271879</v>
       </c>
       <c r="N32" t="n">
-        <v>0.007582828593644768</v>
+        <v>0.007321063649076438</v>
       </c>
       <c r="O32" t="n">
-        <v>1.000058192921504</v>
+        <v>1.000042891033343</v>
       </c>
       <c r="P32" t="n">
-        <v>0.007905645305495354</v>
+        <v>0.007632736485308616</v>
       </c>
       <c r="Q32" t="n">
-        <v>135.527475934193</v>
+        <v>153.6679986172564</v>
       </c>
       <c r="R32" t="n">
-        <v>206.2222737765486</v>
+        <v>235.3326788834259</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[6, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>167</v>
+        <v>354</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>model_26_8_22</t>
+          <t>model_7_8_20</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9999174181823928</v>
+        <v>0.9999226750759822</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6844970630138659</v>
+        <v>0.6578835561543264</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9998709921095716</v>
+        <v>0.9997643119206426</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9985695115522971</v>
+        <v>0.99988726014416</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9998077634031004</v>
+        <v>0.9998410326303968</v>
       </c>
       <c r="H33" t="n">
-        <v>5.759822224207356e-05</v>
+        <v>5.393170418712498e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2200533823192994</v>
+        <v>0.2386154668937353</v>
       </c>
       <c r="J33" t="n">
-        <v>6.060405954618704e-05</v>
+        <v>0.0001702260911497613</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0001999421051308726</v>
+        <v>0.0001305300571802796</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0001302733068104245</v>
+        <v>0.0001503774547940566</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003579759020839035</v>
+        <v>0.003100778132001686</v>
       </c>
       <c r="N33" t="n">
-        <v>0.007589349263413403</v>
+        <v>0.007343820816654297</v>
       </c>
       <c r="O33" t="n">
-        <v>1.000058293047723</v>
+        <v>1.000043158097126</v>
       </c>
       <c r="P33" t="n">
-        <v>0.007912443573675688</v>
+        <v>0.007656462472624095</v>
       </c>
       <c r="Q33" t="n">
-        <v>135.5240377091832</v>
+        <v>153.6555840982613</v>
       </c>
       <c r="R33" t="n">
-        <v>206.2188355515389</v>
+        <v>235.3202643644307</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[6, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>168</v>
+        <v>358</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>model_26_8_19</t>
+          <t>model_7_8_19</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9999171132901271</v>
+        <v>0.9999218884764897</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6843842430849003</v>
+        <v>0.6577890301539067</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9998891344438654</v>
+        <v>0.999770707332716</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9987554601202251</v>
+        <v>0.9998876712224747</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9998332285172216</v>
+        <v>0.9998437243590779</v>
       </c>
       <c r="H34" t="n">
-        <v>5.781087501457174e-05</v>
+        <v>5.448033261042878e-05</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2201320706738328</v>
+        <v>0.2386813958080845</v>
       </c>
       <c r="J34" t="n">
-        <v>5.208133195026384e-05</v>
+        <v>0.0001656069945814301</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0001739517182967122</v>
+        <v>0.0001300541112467218</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0001130163189196471</v>
+        <v>0.0001478311755855109</v>
       </c>
       <c r="M34" t="n">
-        <v>0.003537470590598948</v>
+        <v>0.003105509286460187</v>
       </c>
       <c r="N34" t="n">
-        <v>0.007603346303738357</v>
+        <v>0.007381079366219332</v>
       </c>
       <c r="O34" t="n">
-        <v>1.000058508265793</v>
+        <v>1.000043597129401</v>
       </c>
       <c r="P34" t="n">
-        <v>0.007927036496985144</v>
+        <v>0.007695307195779945</v>
       </c>
       <c r="Q34" t="n">
-        <v>135.5166673018854</v>
+        <v>153.6353415819152</v>
       </c>
       <c r="R34" t="n">
-        <v>206.2114651442411</v>
+        <v>235.3000218480846</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[6, 6], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>169</v>
+        <v>404</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>model_26_8_23</t>
+          <t>model_11_9_1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9999169242335386</v>
+        <v>0.9999044586474278</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6845303143463952</v>
+        <v>0.6394939999320505</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9998652723934057</v>
+        <v>0.9999807870257043</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9985039579636773</v>
+        <v>0.9999096488629826</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9997990205907366</v>
+        <v>0.9999517487964531</v>
       </c>
       <c r="H35" t="n">
-        <v>5.794273604307085e-05</v>
+        <v>6.663709056307495e-05</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2200301905599465</v>
+        <v>0.2514416043766982</v>
       </c>
       <c r="J35" t="n">
-        <v>6.329101162296232e-05</v>
+        <v>1.673743540997054e-05</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0002091046555370538</v>
+        <v>5.464315340063894e-05</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0001361980635728198</v>
+        <v>3.569073501061975e-05</v>
       </c>
       <c r="M35" t="n">
-        <v>0.003592432253035084</v>
+        <v>0.001777179662792743</v>
       </c>
       <c r="N35" t="n">
-        <v>0.00761201261448448</v>
+        <v>0.008163154449296849</v>
       </c>
       <c r="O35" t="n">
-        <v>1.000058641717502</v>
+        <v>1.000037590040356</v>
       </c>
       <c r="P35" t="n">
-        <v>0.007936071750521466</v>
+        <v>0.008510676834262676</v>
       </c>
       <c r="Q35" t="n">
-        <v>135.5121106894625</v>
+        <v>189.2324984401525</v>
       </c>
       <c r="R35" t="n">
-        <v>206.2069085318181</v>
+        <v>292.8369435539495</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[7, 7], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>170</v>
+        <v>405</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>model_26_8_18</t>
+          <t>model_11_9_9</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9999162441627131</v>
+        <v>0.9999044586474278</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6843416630972603</v>
+        <v>0.6394939999320505</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9998954560609334</v>
+        <v>0.9999807870257043</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9988116207934004</v>
+        <v>0.9999096488629826</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9998412117896859</v>
+        <v>0.9999517487964531</v>
       </c>
       <c r="H36" t="n">
-        <v>5.841706406934232e-05</v>
+        <v>6.663709056307495e-05</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2201617688769266</v>
+        <v>0.2514416043766982</v>
       </c>
       <c r="J36" t="n">
-        <v>4.911162478001668e-05</v>
+        <v>1.673743540997054e-05</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0001661020336395298</v>
+        <v>5.464315340063894e-05</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0001076062808734784</v>
+        <v>3.569073501061975e-05</v>
       </c>
       <c r="M36" t="n">
-        <v>0.00352172106373943</v>
+        <v>0.001777179662792743</v>
       </c>
       <c r="N36" t="n">
-        <v>0.007643105656036839</v>
+        <v>0.008163154449296849</v>
       </c>
       <c r="O36" t="n">
-        <v>1.000059121767497</v>
+        <v>1.000037590040356</v>
       </c>
       <c r="P36" t="n">
-        <v>0.007968488487224177</v>
+        <v>0.008510676834262676</v>
       </c>
       <c r="Q36" t="n">
-        <v>135.4958050356839</v>
+        <v>189.2324984401525</v>
       </c>
       <c r="R36" t="n">
-        <v>206.1906028780395</v>
+        <v>292.8369435539495</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[7, 7], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>171</v>
+        <v>406</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>model_26_8_24</t>
+          <t>model_11_9_11</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.999916202485718</v>
+        <v>0.9999044586474278</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6845614681017209</v>
+        <v>0.6394939999320505</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9998596919703749</v>
+        <v>0.9999807870257043</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9984375597114954</v>
+        <v>0.9999096488629826</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9997902392984934</v>
+        <v>0.9999517487964531</v>
       </c>
       <c r="H37" t="n">
-        <v>5.844613246347704e-05</v>
+        <v>6.663709056307495e-05</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2200084617947666</v>
+        <v>0.2514416043766982</v>
       </c>
       <c r="J37" t="n">
-        <v>6.591252793893064e-05</v>
+        <v>1.673743540997054e-05</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0002183852661841201</v>
+        <v>5.464315340063894e-05</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0001421488970615254</v>
+        <v>3.569073501061975e-05</v>
       </c>
       <c r="M37" t="n">
-        <v>0.003604406103626687</v>
+        <v>0.001777179662792743</v>
       </c>
       <c r="N37" t="n">
-        <v>0.007645007028347132</v>
+        <v>0.008163154449296849</v>
       </c>
       <c r="O37" t="n">
-        <v>1.000059151186552</v>
+        <v>1.000037590040356</v>
       </c>
       <c r="P37" t="n">
-        <v>0.007970470804890103</v>
+        <v>0.008510676834262676</v>
       </c>
       <c r="Q37" t="n">
-        <v>135.4948100810499</v>
+        <v>189.2324984401525</v>
       </c>
       <c r="R37" t="n">
-        <v>206.1896079234055</v>
+        <v>292.8369435539495</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 4], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[7, 7], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>206</v>
+        <v>407</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>model_1_7_5</t>
+          <t>model_11_9_2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9999019210168766</v>
+        <v>0.9999044586474278</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6416420531688076</v>
+        <v>0.6394939999320505</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9996850657358354</v>
+        <v>0.9999807870257043</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9998822701620602</v>
+        <v>0.9999096488629826</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9998292185994488</v>
+        <v>0.9999517487964531</v>
       </c>
       <c r="H38" t="n">
-        <v>6.840700811507937e-05</v>
+        <v>6.663709056307495e-05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2499434047571774</v>
+        <v>0.2514416043766982</v>
       </c>
       <c r="J38" t="n">
-        <v>4.986914109913049e-05</v>
+        <v>1.673743540997054e-05</v>
       </c>
       <c r="K38" t="n">
-        <v>3.635885438510682e-05</v>
+        <v>5.464315340063894e-05</v>
       </c>
       <c r="L38" t="n">
-        <v>4.311399774211865e-05</v>
+        <v>3.569073501061975e-05</v>
       </c>
       <c r="M38" t="n">
-        <v>0.00331983683548586</v>
+        <v>0.001777179662792743</v>
       </c>
       <c r="N38" t="n">
-        <v>0.008270852925489569</v>
+        <v>0.008163154449296849</v>
       </c>
       <c r="O38" t="n">
-        <v>1.000117694779748</v>
+        <v>1.000037590040356</v>
       </c>
       <c r="P38" t="n">
-        <v>0.008622960257553502</v>
+        <v>0.008510676834262676</v>
       </c>
       <c r="Q38" t="n">
-        <v>107.1800705615228</v>
+        <v>189.2324984401525</v>
       </c>
       <c r="R38" t="n">
-        <v>160.8106068557236</v>
+        <v>292.8369435539495</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 4], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[7, 7], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>271</v>
+        <v>408</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>model_24_6_1</t>
+          <t>model_11_9_3</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9998772568522829</v>
+        <v>0.9999044586474278</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6953236951806069</v>
+        <v>0.6394939999320505</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9992464413357113</v>
+        <v>0.9999807870257043</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9999311630973508</v>
+        <v>0.9999096488629826</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9996049314884677</v>
+        <v>0.9999517487964531</v>
       </c>
       <c r="H39" t="n">
-        <v>8.560948772677005e-05</v>
+        <v>6.663709056307495e-05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2125021466630589</v>
+        <v>0.2514416043766982</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0004869797480956775</v>
+        <v>1.673743540997054e-05</v>
       </c>
       <c r="K39" t="n">
-        <v>4.807953428294554e-05</v>
+        <v>5.464315340063894e-05</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0002675279455697005</v>
+        <v>3.569073501061975e-05</v>
       </c>
       <c r="M39" t="n">
-        <v>0.003039641464052098</v>
+        <v>0.001777179662792743</v>
       </c>
       <c r="N39" t="n">
-        <v>0.009252539528517024</v>
+        <v>0.008163154449296849</v>
       </c>
       <c r="O39" t="n">
-        <v>1.000056650683562</v>
+        <v>1.000037590040356</v>
       </c>
       <c r="P39" t="n">
-        <v>0.009646439291643251</v>
+        <v>0.008510676834262676</v>
       </c>
       <c r="Q39" t="n">
-        <v>170.7314288860582</v>
+        <v>189.2324984401525</v>
       </c>
       <c r="R39" t="n">
-        <v>263.3659915760414</v>
+        <v>292.8369435539495</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
+          <t>Hidden Size=[7, 7], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>272</v>
+        <v>409</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>model_24_6_2</t>
+          <t>model_11_9_24</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9998772535679586</v>
+        <v>0.9999044586474278</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6953236171988354</v>
+        <v>0.6394939999320505</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9992464253770095</v>
+        <v>0.9999807870257043</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9999311582642559</v>
+        <v>0.9999096488629826</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9996049188770614</v>
+        <v>0.9999517487964531</v>
       </c>
       <c r="H40" t="n">
-        <v>8.561177843968698e-05</v>
+        <v>6.663709056307495e-05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2125022010528936</v>
+        <v>0.2514416043766982</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0004869900612470943</v>
+        <v>1.673743540997054e-05</v>
       </c>
       <c r="K40" t="n">
-        <v>4.808290998608842e-05</v>
+        <v>5.464315340063894e-05</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0002675364856165914</v>
+        <v>3.569073501061975e-05</v>
       </c>
       <c r="M40" t="n">
-        <v>0.00303957893450805</v>
+        <v>0.001777179662792743</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0092526633160235</v>
+        <v>0.008163154449296849</v>
       </c>
       <c r="O40" t="n">
-        <v>1.000056652199404</v>
+        <v>1.000037590040356</v>
       </c>
       <c r="P40" t="n">
-        <v>0.009646568349040152</v>
+        <v>0.008510676834262676</v>
       </c>
       <c r="Q40" t="n">
-        <v>170.7313753713758</v>
+        <v>189.2324984401525</v>
       </c>
       <c r="R40" t="n">
-        <v>263.3659380613591</v>
+        <v>292.8369435539495</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
+          <t>Hidden Size=[7, 7], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>model_24_6_3</t>
+          <t>model_11_9_4</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9998772468545838</v>
+        <v>0.9999044586474278</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6953233864263156</v>
+        <v>0.6394939999320505</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9992463892956478</v>
+        <v>0.9999807870257043</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9999311488343215</v>
+        <v>0.9999096488629826</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9996048968369156</v>
+        <v>0.9999517487964531</v>
       </c>
       <c r="H41" t="n">
-        <v>8.561646080760894e-05</v>
+        <v>6.663709056307495e-05</v>
       </c>
       <c r="I41" t="n">
-        <v>0.212502362009473</v>
+        <v>0.2514416043766982</v>
       </c>
       <c r="J41" t="n">
-        <v>0.000487013378466105</v>
+        <v>1.673743540997054e-05</v>
       </c>
       <c r="K41" t="n">
-        <v>4.808949637853128e-05</v>
+        <v>5.464315340063894e-05</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0002675514105087907</v>
+        <v>3.569073501061975e-05</v>
       </c>
       <c r="M41" t="n">
-        <v>0.003039656208896305</v>
+        <v>0.001777179662792743</v>
       </c>
       <c r="N41" t="n">
-        <v>0.009252916340679242</v>
+        <v>0.008163154449296849</v>
       </c>
       <c r="O41" t="n">
-        <v>1.000056655297884</v>
+        <v>1.000037590040356</v>
       </c>
       <c r="P41" t="n">
-        <v>0.009646832145479322</v>
+        <v>0.008510676834262676</v>
       </c>
       <c r="Q41" t="n">
-        <v>170.7312659882988</v>
+        <v>189.2324984401525</v>
       </c>
       <c r="R41" t="n">
-        <v>263.365828678282</v>
+        <v>292.8369435539495</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
+          <t>Hidden Size=[7, 7], regularizer=0.03, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>model_24_6_4</t>
+          <t>model_13_9_24</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9998772453676729</v>
+        <v>0.9999673817611036</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6953233605968566</v>
+        <v>0.6204445660583643</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9992463876845833</v>
+        <v>0.9999108076138213</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9999311419456817</v>
+        <v>0.9999274996444573</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9996048924758356</v>
+        <v>0.9999360044244613</v>
       </c>
       <c r="H42" t="n">
-        <v>8.561749788130167e-05</v>
+        <v>2.275019644197676e-05</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2125023800247088</v>
+        <v>0.2647279857816253</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0004870144196003748</v>
+        <v>0.0001137418546961061</v>
       </c>
       <c r="K42" t="n">
-        <v>4.809430778904601e-05</v>
+        <v>1.580827322209987e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0002675543636947104</v>
+        <v>6.477493675442601e-05</v>
       </c>
       <c r="M42" t="n">
-        <v>0.00303958479201932</v>
+        <v>0.002088341700504887</v>
       </c>
       <c r="N42" t="n">
-        <v>0.009252972380878572</v>
+        <v>0.004769716599754828</v>
       </c>
       <c r="O42" t="n">
-        <v>1.000056655984151</v>
+        <v>1.000060218287193</v>
       </c>
       <c r="P42" t="n">
-        <v>0.009646890571425959</v>
+        <v>0.004972773310080905</v>
       </c>
       <c r="Q42" t="n">
-        <v>170.7312417624104</v>
+        <v>95.38187355558486</v>
       </c>
       <c r="R42" t="n">
-        <v>263.3658044523936</v>
+        <v>140.4802790757083</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 6], regularizer=0.03, learning_rate=0.05</t>
+          <t>Hidden Size=[4, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>418</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>model_10_9_17</t>
+          <t>model_13_9_23</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9998543467922655</v>
+        <v>0.9999673172543997</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7208698788780216</v>
+        <v>0.6203274346284851</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9995018676523859</v>
+        <v>0.9999118978067055</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9998057146463667</v>
+        <v>0.9999334108108779</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9996241831794923</v>
+        <v>0.9999373277583774</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0001015885345277736</v>
+        <v>2.279518784053413e-05</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1946844864483355</v>
+        <v>0.264809681272536</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0003479491282802201</v>
+        <v>0.0001123515952139128</v>
       </c>
       <c r="K43" t="n">
-        <v>9.022056172498979e-05</v>
+        <v>1.45193783864857e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0002190848450026049</v>
+        <v>6.343548680019926e-05</v>
       </c>
       <c r="M43" t="n">
-        <v>0.002894344699846855</v>
+        <v>0.002106793058543936</v>
       </c>
       <c r="N43" t="n">
-        <v>0.01007911377690388</v>
+        <v>0.004774430629984494</v>
       </c>
       <c r="O43" t="n">
-        <v>1.000057306180092</v>
+        <v>1.000060337376493</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01050820251702851</v>
+        <v>0.004977688026336836</v>
       </c>
       <c r="Q43" t="n">
-        <v>188.3891597566478</v>
+        <v>95.37792220781158</v>
       </c>
       <c r="R43" t="n">
-        <v>291.9936048704449</v>
+        <v>140.476327727935</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[4, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>419</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>model_10_9_20</t>
+          <t>model_13_9_22</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.999854301070547</v>
+        <v>0.9999671035136081</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7204679321271619</v>
+        <v>0.6201858387776621</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9994480783848717</v>
+        <v>0.9999130893340858</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9997738911845117</v>
+        <v>0.9999389166918983</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9995792821478924</v>
+        <v>0.9999386714001314</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0001016204239894585</v>
+        <v>2.294426532480923e-05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1949648316739104</v>
+        <v>0.2649084399281403</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0003855213293871159</v>
+        <v>0.0001108321097514529</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0001049984672690873</v>
+        <v>1.331885363254863e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>0.0002452601916389126</v>
+        <v>6.207548169200074e-05</v>
       </c>
       <c r="M44" t="n">
-        <v>0.002764731093614225</v>
+        <v>0.002126486860026597</v>
       </c>
       <c r="N44" t="n">
-        <v>0.01008069561039606</v>
+        <v>0.004790017257255889</v>
       </c>
       <c r="O44" t="n">
-        <v>1.000057324168965</v>
+        <v>1.000060731974877</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0105098516924473</v>
+        <v>0.00499393820859994</v>
       </c>
       <c r="Q44" t="n">
-        <v>188.3885320390082</v>
+        <v>95.36488505919357</v>
       </c>
       <c r="R44" t="n">
-        <v>291.9929771528053</v>
+        <v>140.463290579317</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[4, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>415</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>model_10_9_18</t>
+          <t>model_13_9_21</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9998547274585187</v>
+        <v>0.9999666429914501</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7207292005712203</v>
+        <v>0.6200271199224362</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9994839610083919</v>
+        <v>0.9999143415459179</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9997948718218834</v>
+        <v>0.9999430946148885</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9996091359398528</v>
+        <v>0.9999399102352392</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0001013230317805038</v>
+        <v>2.326546505579502e-05</v>
       </c>
       <c r="I45" t="n">
-        <v>0.194782605145823</v>
+        <v>0.2650191413411412</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0003604570515219385</v>
+        <v>0.0001092352369425928</v>
       </c>
       <c r="K45" t="n">
-        <v>9.525565931348651e-05</v>
+        <v>1.240788226370375e-05</v>
       </c>
       <c r="L45" t="n">
-        <v>0.0002278567306241799</v>
+        <v>6.082155960314828e-05</v>
       </c>
       <c r="M45" t="n">
-        <v>0.002848804037435473</v>
+        <v>0.002149660320870659</v>
       </c>
       <c r="N45" t="n">
-        <v>0.01006593422293747</v>
+        <v>0.004823428765494005</v>
       </c>
       <c r="O45" t="n">
-        <v>1.000057156409763</v>
+        <v>1.000061582169631</v>
       </c>
       <c r="P45" t="n">
-        <v>0.01049446188216431</v>
+        <v>0.00502877211391511</v>
       </c>
       <c r="Q45" t="n">
-        <v>188.3943936209094</v>
+        <v>95.33708096672824</v>
       </c>
       <c r="R45" t="n">
-        <v>291.9988387347065</v>
+        <v>140.4354864868517</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[4, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>416</v>
+        <v>4</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>model_10_9_19</t>
+          <t>model_13_9_20</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.999854692656029</v>
+        <v>0.9999659091092914</v>
       </c>
       <c r="D46" t="n">
-        <v>0.720595313506849</v>
+        <v>0.6198240197788389</v>
       </c>
       <c r="E46" t="n">
-        <v>0.999466008085379</v>
+        <v>0.9999156468101754</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9997842459584683</v>
+        <v>0.9999463109965003</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9995941489397034</v>
+        <v>0.9999410788552159</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0001013473054232298</v>
+        <v>2.377732479562865e-05</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1948759871651637</v>
+        <v>0.2651607973078813</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0003729973010004347</v>
+        <v>0.0001075707094657145</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0001001900063870504</v>
+        <v>1.170656929874645e-05</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0002365934992454596</v>
+        <v>5.96387077506077e-05</v>
       </c>
       <c r="M46" t="n">
-        <v>0.002805611729938771</v>
+        <v>0.002173700932980755</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01006713988296725</v>
+        <v>0.00487619983138803</v>
       </c>
       <c r="O46" t="n">
-        <v>1.000057170102546</v>
+        <v>1.000062937029</v>
       </c>
       <c r="P46" t="n">
-        <v>0.01049571886963762</v>
+        <v>0.005083789753335409</v>
       </c>
       <c r="Q46" t="n">
-        <v>188.39391454453</v>
+        <v>95.29355634222247</v>
       </c>
       <c r="R46" t="n">
-        <v>291.998359658327</v>
+        <v>140.3919618623459</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Hidden Size=[7, 7], regularizer=0.5, learning_rate=0.05</t>
+          <t>Hidden Size=[4, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>model_15_7_16</t>
+          <t>model_13_9_19</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.8346009946397621</v>
+        <v>0.9999647638552417</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3175671701132302</v>
+        <v>0.6195936582437525</v>
       </c>
       <c r="E47" t="n">
-        <v>-10.46650935349295</v>
+        <v>0.9999170120078602</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.938171018242795</v>
+        <v>0.9999468731460019</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.39983232327821</v>
+        <v>0.999941999477146</v>
       </c>
       <c r="H47" t="n">
-        <v>1.279576532419326</v>
+        <v>2.457610350013112e-05</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4759754500444304</v>
+        <v>0.2653214672383621</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4264866759692428</v>
+        <v>0.0001058297523800874</v>
       </c>
       <c r="K47" t="n">
-        <v>2.862870052383867</v>
+        <v>1.158399592863636e-05</v>
       </c>
       <c r="L47" t="n">
-        <v>1.644678282477699</v>
+        <v>5.870687415436188e-05</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8002961772715763</v>
+        <v>0.002258997990888177</v>
       </c>
       <c r="N47" t="n">
-        <v>1.131183686418491</v>
+        <v>0.004957429122048153</v>
       </c>
       <c r="O47" t="n">
-        <v>4.386955682411869</v>
+        <v>1.000065051344169</v>
       </c>
       <c r="P47" t="n">
-        <v>1.179340517822367</v>
+        <v>0.005168477143066746</v>
       </c>
       <c r="Q47" t="n">
-        <v>73.50694162170707</v>
+        <v>95.22747197915353</v>
       </c>
       <c r="R47" t="n">
-        <v>118.6053471418305</v>
+        <v>140.3258774992769</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>model_15_7_15</t>
+          <t>model_13_9_18</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.8346009946397621</v>
+        <v>0.9999631582245569</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3175671701132302</v>
+        <v>0.6192964319604273</v>
       </c>
       <c r="E48" t="n">
-        <v>-10.46650935349295</v>
+        <v>0.9999184296018105</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.938171018242795</v>
+        <v>0.9999453794844961</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.39983232327821</v>
+        <v>0.9999427316064827</v>
       </c>
       <c r="H48" t="n">
-        <v>1.279576532419326</v>
+        <v>2.569598043789267e-05</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4759754500444304</v>
+        <v>0.2655287732291864</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4264866759692428</v>
+        <v>0.000104021977389255</v>
       </c>
       <c r="K48" t="n">
-        <v>2.862870052383867</v>
+        <v>1.190967997539677e-05</v>
       </c>
       <c r="L48" t="n">
-        <v>1.644678282477699</v>
+        <v>5.796582868232586e-05</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8002961772715763</v>
+        <v>0.00242653232434956</v>
       </c>
       <c r="N48" t="n">
-        <v>1.131183686418491</v>
+        <v>0.005069120282444743</v>
       </c>
       <c r="O48" t="n">
-        <v>4.386955682411869</v>
+        <v>1.000068015585433</v>
       </c>
       <c r="P48" t="n">
-        <v>1.179340517822367</v>
+        <v>0.005284923227393994</v>
       </c>
       <c r="Q48" t="n">
-        <v>73.50694162170707</v>
+        <v>95.13835196298038</v>
       </c>
       <c r="R48" t="n">
-        <v>118.6053471418305</v>
+        <v>140.2367574831038</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 4], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>model_15_7_14</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.8346009946397621</v>
+        <v>0.9999574602193851</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3175671701132302</v>
+        <v>0.6567191289160758</v>
       </c>
       <c r="E49" t="n">
-        <v>-10.46650935349295</v>
+        <v>0.9997520290866009</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.938171018242795</v>
+        <v>0.9999136480980036</v>
       </c>
       <c r="G49" t="n">
-        <v>-1.39983232327821</v>
+        <v>0.9999189083979485</v>
       </c>
       <c r="H49" t="n">
-        <v>1.279576532419326</v>
+        <v>2.967015995742736e-05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4759754500444304</v>
+        <v>0.2394276182945732</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4264866759692428</v>
+        <v>7.564434727203212e-05</v>
       </c>
       <c r="K49" t="n">
-        <v>2.862870052383867</v>
+        <v>8.363032640369252e-05</v>
       </c>
       <c r="L49" t="n">
-        <v>1.644678282477699</v>
+        <v>7.963707869432894e-05</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8002961772715763</v>
+        <v>0.002976877572860683</v>
       </c>
       <c r="N49" t="n">
-        <v>1.131183686418491</v>
+        <v>0.00544703221556724</v>
       </c>
       <c r="O49" t="n">
-        <v>4.386955682411869</v>
+        <v>1.000029170135279</v>
       </c>
       <c r="P49" t="n">
-        <v>1.179340517822367</v>
+        <v>0.005678923653895065</v>
       </c>
       <c r="Q49" t="n">
-        <v>73.50694162170707</v>
+        <v>138.8507374649169</v>
       </c>
       <c r="R49" t="n">
-        <v>118.6053471418305</v>
+        <v>210.7644111321407</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>model_15_7_13</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.8346009946397621</v>
+        <v>0.9999573693606378</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3175671701132302</v>
+        <v>0.6575882494122899</v>
       </c>
       <c r="E50" t="n">
-        <v>-10.46650935349295</v>
+        <v>0.9997977194713409</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.938171018242795</v>
+        <v>0.9999345357328852</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.39983232327821</v>
+        <v>0.9999363038162304</v>
       </c>
       <c r="H50" t="n">
-        <v>1.279576532419326</v>
+        <v>2.973353107797185e-05</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4759754500444304</v>
+        <v>0.2388214340648418</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4264866759692428</v>
+        <v>6.170634429057764e-05</v>
       </c>
       <c r="K50" t="n">
-        <v>2.862870052383867</v>
+        <v>6.340101260102019e-05</v>
       </c>
       <c r="L50" t="n">
-        <v>1.644678282477699</v>
+        <v>6.255367844579891e-05</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8002961772715763</v>
+        <v>0.003032200598780673</v>
       </c>
       <c r="N50" t="n">
-        <v>1.131183686418491</v>
+        <v>0.005452846144718541</v>
       </c>
       <c r="O50" t="n">
-        <v>4.386955682411869</v>
+        <v>1.00002923243842</v>
       </c>
       <c r="P50" t="n">
-        <v>1.179340517822367</v>
+        <v>0.005684985094046828</v>
       </c>
       <c r="Q50" t="n">
-        <v>73.50694162170707</v>
+        <v>138.8464703129282</v>
       </c>
       <c r="R50" t="n">
-        <v>118.6053471418305</v>
+        <v>210.760143980152</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>model_15_7_23</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.8346009946397621</v>
+        <v>0.9999569884593845</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3175671701132302</v>
+        <v>0.6565503284178297</v>
       </c>
       <c r="E51" t="n">
-        <v>-10.46650935349295</v>
+        <v>0.9997428365230149</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.938171018242795</v>
+        <v>0.9999092919400085</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.39983232327821</v>
+        <v>0.9999153321880615</v>
       </c>
       <c r="H51" t="n">
-        <v>1.279576532419326</v>
+        <v>2.999919773046402e-05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4759754500444304</v>
+        <v>0.2395453513367156</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4264866759692428</v>
+        <v>7.844856919745401e-05</v>
       </c>
       <c r="K51" t="n">
-        <v>2.862870052383867</v>
+        <v>8.784919022233705e-05</v>
       </c>
       <c r="L51" t="n">
-        <v>1.644678282477699</v>
+        <v>8.314914284143894e-05</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8002961772715763</v>
+        <v>0.002967437159652965</v>
       </c>
       <c r="N51" t="n">
-        <v>1.131183686418491</v>
+        <v>0.005477152337708348</v>
       </c>
       <c r="O51" t="n">
-        <v>4.386955682411869</v>
+        <v>1.000029493627851</v>
       </c>
       <c r="P51" t="n">
-        <v>1.179340517822367</v>
+        <v>0.005710326051992967</v>
       </c>
       <c r="Q51" t="n">
-        <v>73.50694162170707</v>
+        <v>138.8286798379551</v>
       </c>
       <c r="R51" t="n">
-        <v>118.6053471418305</v>
+        <v>210.742353505179</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Hidden Size=[4, 4], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[6, 5], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_12</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.8373299699203969</v>
+        <v>0.9999564313457879</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7110100186810322</v>
+        <v>0.6563975913785524</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.660000410834247</v>
+        <v>0.9997344360418663</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.046506564858483</v>
+        <v>0.9999052764640607</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.9829999421786029</v>
+        <v>0.9999120475100742</v>
       </c>
       <c r="H52" t="n">
-        <v>1.281479906906125</v>
+        <v>3.038776695409173e-05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.201561429041229</v>
+        <v>0.2396518806211003</v>
       </c>
       <c r="J52" t="n">
-        <v>1.346419734370387</v>
+        <v>8.101116375558463e-05</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7419484016768835</v>
+        <v>9.17381093592735e-05</v>
       </c>
       <c r="L52" t="n">
-        <v>1.044184113435906</v>
+        <v>8.637490423644594e-05</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8029720724244975</v>
+        <v>0.002958935467667997</v>
       </c>
       <c r="N52" t="n">
-        <v>1.132024693593795</v>
+        <v>0.005512510041178313</v>
       </c>
       <c r="O52" t="n">
-        <v>2.259883407945415</v>
+        <v>1.000029875648603</v>
       </c>
       <c r="P52" t="n">
-        <v>1.180217328414249</v>
+        <v>0.005747189006100185</v>
       </c>
       <c r="Q52" t="n">
-        <v>117.5039688253126</v>
+        <v>138.8029408667275</v>
       </c>
       <c r="R52" t="n">
-        <v>189.4176424925364</v>
+        <v>210.7166145339514</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -3740,60 +3740,60 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.8373299699203969</v>
+        <v>0.9999564235667684</v>
       </c>
       <c r="D53" t="n">
-        <v>0.7110100186810322</v>
+        <v>0.6578631038210314</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.660000410834247</v>
+        <v>0.9998115737847747</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.046506564858483</v>
+        <v>0.9999406058152099</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.9829999421786029</v>
+        <v>0.9999414488615469</v>
       </c>
       <c r="H53" t="n">
-        <v>1.281479906906125</v>
+        <v>3.039319257569075e-05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.201561429041229</v>
+        <v>0.2386297317533936</v>
       </c>
       <c r="J53" t="n">
-        <v>1.346419734370387</v>
+        <v>5.748004015580068e-05</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7419484016768835</v>
+        <v>5.752224265636883e-05</v>
       </c>
       <c r="L53" t="n">
-        <v>1.044184113435906</v>
+        <v>5.75009187470556e-05</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8029720724244975</v>
+        <v>0.003052225960835972</v>
       </c>
       <c r="N53" t="n">
-        <v>1.132024693593795</v>
+        <v>0.005513002138190294</v>
       </c>
       <c r="O53" t="n">
-        <v>2.259883407945415</v>
+        <v>1.000029880982787</v>
       </c>
       <c r="P53" t="n">
-        <v>1.180217328414249</v>
+        <v>0.005747702052700748</v>
       </c>
       <c r="Q53" t="n">
-        <v>117.5039688253126</v>
+        <v>138.8025838061181</v>
       </c>
       <c r="R53" t="n">
-        <v>189.4176424925364</v>
+        <v>210.7162574733419</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -3803,60 +3803,60 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.8373299699203969</v>
+        <v>0.9999558223645125</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7110100186810322</v>
+        <v>0.6562594043269414</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.660000410834247</v>
+        <v>0.999726775156611</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.046506564858483</v>
+        <v>0.9999015786953107</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.9829999421786029</v>
+        <v>0.9999090346346348</v>
       </c>
       <c r="H54" t="n">
-        <v>1.281479906906125</v>
+        <v>3.081251225348904e-05</v>
       </c>
       <c r="I54" t="n">
-        <v>0.201561429041229</v>
+        <v>0.2397482617463925</v>
       </c>
       <c r="J54" t="n">
-        <v>1.346419734370387</v>
+        <v>8.334814214033041e-05</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7419484016768835</v>
+        <v>9.531933455953005e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>1.044184113435906</v>
+        <v>8.933373834993022e-05</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8029720724244975</v>
+        <v>0.002951232796481539</v>
       </c>
       <c r="N54" t="n">
-        <v>1.132024693593795</v>
+        <v>0.005550901931532301</v>
       </c>
       <c r="O54" t="n">
-        <v>2.259883407945415</v>
+        <v>1.000030293235763</v>
       </c>
       <c r="P54" t="n">
-        <v>1.180217328414249</v>
+        <v>0.005787215318708712</v>
       </c>
       <c r="Q54" t="n">
-        <v>117.5039688253126</v>
+        <v>138.7751794169646</v>
       </c>
       <c r="R54" t="n">
-        <v>189.4176424925364</v>
+        <v>210.6888530841884</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -3866,60 +3866,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.8373299699203969</v>
+        <v>0.9999551853541712</v>
       </c>
       <c r="D55" t="n">
-        <v>0.7110100186810322</v>
+        <v>0.6561345600269182</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.660000410834247</v>
+        <v>0.9997197876425613</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.046506564858483</v>
+        <v>0.999898185284497</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.9829999421786029</v>
+        <v>0.9999062761441266</v>
       </c>
       <c r="H55" t="n">
-        <v>1.281479906906125</v>
+        <v>3.125680694538847e-05</v>
       </c>
       <c r="I55" t="n">
-        <v>0.201561429041229</v>
+        <v>0.2398353367218138</v>
       </c>
       <c r="J55" t="n">
-        <v>1.346419734370387</v>
+        <v>8.547970641172764e-05</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7419484016768835</v>
+        <v>9.860579435273928e-05</v>
       </c>
       <c r="L55" t="n">
-        <v>1.044184113435906</v>
+        <v>9.204275038223347e-05</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8029720724244975</v>
+        <v>0.002944378941374085</v>
       </c>
       <c r="N55" t="n">
-        <v>1.132024693593795</v>
+        <v>0.005590778742303121</v>
       </c>
       <c r="O55" t="n">
-        <v>2.259883407945415</v>
+        <v>1.000030730042854</v>
       </c>
       <c r="P55" t="n">
-        <v>1.180217328414249</v>
+        <v>0.005828789767870424</v>
       </c>
       <c r="Q55" t="n">
-        <v>117.5039688253126</v>
+        <v>138.7465467664985</v>
       </c>
       <c r="R55" t="n">
-        <v>189.4176424925364</v>
+        <v>210.6602204337223</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -3929,60 +3929,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.8373299699203969</v>
+        <v>0.99995484929822</v>
       </c>
       <c r="D56" t="n">
-        <v>0.7110100186810322</v>
+        <v>0.658164988561047</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.660000410834247</v>
+        <v>0.999826440648875</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.046506564858483</v>
+        <v>0.9999469635739119</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.9829999421786029</v>
+        <v>0.9999468925642691</v>
       </c>
       <c r="H56" t="n">
-        <v>1.281479906906125</v>
+        <v>3.149119540916042e-05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.201561429041229</v>
+        <v>0.2384191766354425</v>
       </c>
       <c r="J56" t="n">
-        <v>1.346419734370387</v>
+        <v>5.29448540912904e-05</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7419484016768835</v>
+        <v>5.136486310659122e-05</v>
       </c>
       <c r="L56" t="n">
-        <v>1.044184113435906</v>
+        <v>5.215485859894082e-05</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8029720724244975</v>
+        <v>0.003074440426016214</v>
       </c>
       <c r="N56" t="n">
-        <v>1.132024693593795</v>
+        <v>0.0056117016500488</v>
       </c>
       <c r="O56" t="n">
-        <v>2.259883407945415</v>
+        <v>1.000030960481221</v>
       </c>
       <c r="P56" t="n">
-        <v>1.180217328414249</v>
+        <v>0.005850603407115226</v>
       </c>
       <c r="Q56" t="n">
-        <v>117.5039688253126</v>
+        <v>138.7316051240468</v>
       </c>
       <c r="R56" t="n">
-        <v>189.4176424925364</v>
+        <v>210.6452787912707</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -3992,60 +3992,60 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.8373299699203969</v>
+        <v>0.9999545408840995</v>
       </c>
       <c r="D57" t="n">
-        <v>0.7110100186810322</v>
+        <v>0.6560218008052869</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.660000410834247</v>
+        <v>0.9997134435881111</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.046506564858483</v>
+        <v>0.9998950725874636</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.9829999421786029</v>
+        <v>0.9999037560068764</v>
       </c>
       <c r="H57" t="n">
-        <v>1.281479906906125</v>
+        <v>3.170630456469058e-05</v>
       </c>
       <c r="I57" t="n">
-        <v>0.201561429041229</v>
+        <v>0.2399139827348895</v>
       </c>
       <c r="J57" t="n">
-        <v>1.346419734370387</v>
+        <v>8.741498120411876e-05</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7419484016768835</v>
+        <v>0.0001016203876955438</v>
       </c>
       <c r="L57" t="n">
-        <v>1.044184113435906</v>
+        <v>9.451768444983127e-05</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8029720724244975</v>
+        <v>0.002938210479804867</v>
       </c>
       <c r="N57" t="n">
-        <v>1.132024693593795</v>
+        <v>0.005630835156945245</v>
       </c>
       <c r="O57" t="n">
-        <v>2.259883407945415</v>
+        <v>1.000031171965189</v>
       </c>
       <c r="P57" t="n">
-        <v>1.180217328414249</v>
+        <v>0.005870551467012072</v>
       </c>
       <c r="Q57" t="n">
-        <v>117.5039688253126</v>
+        <v>138.7179900293771</v>
       </c>
       <c r="R57" t="n">
-        <v>189.4176424925364</v>
+        <v>210.631663696601</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -4055,60 +4055,60 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>177</v>
+        <v>58</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>model_5_5_20</t>
+          <t>model_5_8_14</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.999872460934557</v>
+        <v>0.9998909143649521</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4272465209132277</v>
+        <v>0.4535086543268019</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9999797698452421</v>
+        <v>0.9996734841827823</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9996650388518905</v>
+        <v>0.999518882003814</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9998672456542589</v>
+        <v>0.9996078159071105</v>
       </c>
       <c r="H58" t="n">
-        <v>8.8954489605355e-05</v>
+        <v>7.608380189430233e-05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3994775500734228</v>
+        <v>0.3811605374339124</v>
       </c>
       <c r="J58" t="n">
-        <v>5.900260647481696e-06</v>
+        <v>0.0002187017503041196</v>
       </c>
       <c r="K58" t="n">
-        <v>5.830575251664376e-05</v>
+        <v>0.0002423368321036702</v>
       </c>
       <c r="L58" t="n">
-        <v>3.210300658206273e-05</v>
+        <v>0.0002305263663528174</v>
       </c>
       <c r="M58" t="n">
-        <v>0.003378190416651791</v>
+        <v>0.003316647614037676</v>
       </c>
       <c r="N58" t="n">
-        <v>0.009431568777534044</v>
+        <v>0.008722602931138293</v>
       </c>
       <c r="O58" t="n">
-        <v>1.003060937570633</v>
+        <v>1.002618055241149</v>
       </c>
       <c r="P58" t="n">
-        <v>0.00983309018643256</v>
+        <v>0.009093942196194119</v>
       </c>
       <c r="Q58" t="n">
-        <v>68.65477134353272</v>
+        <v>68.96735033730626</v>
       </c>
       <c r="R58" t="n">
-        <v>99.12666696523773</v>
+        <v>99.43924595901127</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -4118,60 +4118,60 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>model_5_5_19</t>
+          <t>model_5_8_13</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.999872460934557</v>
+        <v>0.9998908399323955</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4272465209132277</v>
+        <v>0.4536032835411122</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9999797698452421</v>
+        <v>0.9996708793194273</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9996650388518905</v>
+        <v>0.9995267923062152</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9998672456542589</v>
+        <v>0.9996097330364301</v>
       </c>
       <c r="H59" t="n">
-        <v>8.8954489605355e-05</v>
+        <v>7.613571626317364e-05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3994775500734228</v>
+        <v>0.3810945365311185</v>
       </c>
       <c r="J59" t="n">
-        <v>5.900260647481696e-06</v>
+        <v>0.0002204464993943643</v>
       </c>
       <c r="K59" t="n">
-        <v>5.830575251664376e-05</v>
+        <v>0.0002383524506419746</v>
       </c>
       <c r="L59" t="n">
-        <v>3.210300658206273e-05</v>
+        <v>0.0002293994750181694</v>
       </c>
       <c r="M59" t="n">
-        <v>0.003378190416651791</v>
+        <v>0.003356964235021544</v>
       </c>
       <c r="N59" t="n">
-        <v>0.009431568777534044</v>
+        <v>0.008725578276720325</v>
       </c>
       <c r="O59" t="n">
-        <v>1.003060937570633</v>
+        <v>1.002619841622509</v>
       </c>
       <c r="P59" t="n">
-        <v>0.00983309018643256</v>
+        <v>0.009097044208397393</v>
       </c>
       <c r="Q59" t="n">
-        <v>68.65477134353272</v>
+        <v>68.96598613982324</v>
       </c>
       <c r="R59" t="n">
-        <v>99.12666696523773</v>
+        <v>99.43788176152826</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -4181,60 +4181,60 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>179</v>
+        <v>60</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>model_5_5_18</t>
+          <t>model_5_8_12</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.999872460934557</v>
+        <v>0.9998907162755313</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4272465209132277</v>
+        <v>0.4537620494267296</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9999797698452421</v>
+        <v>0.9996667772546468</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9996650388518905</v>
+        <v>0.9995371290950149</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9998672456542589</v>
+        <v>0.9996118354303267</v>
       </c>
       <c r="H60" t="n">
-        <v>8.8954489605355e-05</v>
+        <v>7.622196303947315e-05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3994775500734228</v>
+        <v>0.3809838023158976</v>
       </c>
       <c r="J60" t="n">
-        <v>5.900260647481696e-06</v>
+        <v>0.0002231940806754593</v>
       </c>
       <c r="K60" t="n">
-        <v>5.830575251664376e-05</v>
+        <v>0.000233145859594255</v>
       </c>
       <c r="L60" t="n">
-        <v>3.210300658206273e-05</v>
+        <v>0.000228163684902171</v>
       </c>
       <c r="M60" t="n">
-        <v>0.003378190416651791</v>
+        <v>0.003383005494644326</v>
       </c>
       <c r="N60" t="n">
-        <v>0.009431568777534044</v>
+        <v>0.008730519058994897</v>
       </c>
       <c r="O60" t="n">
-        <v>1.003060937570633</v>
+        <v>1.002622809387249</v>
       </c>
       <c r="P60" t="n">
-        <v>0.00983309018643256</v>
+        <v>0.009102195330002224</v>
       </c>
       <c r="Q60" t="n">
-        <v>68.65477134353272</v>
+        <v>68.96372181587431</v>
       </c>
       <c r="R60" t="n">
-        <v>99.12666696523773</v>
+        <v>99.43561743757932</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -4244,60 +4244,60 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>model_5_5_17</t>
+          <t>model_5_8_11</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.999872460934557</v>
+        <v>0.9998896072909489</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4272465209132277</v>
+        <v>0.4523008584219047</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9999797698452421</v>
+        <v>0.9996790052938079</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9996650388518905</v>
+        <v>0.9995163171601589</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9998672456542589</v>
+        <v>0.9996098746939122</v>
       </c>
       <c r="H61" t="n">
-        <v>8.8954489605355e-05</v>
+        <v>7.6995444930391e-05</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3994775500734228</v>
+        <v>0.382002937116663</v>
       </c>
       <c r="J61" t="n">
-        <v>5.900260647481696e-06</v>
+        <v>0.0002150036855205868</v>
       </c>
       <c r="K61" t="n">
-        <v>5.830575251664376e-05</v>
+        <v>0.0002436287315777015</v>
       </c>
       <c r="L61" t="n">
-        <v>3.210300658206273e-05</v>
+        <v>0.0002293162085491442</v>
       </c>
       <c r="M61" t="n">
-        <v>0.003378190416651791</v>
+        <v>0.003546165659585913</v>
       </c>
       <c r="N61" t="n">
-        <v>0.009431568777534044</v>
+        <v>0.008774704834374258</v>
       </c>
       <c r="O61" t="n">
-        <v>1.003060937570633</v>
+        <v>1.002649425017227</v>
       </c>
       <c r="P61" t="n">
-        <v>0.00983309018643256</v>
+        <v>0.00914826218531665</v>
       </c>
       <c r="Q61" t="n">
-        <v>68.65477134353272</v>
+        <v>68.94352858921718</v>
       </c>
       <c r="R61" t="n">
-        <v>99.12666696523773</v>
+        <v>99.4154242109222</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -4307,60 +4307,60 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>model_5_5_16</t>
+          <t>model_5_8_15</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.999872460934557</v>
+        <v>0.9998895154933252</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4272465209132277</v>
+        <v>0.453649656980632</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9999797698452421</v>
+        <v>0.9996670820790399</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9996650388518905</v>
+        <v>0.9995099011753937</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9998672456542589</v>
+        <v>0.9996003442169298</v>
       </c>
       <c r="H62" t="n">
-        <v>8.8954489605355e-05</v>
+        <v>7.705947088776548e-05</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3994775500734228</v>
+        <v>0.3810621925145664</v>
       </c>
       <c r="J62" t="n">
-        <v>5.900260647481696e-06</v>
+        <v>0.0002229899079377449</v>
       </c>
       <c r="K62" t="n">
-        <v>5.830575251664376e-05</v>
+        <v>0.0002468604323977454</v>
       </c>
       <c r="L62" t="n">
-        <v>3.210300658206273e-05</v>
+        <v>0.0002349182364441838</v>
       </c>
       <c r="M62" t="n">
-        <v>0.003378190416651791</v>
+        <v>0.003258912177623208</v>
       </c>
       <c r="N62" t="n">
-        <v>0.009431568777534044</v>
+        <v>0.008778352401662026</v>
       </c>
       <c r="O62" t="n">
-        <v>1.003060937570633</v>
+        <v>1.002651628160196</v>
       </c>
       <c r="P62" t="n">
-        <v>0.00983309018643256</v>
+        <v>0.009152065037095362</v>
       </c>
       <c r="Q62" t="n">
-        <v>68.65477134353272</v>
+        <v>68.94186617005397</v>
       </c>
       <c r="R62" t="n">
-        <v>99.12666696523773</v>
+        <v>99.41376179175899</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -4370,1572 +4370,1572 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>352</v>
+        <v>64</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>model_25_7_7</t>
+          <t>model_5_8_10</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.816952813625083</v>
+        <v>0.9998887278873293</v>
       </c>
       <c r="D63" t="n">
-        <v>0.6470604733949927</v>
+        <v>0.4523801133236187</v>
       </c>
       <c r="E63" t="n">
-        <v>-3.676586454247006</v>
+        <v>0.9996789306512722</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.9194854511108208</v>
+        <v>0.9995183653892991</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.9832083899478554</v>
+        <v>0.99961070974405</v>
       </c>
       <c r="H63" t="n">
-        <v>1.267267480842307</v>
+        <v>7.760880131546641e-05</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2461642269498667</v>
+        <v>0.3819476593136918</v>
       </c>
       <c r="J63" t="n">
-        <v>1.055938118674048</v>
+        <v>0.0002150536814238291</v>
       </c>
       <c r="K63" t="n">
-        <v>1.082396100049207</v>
+        <v>0.0002425970483623745</v>
       </c>
       <c r="L63" t="n">
-        <v>1.069167178217443</v>
+        <v>0.0002288253648931017</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8011946819012681</v>
+        <v>0.003626042394911187</v>
       </c>
       <c r="N63" t="n">
-        <v>1.125729754800106</v>
+        <v>0.008809585762989449</v>
       </c>
       <c r="O63" t="n">
-        <v>2.282554927264765</v>
+        <v>1.002670530704097</v>
       </c>
       <c r="P63" t="n">
-        <v>1.173654401043793</v>
+        <v>0.009184628067276466</v>
       </c>
       <c r="Q63" t="n">
-        <v>115.526274014825</v>
+        <v>68.92765943638562</v>
       </c>
       <c r="R63" t="n">
-        <v>186.2210718571806</v>
+        <v>99.39955505809064</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[4, 2], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>353</v>
+        <v>622</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>model_25_7_9</t>
+          <t>model_11_7_5</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-0.816952813625083</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6470604733949927</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E64" t="n">
-        <v>-3.676586454247006</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.9194854511108208</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.9832083899478554</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H64" t="n">
-        <v>1.267267480842307</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2461642269498667</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J64" t="n">
-        <v>1.055938118674048</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K64" t="n">
-        <v>1.082396100049207</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L64" t="n">
-        <v>1.069167178217443</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8011946819012681</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N64" t="n">
-        <v>1.125729754800106</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O64" t="n">
-        <v>2.282554927264765</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P64" t="n">
-        <v>1.173654401043793</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q64" t="n">
-        <v>115.526274014825</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R64" t="n">
-        <v>186.2210718571806</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>354</v>
+        <v>624</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>model_25_7_13</t>
+          <t>model_11_7_6</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.816952813625083</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D65" t="n">
-        <v>0.6470604733949927</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.676586454247006</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.9194854511108208</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.9832083899478554</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H65" t="n">
-        <v>1.267267480842307</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2461642269498667</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J65" t="n">
-        <v>1.055938118674048</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K65" t="n">
-        <v>1.082396100049207</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L65" t="n">
-        <v>1.069167178217443</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M65" t="n">
-        <v>0.8011946819012681</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N65" t="n">
-        <v>1.125729754800106</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O65" t="n">
-        <v>2.282554927264765</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P65" t="n">
-        <v>1.173654401043793</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q65" t="n">
-        <v>115.526274014825</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R65" t="n">
-        <v>186.2210718571806</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>355</v>
+        <v>625</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>model_25_7_5</t>
+          <t>model_11_7_19</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-0.816952813625083</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6470604733949927</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E66" t="n">
-        <v>-3.676586454247006</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9194854511108208</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.9832083899478554</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H66" t="n">
-        <v>1.267267480842307</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2461642269498667</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J66" t="n">
-        <v>1.055938118674048</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K66" t="n">
-        <v>1.082396100049207</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L66" t="n">
-        <v>1.069167178217443</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8011946819012681</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N66" t="n">
-        <v>1.125729754800106</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O66" t="n">
-        <v>2.282554927264765</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P66" t="n">
-        <v>1.173654401043793</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q66" t="n">
-        <v>115.526274014825</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R66" t="n">
-        <v>186.2210718571806</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>356</v>
+        <v>626</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>model_25_7_4</t>
+          <t>model_11_7_18</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.816952813625083</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6470604733949927</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E67" t="n">
-        <v>-3.676586454247006</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.9194854511108208</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.9832083899478554</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H67" t="n">
-        <v>1.267267480842307</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2461642269498667</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J67" t="n">
-        <v>1.055938118674048</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K67" t="n">
-        <v>1.082396100049207</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L67" t="n">
-        <v>1.069167178217443</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8011946819012681</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N67" t="n">
-        <v>1.125729754800106</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O67" t="n">
-        <v>2.282554927264765</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P67" t="n">
-        <v>1.173654401043793</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q67" t="n">
-        <v>115.526274014825</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R67" t="n">
-        <v>186.2210718571806</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>398</v>
+        <v>627</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>model_21_8_13</t>
+          <t>model_11_7_17</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.9998398885653129</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D68" t="n">
-        <v>0.6637862584611289</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9990900185086943</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9986179247604031</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9992019515708304</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0001116726934064415</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2344985175561355</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0002952084554723299</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0002531292133818757</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L68" t="n">
-        <v>0.0002741688344271028</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M68" t="n">
-        <v>0.003606057257069049</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N68" t="n">
-        <v>0.01056753014693791</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O68" t="n">
-        <v>1.000109790698071</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01101741178309616</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q68" t="n">
-        <v>136.1998766909195</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R68" t="n">
-        <v>208.1135503581433</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>399</v>
+        <v>628</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>model_21_8_15</t>
+          <t>model_11_7_16</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.9998392341330478</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D69" t="n">
-        <v>0.6641344474209454</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9989484684619525</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F69" t="n">
-        <v>0.998572398629435</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9991229837603802</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0001121291393426277</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2342556667002108</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0003411289176684513</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0002614673945388057</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L69" t="n">
-        <v>0.0003012981561036285</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M69" t="n">
-        <v>0.003357003472712287</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N69" t="n">
-        <v>0.01058910474698535</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O69" t="n">
-        <v>1.000110239451624</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0110399048585332</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q69" t="n">
-        <v>136.1917186421053</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R69" t="n">
-        <v>208.1053923093292</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>400</v>
+        <v>629</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>model_21_8_12</t>
+          <t>model_11_7_15</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.9998387056214627</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D70" t="n">
-        <v>0.6635815203682718</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9991670849901146</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9986446191597441</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9992454486291896</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0001124977595621553</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2346413159410039</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0002702072030664978</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0002482400929394463</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L70" t="n">
-        <v>0.0002592254583668624</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M70" t="n">
-        <v>0.003752057778046954</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N70" t="n">
-        <v>0.01060649610201952</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O70" t="n">
-        <v>1.000110601859568</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P70" t="n">
-        <v>0.01105803659955624</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q70" t="n">
-        <v>136.1851545030423</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R70" t="n">
-        <v>208.0988281702662</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>401</v>
+        <v>630</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>model_21_8_16</t>
+          <t>model_11_7_14</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.9998379180824891</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D71" t="n">
-        <v>0.6642822003049231</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9988842663762694</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9985529957962027</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9990874989459877</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0001130470432439286</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I71" t="n">
-        <v>0.234152613707496</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0003619568122286402</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K71" t="n">
-        <v>0.000265021053393808</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0003134889328112241</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M71" t="n">
-        <v>0.003251087154050901</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N71" t="n">
-        <v>0.01063235831055033</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O71" t="n">
-        <v>1.000111141886293</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P71" t="n">
-        <v>0.01108499981584635</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q71" t="n">
-        <v>136.175413027985</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R71" t="n">
-        <v>208.0890866952089</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>402</v>
+        <v>631</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>model_21_8_17</t>
+          <t>model_11_7_13</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.9998361985165094</v>
+        <v>0.9997153476427126</v>
       </c>
       <c r="D72" t="n">
-        <v>0.6644145587246948</v>
+        <v>0.6194184338783597</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9988244791849437</v>
+        <v>0.9999999999998201</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9985355482141247</v>
+        <v>0.9999999999997881</v>
       </c>
       <c r="G72" t="n">
-        <v>0.999054619799382</v>
+        <v>0.9999999999998154</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0001142463864690235</v>
+        <v>0.0001985360726102891</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2340602978697184</v>
+        <v>0.2654436807259377</v>
       </c>
       <c r="J72" t="n">
-        <v>0.0003813524643126919</v>
+        <v>1.039739434322628e-13</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0002682166049819573</v>
+        <v>1.09105680460183e-13</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0003247845346473246</v>
+        <v>1.012219485077124e-13</v>
       </c>
       <c r="M72" t="n">
-        <v>0.003155830815393289</v>
+        <v>0.00461585434007414</v>
       </c>
       <c r="N72" t="n">
-        <v>0.01068861012802991</v>
+        <v>0.01409028291448717</v>
       </c>
       <c r="O72" t="n">
-        <v>1.000112321017251</v>
+        <v>1.000525512044223</v>
       </c>
       <c r="P72" t="n">
-        <v>0.01114364638965336</v>
+        <v>0.01469013542906352</v>
       </c>
       <c r="Q72" t="n">
-        <v>136.1543063139401</v>
+        <v>91.04907949670155</v>
       </c>
       <c r="R72" t="n">
-        <v>208.0679799811639</v>
+        <v>136.147485016825</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Hidden Size=[6, 5], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[5, 3], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>421</v>
+        <v>24</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>model_9_3_14</t>
+          <t>model_27_4_16</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.9998134323178985</v>
+        <v>0.9999999385584991</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4302377896119317</v>
+        <v>0.7057082380769653</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9995802058148181</v>
+        <v>0.9999998646642948</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9991552396858996</v>
+        <v>0.9999994750845159</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9995906720845834</v>
+        <v>0.9999997630701901</v>
       </c>
       <c r="H73" t="n">
-        <v>0.000130125094460561</v>
+        <v>4.285351575506226e-08</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3973912341713791</v>
+        <v>0.205259254378085</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0002197337088028713</v>
+        <v>9.449011843930362e-08</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0003763041166958021</v>
+        <v>1.307755267672092e-07</v>
       </c>
       <c r="L73" t="n">
-        <v>0.0002980189127493367</v>
+        <v>1.126328226032564e-07</v>
       </c>
       <c r="M73" t="n">
-        <v>0.004622603213278625</v>
+        <v>7.513299076503403e-05</v>
       </c>
       <c r="N73" t="n">
-        <v>0.01140723868692862</v>
+        <v>0.0002070109073335564</v>
       </c>
       <c r="O73" t="n">
-        <v>1.00034443264388</v>
+        <v>1.000000024173705</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01189286845407058</v>
+        <v>0.0002158237902303995</v>
       </c>
       <c r="Q73" t="n">
-        <v>91.89402861021541</v>
+        <v>203.9309562946179</v>
       </c>
       <c r="R73" t="n">
-        <v>136.9924341303388</v>
+        <v>307.5354014084149</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>423</v>
+        <v>25</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>model_9_3_15</t>
+          <t>model_27_4_15</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.999809661832631</v>
+        <v>0.9999999385683593</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4303190163193522</v>
+        <v>0.7057191589754501</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9995100051356541</v>
+        <v>0.999999871314962</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9991081005998786</v>
+        <v>0.9999994971458266</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9995510167000442</v>
+        <v>0.9999997737349279</v>
       </c>
       <c r="H74" t="n">
-        <v>0.000132754889428691</v>
+        <v>4.28466386052853e-08</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3973345810959013</v>
+        <v>0.2052516373946346</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0002564789905092275</v>
+        <v>8.984668506303143e-08</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0003973025369942908</v>
+        <v>1.252792523918206e-07</v>
       </c>
       <c r="L74" t="n">
-        <v>0.0003268907637517591</v>
+        <v>1.07562968727426e-07</v>
       </c>
       <c r="M74" t="n">
-        <v>0.004550843876384613</v>
+        <v>7.549963804978497e-05</v>
       </c>
       <c r="N74" t="n">
-        <v>0.01152193080298137</v>
+        <v>0.0002069942960694456</v>
       </c>
       <c r="O74" t="n">
-        <v>1.000351393539758</v>
+        <v>1.000000024169826</v>
       </c>
       <c r="P74" t="n">
-        <v>0.01201244325094911</v>
+        <v>0.0002158064717903855</v>
       </c>
       <c r="Q74" t="n">
-        <v>91.85401213333191</v>
+        <v>203.9312772811945</v>
       </c>
       <c r="R74" t="n">
-        <v>136.9524176534553</v>
+        <v>307.5357223949916</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>424</v>
+        <v>26</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>model_9_3_11</t>
+          <t>model_27_4_17</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.9998094816227628</v>
+        <v>0.9999999382492674</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4298529531088932</v>
+        <v>0.7056984676739759</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9997790550607649</v>
+        <v>0.9999998585188015</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9993134339569143</v>
+        <v>0.9999994545380037</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9997105471371779</v>
+        <v>0.9999997531733557</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0001328805801477082</v>
+        <v>4.306919517542173e-08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3976596455368723</v>
+        <v>0.2052660689270872</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0001156496508361982</v>
+        <v>9.878084415067396e-08</v>
       </c>
       <c r="K75" t="n">
-        <v>0.0003058354234737572</v>
+        <v>1.358944098029877e-07</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0002107416186912952</v>
+        <v>1.173376269768308e-07</v>
       </c>
       <c r="M75" t="n">
-        <v>0.004967281549311515</v>
+        <v>7.482751101777355e-05</v>
       </c>
       <c r="N75" t="n">
-        <v>0.01152738392471198</v>
+        <v>0.0002075311908495244</v>
       </c>
       <c r="O75" t="n">
-        <v>1.000351726234899</v>
+        <v>1.00000002429537</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01201812852336131</v>
+        <v>0.0002163662232927777</v>
       </c>
       <c r="Q75" t="n">
-        <v>91.85211945343343</v>
+        <v>203.9209156489717</v>
       </c>
       <c r="R75" t="n">
-        <v>136.9505249735569</v>
+        <v>307.5253607627688</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>425</v>
+        <v>27</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>model_9_3_16</t>
+          <t>model_27_4_14</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.9998044405251622</v>
+        <v>0.9999999381925098</v>
       </c>
       <c r="D76" t="n">
-        <v>0.4303838888760601</v>
+        <v>0.7057314078782759</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9994404095602268</v>
+        <v>0.9999998783689968</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9990636549725834</v>
+        <v>0.9999995204119411</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9995124046475837</v>
+        <v>0.9999997850115783</v>
       </c>
       <c r="H76" t="n">
-        <v>0.000136396587282909</v>
+        <v>4.310878182859926e-08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3972893345265361</v>
+        <v>0.2052430941698954</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0002929075415580569</v>
+        <v>8.492162420976703e-08</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0004171011381372948</v>
+        <v>1.194828176094378e-07</v>
       </c>
       <c r="L76" t="n">
-        <v>0.0003550029971468072</v>
+        <v>1.022022209096024e-07</v>
       </c>
       <c r="M76" t="n">
-        <v>0.004487018970611979</v>
+        <v>7.594173895939373e-05</v>
       </c>
       <c r="N76" t="n">
-        <v>0.01167889495127467</v>
+        <v>0.0002076265441329679</v>
       </c>
       <c r="O76" t="n">
-        <v>1.000361032876624</v>
+        <v>1.000000024317701</v>
       </c>
       <c r="P76" t="n">
-        <v>0.01217608968799583</v>
+        <v>0.0002164656359629059</v>
       </c>
       <c r="Q76" t="n">
-        <v>91.79988766557588</v>
+        <v>203.919078211736</v>
       </c>
       <c r="R76" t="n">
-        <v>136.8982931856993</v>
+        <v>307.5235233255331</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>426</v>
+        <v>28</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>model_9_3_10</t>
+          <t>model_27_4_18</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.999799585827322</v>
+        <v>0.9999999378320265</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4296439191815783</v>
+        <v>0.7056896236977865</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9998320119833325</v>
+        <v>0.9999998530991067</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9993699555391964</v>
+        <v>0.9999994363286121</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9997468735486883</v>
+        <v>0.9999997444219169</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0001397825864437454</v>
+        <v>4.336020761266352e-08</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3978054401312572</v>
+        <v>0.2052722373225138</v>
       </c>
       <c r="J77" t="n">
-        <v>8.79303030860066e-05</v>
+        <v>1.025648241874107e-07</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0002806575076319213</v>
+        <v>1.404310311185613e-07</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0001842934893195095</v>
+        <v>1.21497927652986e-07</v>
       </c>
       <c r="M77" t="n">
-        <v>0.005152695071399611</v>
+        <v>7.453178331519057e-05</v>
       </c>
       <c r="N77" t="n">
-        <v>0.01182296859691953</v>
+        <v>0.0002082311398726509</v>
       </c>
       <c r="O77" t="n">
-        <v>1.000369995395713</v>
+        <v>1.000000024459531</v>
       </c>
       <c r="P77" t="n">
-        <v>0.01232629684700936</v>
+        <v>0.0002170959705949129</v>
       </c>
       <c r="Q77" t="n">
-        <v>91.75084459282219</v>
+        <v>203.9074473834231</v>
       </c>
       <c r="R77" t="n">
-        <v>136.8492501129456</v>
+        <v>307.5118924972202</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 3], regularizer=0.5, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>505</v>
+        <v>29</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>model_27_9_5</t>
+          <t>model_27_4_13</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.9997411850485044</v>
+        <v>0.9999999374523139</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6219949369035224</v>
+        <v>0.705744903797787</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9992653203410173</v>
+        <v>0.999999886105513</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9995986051247342</v>
+        <v>0.9999995472619336</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9994485888870477</v>
+        <v>0.9999997977285108</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0001805152941378563</v>
+        <v>4.362504520922011e-08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2636466508451418</v>
+        <v>0.2052336811902121</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0006857312812995867</v>
+        <v>7.952006123070758e-08</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0003572465882807641</v>
+        <v>1.127935085246325e-07</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0005214889347901754</v>
+        <v>9.615678487767001e-08</v>
       </c>
       <c r="M78" t="n">
-        <v>0.006641632352243322</v>
+        <v>7.634680707299703e-05</v>
       </c>
       <c r="N78" t="n">
-        <v>0.01343559801936097</v>
+        <v>0.0002088660939674511</v>
       </c>
       <c r="O78" t="n">
-        <v>1.000182692906938</v>
+        <v>1.000000024608926</v>
       </c>
       <c r="P78" t="n">
-        <v>0.01400757924256723</v>
+        <v>0.0002177579560000649</v>
       </c>
       <c r="Q78" t="n">
-        <v>133.2393901034304</v>
+        <v>203.8952688402197</v>
       </c>
       <c r="R78" t="n">
-        <v>203.9341879457861</v>
+        <v>307.4997139540168</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>506</v>
+        <v>30</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>model_27_9_6</t>
+          <t>model_27_4_19</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.9997409171345143</v>
+        <v>0.9999999372815699</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6221606675075196</v>
+        <v>0.7056815214005194</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9992240690341431</v>
+        <v>0.9999998480909692</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9996223655053467</v>
+        <v>0.9999994191351215</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9994394125265013</v>
+        <v>0.9999997362389054</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0001807021557254221</v>
+        <v>4.374413377982379e-08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2635310589577515</v>
+        <v>0.2052778884202032</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0007242342004593935</v>
+        <v>1.060614586980932e-07</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0003360995447256816</v>
+        <v>1.447145545973353e-07</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0005301673425592381</v>
+        <v>1.253880066477142e-07</v>
       </c>
       <c r="M79" t="n">
-        <v>0.006522059901552027</v>
+        <v>7.421413569706764e-05</v>
       </c>
       <c r="N79" t="n">
-        <v>0.01344255019426828</v>
+        <v>0.000209150983215054</v>
       </c>
       <c r="O79" t="n">
-        <v>1.000182882022696</v>
+        <v>1.000000024676104</v>
       </c>
       <c r="P79" t="n">
-        <v>0.01401482738595333</v>
+        <v>0.0002180549735727403</v>
       </c>
       <c r="Q79" t="n">
-        <v>133.2373208611576</v>
+        <v>203.8898166363312</v>
       </c>
       <c r="R79" t="n">
-        <v>203.9321187035132</v>
+        <v>307.4942617501282</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>507</v>
+        <v>31</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>model_27_9_4</t>
+          <t>model_27_4_20</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.9997402224432987</v>
+        <v>0.9999999366025285</v>
       </c>
       <c r="D80" t="n">
-        <v>0.6218081742063298</v>
+        <v>0.7056744001601287</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9993078854902009</v>
+        <v>0.9999998432657016</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9995716908384122</v>
+        <v>0.9999994036727673</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9994569290538777</v>
+        <v>0.9999997286438039</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0001811866810142119</v>
+        <v>4.421774377888388e-08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.263776911956499</v>
+        <v>0.2052828552615558</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0006460020551920201</v>
+        <v>1.094304153178402e-07</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0003812006483772317</v>
+        <v>1.485667890537366e-07</v>
       </c>
       <c r="L80" t="n">
-        <v>0.000513601344906631</v>
+        <v>1.289986021857884e-07</v>
       </c>
       <c r="M80" t="n">
-        <v>0.006781215061954402</v>
+        <v>7.406036674991519e-05</v>
       </c>
       <c r="N80" t="n">
-        <v>0.01346056020432329</v>
+        <v>0.0002102801554566761</v>
       </c>
       <c r="O80" t="n">
-        <v>1.000183372392966</v>
+        <v>1.000000024943267</v>
       </c>
       <c r="P80" t="n">
-        <v>0.01403360411942225</v>
+        <v>0.0002192322170143971</v>
       </c>
       <c r="Q80" t="n">
-        <v>133.2319653427871</v>
+        <v>203.8682793709165</v>
       </c>
       <c r="R80" t="n">
-        <v>203.9267631851427</v>
+        <v>307.4727244847136</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[21], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>508</v>
+        <v>47</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>model_27_9_7</t>
+          <t>model_9_4_0</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.9997397410301249</v>
+        <v>0.9999998397209885</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6223076943399952</v>
+        <v>0.6981931147042963</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9991845387547407</v>
+        <v>0.9999999554912982</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9996433391936241</v>
+        <v>0.9999989519277426</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9994297751760323</v>
+        <v>0.9999996868008874</v>
       </c>
       <c r="H81" t="n">
-        <v>0.000181522451572265</v>
+        <v>1.117895729583592e-07</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2634285123631397</v>
+        <v>0.2105008167308794</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0007611307564117458</v>
+        <v>5.848004065742871e-08</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0003174326930977737</v>
+        <v>5.048460874283584e-07</v>
       </c>
       <c r="L81" t="n">
-        <v>0.0005392817247547597</v>
+        <v>2.816630640428936e-07</v>
       </c>
       <c r="M81" t="n">
-        <v>0.006411802296011761</v>
+        <v>8.806399497521135e-05</v>
       </c>
       <c r="N81" t="n">
-        <v>0.01347302681554019</v>
+        <v>0.0003343494772814206</v>
       </c>
       <c r="O81" t="n">
-        <v>1.00018371221403</v>
+        <v>1.000000085482139</v>
       </c>
       <c r="P81" t="n">
-        <v>0.01404660146008809</v>
+        <v>0.0003485834267281232</v>
       </c>
       <c r="Q81" t="n">
-        <v>133.2282624235739</v>
+        <v>170.0132950914117</v>
       </c>
       <c r="R81" t="n">
-        <v>203.9230602659295</v>
+        <v>254.1157270073175</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Hidden Size=[5, 6], regularizer=0.3, learning_rate=0.1</t>
+          <t>Hidden Size=[17], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>model_12_3_24</t>
+          <t>model_9_4_2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.9999999996019001</v>
+        <v>0.9999998385059362</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6454956274887458</v>
+        <v>0.698196519331113</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9999999981292351</v>
+        <v>0.9999999851701499</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9999999999998979</v>
+        <v>0.9999987647803507</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9999999991112503</v>
+        <v>0.999999658361317</v>
       </c>
       <c r="H82" t="n">
-        <v>2.776621751554447e-10</v>
+        <v>1.126370337873882e-07</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2472556577865098</v>
+        <v>0.2104984421106819</v>
       </c>
       <c r="J82" t="n">
-        <v>1.017791267645133e-09</v>
+        <v>1.948495923285882e-08</v>
       </c>
       <c r="K82" t="n">
-        <v>5.994109880543635e-14</v>
+        <v>5.949931435476255e-07</v>
       </c>
       <c r="L82" t="n">
-        <v>5.08926079976734e-10</v>
+        <v>3.072390513902421e-07</v>
       </c>
       <c r="M82" t="n">
-        <v>4.293428399004596e-06</v>
+        <v>8.560788063684639e-05</v>
       </c>
       <c r="N82" t="n">
-        <v>1.666319822709448e-05</v>
+        <v>0.0003356144123654231</v>
       </c>
       <c r="O82" t="n">
-        <v>1.00000000021232</v>
+        <v>1.000000086130167</v>
       </c>
       <c r="P82" t="n">
-        <v>1.737258507319747e-05</v>
+        <v>0.0003499022127174283</v>
       </c>
       <c r="Q82" t="n">
-        <v>182.0092318769428</v>
+        <v>169.9981905568942</v>
       </c>
       <c r="R82" t="n">
-        <v>266.1116637928487</v>
+        <v>254.1006224728</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
+          <t>Hidden Size=[17], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>model_12_3_11</t>
+          <t>model_9_4_3</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.9999999996019001</v>
+        <v>0.9999998301921935</v>
       </c>
       <c r="D83" t="n">
-        <v>0.6454956274887458</v>
+        <v>0.6982018232052047</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9999999981292351</v>
+        <v>0.9999999814186387</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9999999999998979</v>
+        <v>0.9999986654491457</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9999999991112503</v>
+        <v>0.9999996290188297</v>
       </c>
       <c r="H83" t="n">
-        <v>2.776621751554447e-10</v>
+        <v>1.184356079602757e-07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2472556577865098</v>
+        <v>0.2104947428252031</v>
       </c>
       <c r="J83" t="n">
-        <v>1.017791267645133e-09</v>
+        <v>2.441407456514815e-08</v>
       </c>
       <c r="K83" t="n">
-        <v>5.994109880543635e-14</v>
+        <v>6.428400069802995e-07</v>
       </c>
       <c r="L83" t="n">
-        <v>5.08926079976734e-10</v>
+        <v>3.336270407727238e-07</v>
       </c>
       <c r="M83" t="n">
-        <v>4.293428399004596e-06</v>
+        <v>9.188573396665513e-05</v>
       </c>
       <c r="N83" t="n">
-        <v>1.666319822709448e-05</v>
+        <v>0.0003441447485583293</v>
       </c>
       <c r="O83" t="n">
-        <v>1.00000000021232</v>
+        <v>1.000000090564164</v>
       </c>
       <c r="P83" t="n">
-        <v>1.737258507319747e-05</v>
+        <v>0.0003587957029822967</v>
       </c>
       <c r="Q83" t="n">
-        <v>182.0092318769428</v>
+        <v>169.8977928336057</v>
       </c>
       <c r="R83" t="n">
-        <v>266.1116637928487</v>
+        <v>254.0002247495115</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
+          <t>Hidden Size=[17], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>model_12_3_1</t>
+          <t>model_9_4_4</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.9999999996019001</v>
+        <v>0.9999998186744813</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6454956274887458</v>
+        <v>0.6982056648840023</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9999999981292351</v>
+        <v>0.9999999690427043</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9999999999998979</v>
+        <v>0.9999985663662679</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9999999991112503</v>
+        <v>0.9999995934426604</v>
       </c>
       <c r="H84" t="n">
-        <v>2.776621751554447e-10</v>
+        <v>1.264688502378577e-07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2472556577865098</v>
+        <v>0.2104920633749855</v>
       </c>
       <c r="J84" t="n">
-        <v>1.017791267645133e-09</v>
+        <v>4.067483072396096e-08</v>
       </c>
       <c r="K84" t="n">
-        <v>5.994109880543635e-14</v>
+        <v>6.905672536311155e-07</v>
       </c>
       <c r="L84" t="n">
-        <v>5.08926079976734e-10</v>
+        <v>3.656210421775382e-07</v>
       </c>
       <c r="M84" t="n">
-        <v>4.293428399004596e-06</v>
+        <v>9.904926035750645e-05</v>
       </c>
       <c r="N84" t="n">
-        <v>1.666319822709448e-05</v>
+        <v>0.0003556245917225885</v>
       </c>
       <c r="O84" t="n">
-        <v>1.00000000021232</v>
+        <v>1.000000096706943</v>
       </c>
       <c r="P84" t="n">
-        <v>1.737258507319747e-05</v>
+        <v>0.0003707642668366099</v>
       </c>
       <c r="Q84" t="n">
-        <v>182.0092318769428</v>
+        <v>169.7665396045613</v>
       </c>
       <c r="R84" t="n">
-        <v>266.1116637928487</v>
+        <v>253.8689715204671</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
+          <t>Hidden Size=[17], regularizer=0.5, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>model_12_3_2</t>
+          <t>model_7_9_19</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.9999999996019001</v>
+        <v>0.9999997998050718</v>
       </c>
       <c r="D85" t="n">
-        <v>0.6454956274887458</v>
+        <v>0.7442000061820437</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9999999981292351</v>
+        <v>0.9999997282772525</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9999999999998979</v>
+        <v>0.9999988674743444</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9999999991112503</v>
+        <v>0.9999994618086228</v>
       </c>
       <c r="H85" t="n">
-        <v>2.776621751554447e-10</v>
+        <v>1.396296703302e-07</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2472556577865098</v>
+        <v>0.1784124559175529</v>
       </c>
       <c r="J85" t="n">
-        <v>1.017791267645133e-09</v>
+        <v>1.056485003717868e-07</v>
       </c>
       <c r="K85" t="n">
-        <v>5.994109880543635e-14</v>
+        <v>7.596010178685389e-07</v>
       </c>
       <c r="L85" t="n">
-        <v>5.08926079976734e-10</v>
+        <v>4.326247591201629e-07</v>
       </c>
       <c r="M85" t="n">
-        <v>4.293428399004596e-06</v>
+        <v>6.610117779440543e-05</v>
       </c>
       <c r="N85" t="n">
-        <v>1.666319822709448e-05</v>
+        <v>0.0003736705371449561</v>
       </c>
       <c r="O85" t="n">
-        <v>1.00000000021232</v>
+        <v>1.000000117187275</v>
       </c>
       <c r="P85" t="n">
-        <v>1.737258507319747e-05</v>
+        <v>0.0003895784655158645</v>
       </c>
       <c r="Q85" t="n">
-        <v>182.0092318769428</v>
+        <v>161.5685442620385</v>
       </c>
       <c r="R85" t="n">
-        <v>266.1116637928487</v>
+        <v>240.7954728784715</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
+          <t>Hidden Size=[16], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>model_12_3_3</t>
+          <t>model_7_9_20</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.9999999996019001</v>
+        <v>0.9999997998050718</v>
       </c>
       <c r="D86" t="n">
-        <v>0.6454956274887458</v>
+        <v>0.7442000061820437</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9999999981292351</v>
+        <v>0.9999997282772525</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9999999999998979</v>
+        <v>0.9999988674743444</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9999999991112503</v>
+        <v>0.9999994618086228</v>
       </c>
       <c r="H86" t="n">
-        <v>2.776621751554447e-10</v>
+        <v>1.396296703302e-07</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2472556577865098</v>
+        <v>0.1784124559175529</v>
       </c>
       <c r="J86" t="n">
-        <v>1.017791267645133e-09</v>
+        <v>1.056485003717868e-07</v>
       </c>
       <c r="K86" t="n">
-        <v>5.994109880543635e-14</v>
+        <v>7.596010178685389e-07</v>
       </c>
       <c r="L86" t="n">
-        <v>5.08926079976734e-10</v>
+        <v>4.326247591201629e-07</v>
       </c>
       <c r="M86" t="n">
-        <v>4.293428399004596e-06</v>
+        <v>6.610117779440543e-05</v>
       </c>
       <c r="N86" t="n">
-        <v>1.666319822709448e-05</v>
+        <v>0.0003736705371449561</v>
       </c>
       <c r="O86" t="n">
-        <v>1.00000000021232</v>
+        <v>1.000000117187275</v>
       </c>
       <c r="P86" t="n">
-        <v>1.737258507319747e-05</v>
+        <v>0.0003895784655158645</v>
       </c>
       <c r="Q86" t="n">
-        <v>182.0092318769428</v>
+        <v>161.5685442620385</v>
       </c>
       <c r="R86" t="n">
-        <v>266.1116637928487</v>
+        <v>240.7954728784715</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Hidden Size=[17], regularizer=0.3, learning_rate=0.5</t>
+          <t>Hidden Size=[16], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>229</v>
+        <v>61</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>model_7_7_6</t>
+          <t>model_7_9_17</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.9999999993247947</v>
+        <v>0.9999997998050718</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6648820990179763</v>
+        <v>0.7442000061820437</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9999999990045999</v>
+        <v>0.9999997282772525</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9999999982719161</v>
+        <v>0.9999988674743444</v>
       </c>
       <c r="G87" t="n">
-        <v>0.9999999987079971</v>
+        <v>0.9999994618086228</v>
       </c>
       <c r="H87" t="n">
-        <v>4.709345124382253e-10</v>
+        <v>1.396296703302e-07</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2337342032099032</v>
+        <v>0.1784124559175529</v>
       </c>
       <c r="J87" t="n">
-        <v>5.682629716495394e-10</v>
+        <v>1.056485003717868e-07</v>
       </c>
       <c r="K87" t="n">
-        <v>6.761849205696576e-10</v>
+        <v>7.596010178685389e-07</v>
       </c>
       <c r="L87" t="n">
-        <v>6.226291189178326e-10</v>
+        <v>4.326247591201629e-07</v>
       </c>
       <c r="M87" t="n">
-        <v>6.032537760572896e-06</v>
+        <v>6.610117779440543e-05</v>
       </c>
       <c r="N87" t="n">
-        <v>2.17010256079805e-05</v>
+        <v>0.0003736705371449561</v>
       </c>
       <c r="O87" t="n">
-        <v>1.000000000395242</v>
+        <v>1.000000117187275</v>
       </c>
       <c r="P87" t="n">
-        <v>2.262488319542814e-05</v>
+        <v>0.0003895784655158645</v>
       </c>
       <c r="Q87" t="n">
-        <v>172.9526041419766</v>
+        <v>161.5685442620385</v>
       </c>
       <c r="R87" t="n">
-        <v>252.1795327584096</v>
+        <v>240.7954728784715</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -5945,60 +5945,60 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>model_7_7_5</t>
+          <t>model_7_9_21</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.9999999992733436</v>
+        <v>0.9999997998050718</v>
       </c>
       <c r="D88" t="n">
-        <v>0.6648944639332407</v>
+        <v>0.7442000061820437</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9999999991960528</v>
+        <v>0.9999997282772525</v>
       </c>
       <c r="F88" t="n">
-        <v>0.999999998454481</v>
+        <v>0.9999988674743444</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9999999988963567</v>
+        <v>0.9999994618086228</v>
       </c>
       <c r="H88" t="n">
-        <v>5.068200144513984e-10</v>
+        <v>1.396296703302e-07</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2337255790701345</v>
+        <v>0.1784124559175529</v>
       </c>
       <c r="J88" t="n">
-        <v>4.589646316336132e-10</v>
+        <v>1.056485003717868e-07</v>
       </c>
       <c r="K88" t="n">
-        <v>6.047488047201463e-10</v>
+        <v>7.596010178685389e-07</v>
       </c>
       <c r="L88" t="n">
-        <v>5.318567181768798e-10</v>
+        <v>4.326247591201629e-07</v>
       </c>
       <c r="M88" t="n">
-        <v>6.233719184441904e-06</v>
+        <v>6.610117779440543e-05</v>
       </c>
       <c r="N88" t="n">
-        <v>2.251266342420191e-05</v>
+        <v>0.0003736705371449561</v>
       </c>
       <c r="O88" t="n">
-        <v>1.00000000042536</v>
+        <v>1.000000117187275</v>
       </c>
       <c r="P88" t="n">
-        <v>2.3471074113808e-05</v>
+        <v>0.0003895784655158645</v>
       </c>
       <c r="Q88" t="n">
-        <v>172.8057303528944</v>
+        <v>161.5685442620385</v>
       </c>
       <c r="R88" t="n">
-        <v>252.0326589693275</v>
+        <v>240.7954728784715</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -6008,60 +6008,60 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>model_7_7_4</t>
+          <t>model_7_9_22</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.9999999992355183</v>
+        <v>0.9999997998050718</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6649073081394713</v>
+        <v>0.7442000061820437</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9999999994502354</v>
+        <v>0.9999997282772525</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9999999987556912</v>
+        <v>0.9999988674743444</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9999999991691993</v>
+        <v>0.9999994618086228</v>
       </c>
       <c r="H89" t="n">
-        <v>5.332019723327619e-10</v>
+        <v>1.396296703302e-07</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2337166206399809</v>
+        <v>0.1784124559175529</v>
       </c>
       <c r="J89" t="n">
-        <v>3.138545177715458e-10</v>
+        <v>1.056485003717868e-07</v>
       </c>
       <c r="K89" t="n">
-        <v>4.868877147661604e-10</v>
+        <v>7.596010178685389e-07</v>
       </c>
       <c r="L89" t="n">
-        <v>4.003711162688531e-10</v>
+        <v>4.326247591201629e-07</v>
       </c>
       <c r="M89" t="n">
-        <v>6.312434753116786e-06</v>
+        <v>6.610117779440543e-05</v>
       </c>
       <c r="N89" t="n">
-        <v>2.309116654335077e-05</v>
+        <v>0.0003736705371449561</v>
       </c>
       <c r="O89" t="n">
-        <v>1.000000000447502</v>
+        <v>1.000000117187275</v>
       </c>
       <c r="P89" t="n">
-        <v>2.407420530840557e-05</v>
+        <v>0.0003895784655158645</v>
       </c>
       <c r="Q89" t="n">
-        <v>172.7042416571643</v>
+        <v>161.5685442620385</v>
       </c>
       <c r="R89" t="n">
-        <v>251.9311702735973</v>
+        <v>240.7954728784715</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -6071,60 +6071,60 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>232</v>
+        <v>64</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>model_7_7_3</t>
+          <t>model_7_9_0</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.9999999989493326</v>
+        <v>0.9999997998050718</v>
       </c>
       <c r="D90" t="n">
-        <v>0.6648995475750088</v>
+        <v>0.7442000061820437</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9999999992658696</v>
+        <v>0.9999997282772525</v>
       </c>
       <c r="F90" t="n">
-        <v>0.999999999259471</v>
+        <v>0.9999988674743444</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9999999992657446</v>
+        <v>0.9999994618086228</v>
       </c>
       <c r="H90" t="n">
-        <v>7.328075302124826e-10</v>
+        <v>1.396296703302e-07</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2337220333897797</v>
+        <v>0.1784124559175529</v>
       </c>
       <c r="J90" t="n">
-        <v>4.191070052153439e-10</v>
+        <v>1.056485003717868e-07</v>
       </c>
       <c r="K90" t="n">
-        <v>2.897628425429315e-10</v>
+        <v>7.596010178685389e-07</v>
       </c>
       <c r="L90" t="n">
-        <v>3.53845009959606e-10</v>
+        <v>4.326247591201629e-07</v>
       </c>
       <c r="M90" t="n">
-        <v>7.788755377889258e-06</v>
+        <v>6.610117779440543e-05</v>
       </c>
       <c r="N90" t="n">
-        <v>2.707041799109284e-05</v>
+        <v>0.0003736705371449561</v>
       </c>
       <c r="O90" t="n">
-        <v>1.000000000615025</v>
+        <v>1.000000117187275</v>
       </c>
       <c r="P90" t="n">
-        <v>2.822286172846409e-05</v>
+        <v>0.0003895784655158645</v>
       </c>
       <c r="Q90" t="n">
-        <v>172.0682760533529</v>
+        <v>161.5685442620385</v>
       </c>
       <c r="R90" t="n">
-        <v>251.2952046697859</v>
+        <v>240.7954728784715</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -6134,60 +6134,60 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>234</v>
+        <v>65</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>model_7_7_2</t>
+          <t>model_7_9_18</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.9999999987866073</v>
+        <v>0.9999997998050718</v>
       </c>
       <c r="D91" t="n">
-        <v>0.6649132578559733</v>
+        <v>0.7442000061820437</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9999999994776528</v>
+        <v>0.9999997282772525</v>
       </c>
       <c r="F91" t="n">
-        <v>0.999999999246484</v>
+        <v>0.9999988674743444</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9999999993846913</v>
+        <v>0.9999994618086228</v>
       </c>
       <c r="H91" t="n">
-        <v>8.463033004999989e-10</v>
+        <v>1.396296703302e-07</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2337124708997197</v>
+        <v>0.1784124559175529</v>
       </c>
       <c r="J91" t="n">
-        <v>2.982022362809777e-10</v>
+        <v>1.056485003717868e-07</v>
       </c>
       <c r="K91" t="n">
-        <v>2.948445678491528e-10</v>
+        <v>7.596010178685389e-07</v>
       </c>
       <c r="L91" t="n">
-        <v>2.965234020650653e-10</v>
+        <v>4.326247591201629e-07</v>
       </c>
       <c r="M91" t="n">
-        <v>8.146597837000965e-06</v>
+        <v>6.610117779440543e-05</v>
       </c>
       <c r="N91" t="n">
-        <v>2.90912925202714e-05</v>
+        <v>0.0003736705371449561</v>
       </c>
       <c r="O91" t="n">
-        <v>1.000000000710279</v>
+        <v>1.000000117187275</v>
       </c>
       <c r="P91" t="n">
-        <v>3.032976907013677e-05</v>
+        <v>0.0003895784655158645</v>
       </c>
       <c r="Q91" t="n">
-        <v>171.7802866186856</v>
+        <v>161.5685442620385</v>
       </c>
       <c r="R91" t="n">
-        <v>251.0072152351187</v>
+        <v>240.7954728784715</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -6197,375 +6197,375 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>317</v>
+        <v>1172</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>model_22_7_15</t>
+          <t>model_3_9_20</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.9999999919840447</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D92" t="n">
-        <v>0.6883950691503815</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9999999290416339</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9999999765380368</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9999999726616423</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H92" t="n">
-        <v>5.590876877308144e-09</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I92" t="n">
-        <v>0.217334645553057</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J92" t="n">
-        <v>8.507294233862944e-09</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K92" t="n">
-        <v>1.611306566309559e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L92" t="n">
-        <v>1.231017994847927e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M92" t="n">
-        <v>2.046853175736909e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N92" t="n">
-        <v>7.477216646124508e-05</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O92" t="n">
-        <v>1.000000003375139</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P92" t="n">
-        <v>7.795537238722289e-05</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q92" t="n">
-        <v>200.0042593934624</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R92" t="n">
-        <v>298.7332012077866</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>318</v>
+        <v>1173</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>model_22_7_23</t>
+          <t>model_3_9_21</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.9999999919840447</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D93" t="n">
-        <v>0.6883950691503815</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9999999290416339</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9999999765380368</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9999999726616423</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H93" t="n">
-        <v>5.590876877308144e-09</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.217334645553057</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J93" t="n">
-        <v>8.507294233862944e-09</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K93" t="n">
-        <v>1.611306566309559e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L93" t="n">
-        <v>1.231017994847927e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M93" t="n">
-        <v>2.046853175736909e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N93" t="n">
-        <v>7.477216646124508e-05</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O93" t="n">
-        <v>1.000000003375139</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P93" t="n">
-        <v>7.795537238722289e-05</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q93" t="n">
-        <v>200.0042593934624</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R93" t="n">
-        <v>298.7332012077866</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>319</v>
+        <v>1174</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>model_22_7_12</t>
+          <t>model_3_9_22</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.9999999919840447</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D94" t="n">
-        <v>0.6883950691503815</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9999999290416339</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9999999765380368</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9999999726616423</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H94" t="n">
-        <v>5.590876877308144e-09</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I94" t="n">
-        <v>0.217334645553057</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J94" t="n">
-        <v>8.507294233862944e-09</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K94" t="n">
-        <v>1.611306566309559e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L94" t="n">
-        <v>1.231017994847927e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M94" t="n">
-        <v>2.046853175736909e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N94" t="n">
-        <v>7.477216646124508e-05</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O94" t="n">
-        <v>1.000000003375139</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P94" t="n">
-        <v>7.795537238722289e-05</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q94" t="n">
-        <v>200.0042593934624</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R94" t="n">
-        <v>298.7332012077866</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>320</v>
+        <v>1175</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>model_22_7_10</t>
+          <t>model_3_9_0</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.9999999919840447</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D95" t="n">
-        <v>0.6883950691503815</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9999999290416339</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9999999765380368</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9999999726616423</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H95" t="n">
-        <v>5.590876877308144e-09</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.217334645553057</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J95" t="n">
-        <v>8.507294233862944e-09</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K95" t="n">
-        <v>1.611306566309559e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L95" t="n">
-        <v>1.231017994847927e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M95" t="n">
-        <v>2.046853175736909e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N95" t="n">
-        <v>7.477216646124508e-05</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O95" t="n">
-        <v>1.000000003375139</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P95" t="n">
-        <v>7.795537238722289e-05</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q95" t="n">
-        <v>200.0042593934624</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R95" t="n">
-        <v>298.7332012077866</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>321</v>
+        <v>1184</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>model_22_7_9</t>
+          <t>model_3_9_17</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.9999999919840447</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D96" t="n">
-        <v>0.6883950691503815</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9999999290416339</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9999999765380368</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G96" t="n">
-        <v>0.9999999726616423</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H96" t="n">
-        <v>5.590876877308144e-09</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.217334645553057</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J96" t="n">
-        <v>8.507294233862944e-09</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K96" t="n">
-        <v>1.611306566309559e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L96" t="n">
-        <v>1.231017994847927e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M96" t="n">
-        <v>2.046853175736909e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N96" t="n">
-        <v>7.477216646124508e-05</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O96" t="n">
-        <v>1.000000003375139</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P96" t="n">
-        <v>7.795537238722289e-05</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q96" t="n">
-        <v>200.0042593934624</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R96" t="n">
-        <v>298.7332012077866</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Hidden Size=[20], regularizer=0.5, learning_rate=0.5</t>
+          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>543</v>
+        <v>1185</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>model_3_7_0</t>
+          <t>model_3_9_16</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.9999999782017038</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D97" t="n">
-        <v>0.6555855082500333</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9999998917091525</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9999999189702031</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G97" t="n">
-        <v>0.9999998989152552</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H97" t="n">
-        <v>1.520362647976472e-08</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2402182830795437</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J97" t="n">
-        <v>8.414343367327005e-08</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K97" t="n">
-        <v>1.088696349308891e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L97" t="n">
-        <v>4.750688960010146e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M97" t="n">
-        <v>2.123938392069712e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N97" t="n">
-        <v>0.0001233029864997792</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O97" t="n">
-        <v>1.000000014139435</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0001285522499074443</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q97" t="n">
-        <v>158.0034637067116</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R97" t="n">
-        <v>232.3548890236719</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -6575,60 +6575,60 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>544</v>
+        <v>1187</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>model_3_7_11</t>
+          <t>model_3_9_15</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.9999999781940745</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D98" t="n">
-        <v>0.6555855581853158</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E98" t="n">
-        <v>0.999999891652635</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9999999189733376</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G98" t="n">
-        <v>0.9999998988513028</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H98" t="n">
-        <v>1.520894772343696e-08</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2402182482512536</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J98" t="n">
-        <v>8.418734845135642e-08</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K98" t="n">
-        <v>1.088654234116888e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L98" t="n">
-        <v>4.753694539626266e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M98" t="n">
-        <v>2.115705962381663e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N98" t="n">
-        <v>0.0001233245625308963</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O98" t="n">
-        <v>1.000000014144384</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0001285747444748746</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q98" t="n">
-        <v>158.0027638325489</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R98" t="n">
-        <v>232.3541891495092</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -6638,60 +6638,60 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>545</v>
+        <v>1189</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>model_3_7_1</t>
+          <t>model_3_9_24</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.9999999781940745</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D99" t="n">
-        <v>0.6555855581853158</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E99" t="n">
-        <v>0.999999891652635</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9999999189733376</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G99" t="n">
-        <v>0.9999998988513028</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H99" t="n">
-        <v>1.520894772343696e-08</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2402182482512536</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J99" t="n">
-        <v>8.418734845135642e-08</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K99" t="n">
-        <v>1.088654234116888e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L99" t="n">
-        <v>4.753694539626266e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M99" t="n">
-        <v>2.115705962381663e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N99" t="n">
-        <v>0.0001233245625308963</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O99" t="n">
-        <v>1.000000014144384</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0001285747444748746</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q99" t="n">
-        <v>158.0027638325489</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R99" t="n">
-        <v>232.3541891495092</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -6701,125 +6701,62 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>546</v>
+        <v>1190</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>model_3_7_13</t>
+          <t>model_3_9_11</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.9999999781940745</v>
+        <v>0.9999408192624218</v>
       </c>
       <c r="D100" t="n">
-        <v>0.6555855581853158</v>
+        <v>0.6640299891590884</v>
       </c>
       <c r="E100" t="n">
-        <v>0.999999891652635</v>
+        <v>0.999993012051092</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9999999189733376</v>
+        <v>0.999994878119744</v>
       </c>
       <c r="G100" t="n">
-        <v>0.9999998988513028</v>
+        <v>0.9999942473472756</v>
       </c>
       <c r="H100" t="n">
-        <v>1.520894772343696e-08</v>
+        <v>4.127670441559672e-05</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2402182482512536</v>
+        <v>0.2343285230547424</v>
       </c>
       <c r="J100" t="n">
-        <v>8.418734845135642e-08</v>
+        <v>8.150481020462978e-06</v>
       </c>
       <c r="K100" t="n">
-        <v>1.088654234116888e-08</v>
+        <v>3.160451482841003e-06</v>
       </c>
       <c r="L100" t="n">
-        <v>4.753694539626266e-08</v>
+        <v>5.65546625165199e-06</v>
       </c>
       <c r="M100" t="n">
-        <v>2.115705962381663e-05</v>
+        <v>0.001888904544478138</v>
       </c>
       <c r="N100" t="n">
-        <v>0.0001233245625308963</v>
+        <v>0.006424694888910813</v>
       </c>
       <c r="O100" t="n">
-        <v>1.000000014144384</v>
+        <v>1.000038387505456</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0001285747444748746</v>
+        <v>0.006698207451283605</v>
       </c>
       <c r="Q100" t="n">
-        <v>158.0027638325489</v>
+        <v>142.1904245497429</v>
       </c>
       <c r="R100" t="n">
-        <v>232.3541891495092</v>
+        <v>216.5418498667031</v>
       </c>
       <c r="S100" t="inlineStr">
-        <is>
-          <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>547</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>model_3_7_23</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>0.9999999781940745</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0.6555855581853158</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0.999999891652635</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.9999999189733376</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0.9999998988513028</v>
-      </c>
-      <c r="H101" t="n">
-        <v>1.520894772343696e-08</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0.2402182482512536</v>
-      </c>
-      <c r="J101" t="n">
-        <v>8.418734845135642e-08</v>
-      </c>
-      <c r="K101" t="n">
-        <v>1.088654234116888e-08</v>
-      </c>
-      <c r="L101" t="n">
-        <v>4.753694539626266e-08</v>
-      </c>
-      <c r="M101" t="n">
-        <v>2.115705962381663e-05</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0.0001233245625308963</v>
-      </c>
-      <c r="O101" t="n">
-        <v>1.000000014144384</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0.0001285747444748746</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>158.0027638325489</v>
-      </c>
-      <c r="R101" t="n">
-        <v>232.3541891495092</v>
-      </c>
-      <c r="S101" t="inlineStr">
         <is>
           <t>Hidden Size=[15], regularizer=0.3, learning_rate=0.1</t>
         </is>
